--- a/Excel/02Functions_Formulas/sample-data-fx.blank.xlsx
+++ b/Excel/02Functions_Formulas/sample-data-fx.blank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30117"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell 7490\Documents\PythonClassSF\DataAnalytics01\Excel\02Functions_Formulas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F61C9D7-E9A8-4D8D-AC5F-4217D60932A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF60EF9A-8E98-425F-BFB5-280FCDC9DB38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{26D4546B-D2A1-4444-8EAF-A6228F96F0C1}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="6" xr2:uid="{26D4546B-D2A1-4444-8EAF-A6228F96F0C1}"/>
   </bookViews>
   <sheets>
     <sheet name="Concepts" sheetId="2" r:id="rId1"/>
@@ -18,6 +18,8 @@
     <sheet name="Task 01" sheetId="3" r:id="rId3"/>
     <sheet name="Task 02" sheetId="4" r:id="rId4"/>
     <sheet name="Task 03" sheetId="5" r:id="rId5"/>
+    <sheet name="Task 04" sheetId="6" r:id="rId6"/>
+    <sheet name="Task 05" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,14 +42,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -62,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2400" uniqueCount="771">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2412" uniqueCount="780">
   <si>
     <t>Essential Excel Functions &amp; Formulas</t>
   </si>
@@ -2375,6 +2377,33 @@
   </si>
   <si>
     <t>Average Salary</t>
+  </si>
+  <si>
+    <t>All emps</t>
+  </si>
+  <si>
+    <t>Lowest Salary</t>
+  </si>
+  <si>
+    <t>Highest Salary</t>
+  </si>
+  <si>
+    <t>Top 5 Salaries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                 References for top 5 salaries</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Link to the Cell. Change the values then have the top give value rows.</t>
+  </si>
+  <si>
+    <t>with Sort + Take</t>
+  </si>
+  <si>
+    <t>Departments</t>
+  </si>
+  <si>
+    <t>Count:</t>
   </si>
 </sst>
 </file>
@@ -2382,11 +2411,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
-    <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="164" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2427,6 +2456,13 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2518,7 +2554,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -2528,7 +2564,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2588,13 +2624,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2605,10 +2643,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="167" formatCode="d\-mmm\-yy"/>
+      <numFmt numFmtId="20" formatCode="d\-mmm\-yy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+      <numFmt numFmtId="10" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2621,6 +2659,106 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>628650</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="5" name="">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15296B76-45B2-421A-8B14-C46094E7F081}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="6943725" y="866775"/>
+            <a:ext cx="476250" cy="1019175"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="5" name="">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15296B76-45B2-421A-8B14-C46094E7F081}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6926139" y="849215"/>
+              <a:ext cx="511780" cy="1054653"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/ink/ink1.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.1" units="cm"/>
+      <inkml:brushProperty name="height" value="0.1" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">19341 3007 16383 0 0,'0'-3'0'0'0,"0"-4"0"0"0,0-3 0 0 0,0-4 0 0 0,0-2 0 0 0,0-8 0 0 0,3 1 0 0 0,1 1 0 0 0,0 2 0 0 0,-1 0 0 0 0,2-2 0 0 0,0 0 0 0 0,3 1 0 0 0,-1-3 0 0 0,-1 1 0 0 0,2 0 0 0 0,-2-1 0 0 0,0 0 0 0 0,-3 1 0 0 0,-1 2 0 0 0,3 4 0 0 0,-1 2 0 0 0,3 1 0 0 0,6 2 0 0 0,0 1 0 0 0,-1-1 0 0 0,-3-2 0 0 0,0-1 0 0 0,-2-1 0 0 0,1 2 0 0 0,3 4 0 0 0,1 3 0 0 0,0 0 0 0 0,0 1 0 0 0,2-4 0 0 0,3-1 0 0 0,3 2 0 0 0,1 2 0 0 0,-1 3 0 0 0,0 1 0 0 0,-1 2 0 0 0,0 4 0 0 0,-1 1 0 0 0,3 0 0 0 0,3 3 0 0 0,5 2 0 0 0,2 1 0 0 0,0-3 0 0 0,-3 2 0 0 0,-1-1 0 0 0,0 0 0 0 0,-4 0 0 0 0,-1-2 0 0 0,-2 2 0 0 0,-2-2 0 0 0,0 2 0 0 0,-1-1 0 0 0,1-1 0 0 0,-4 1 0 0 0,-1 0 0 0 0,1 4 0 0 0,0 1 0 0 0,-2 0 0 0 0,1 0 0 0 0,0-1 0 0 0,1-1 0 0 0,-1 0 0 0 0,-1 2 0 0 0,4-2 0 0 0,0 1 0 0 0,-1-1 0 0 0,-2 0 0 0 0,-1-2 0 0 0,-2 2 0 0 0,0-2 0 0 0,-1 1 0 0 0,-3 2 0 0 0,1 0 0 0 0,-1 0 0 0 0,2-2 0 0 0,2 1 0 0 0,3-1 0 0 0,-1 1 0 0 0,-3 1 0 0 0,3-1 0 0 0,0 2 0 0 0,1-3 0 0 0,-2 1 0 0 0,-3 5 0 0 0,0 2 0 0 0,-1 2 0 0 0,-1 1 0 0 0,0-4 0 0 0,0-1 0 0 0,2-3 0 0 0,-1-1 0 0 0,2 1 0 0 0,-1 2 0 0 0,1-3 0 0 0,-1 1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0-1 0 0 0,1-1 0 0 0,0 0 0 0 0,-3 2 0 0 0,2-2 0 0 0,0 1 0 0 0,1 2 0 0 0,0 4 0 0 0,-3 2 0 0 0,3 1 0 0 0,-2 1 0 0 0,-1-1 0 0 0,-1-1 0 0 0,-2-1 0 0 0,-1 4 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 0 0 0 0,0-2 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 3 0 0 0,0 0 0 0 0,0 1 0 0 0,0-2 0 0 0,0 0 0 0 0,-3-4 0 0 0,-1-2 0 0 0,-3 0 0 0 0,0 1 0 0 0,1 3 0 0 0,-4 2 0 0 0,-1 1 0 0 0,-1-4 0 0 0,-2-1 0 0 0,2-1 0 0 0,-1-2 0 0 0,0-5 0 0 0,1 1 0 0 0,0-2 0 0 0,0-2 0 0 0,-6-2 0 0 0,-1-1 0 0 0,-1-1 0 0 0,0-1 0 0 0,0-1 0 0 0,4-2 0 0 0,1-4 0 0 0,4-4 0 0 0,0 0 0 0 0,-1 1 0 0 0,-4 4 0 0 0,-3 1 0 0 0,0 3 0 0 0,-1 1 0 0 0,0 1 0 0 0,1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,-2 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,2 0 0 0 0,3 3 0 0 0,5 4 0 0 0,5 4 0 0 0,0 3 0 0 0,1 2 0 0 0,-1-2 0 0 0,-2 0 0 0 0,0 1 0 0 0,1 0 0 0 0,-3 1 0 0 0,0 1 0 0 0,-2-3 0 0 0,0 0 0 0 0,0 0 0 0 0,1-3 0 0 0,-1 1 0 0 0,-2-2 0 0 0,0 3 0 0 0,1 2 0 0 0,4 2 0 0 0,0-2 0 0 0,2-1 0 0 0,-3-2 0 0 0,-1-1 0 0 0,0-1 0 0 0,1-1 0 0 0,-1-1 0 0 0,0-2 0 0 0,1 1 0 0 0,0 2 0 0 0,-2 6 0 0 0,-1 0 0 0 0,1 1 0 0 0,1 0 0 0 0,-4-2 0 0 0,-3-1 0 0 0,0-2 0 0 0,-1-3 0 0 0,1-4 0 0 0,0-1 0 0 0,0-2 0 0 0,1-1 0 0 0,0 0 0 0 0,0 2 0 0 0,1 1 0 0 0,-1 4 0 0 0,-2-1 0 0 0,-2 0 0 0 0,1-1 0 0 0,0-3 0 0 0,1 0 0 0 0,1-1 0 0 0,1-1 0 0 0,3-3 0 0 0,4-4 0 0 0,5-5 0 0 0,2-2 0 0 0,6 1 0 0 0,1-3 0 0 0,5 0 0 0 0,0 1 0 0 0,-2 0 0 0 0,3 1 0 0 0,1 5 0 0 0,3 0 0 0 0,1 1 0 0 0,3 3 0 0 0,0 2 0 0 0,1 1 0 0 0,3 1 0 0 0,1 1 0 0 0,-3 3 0 0 0,-5 5 0 0 0,-5 6 0 0 0,-4 4 0 0 0,-2 2 0 0 0,-3 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,0-1 0 0 0,3-3 0 0 0,1-2 0 0 0,1 3 0 0 0,2-2 0 0 0,3-3 0 0 0,0 0 0 0 0,1-3 0 0 0,0 0 0 0 0,-3 2 0 0 0,1 2 0 0 0,-1 2 0 0 0,2-2 0 0 0,-2 0 0 0 0,5 1 0 0 0,3-3 0 0 0,-1 1 0 0 0,0-2 0 0 0,1 0 0 0 0,-2 2 0 0 0,-4 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,0 2 0 0 0,3-3 0 0 0,1 1 0 0 0,6-2 0 0 0,-1 0 0 0 0,0 4 0 0 0,0 1 0 0 0,0 0 0 0 0,0-3 0 0 0,-2 0 0 0 0,-2-2 0 0 0,1 1 0 0 0,1-3 0 0 0,0-2 0 0 0,1-1 0 0 0,1-3 0 0 0,1-1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,2-1 0 0 0,2 1 0 0 0,0 0 0 0 0,-2 0 0 0 0,-3-3 0 0 0,-5-4 0 0 0,-4-7 0 0 0,-4-4 0 0 0,0 1 0 0 0,1 1 0 0 0,-2-1 0 0 0,-1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,-1-1 0 0 0,0 7 0 0 0,0 7 0 0 0,3 5 0 0 0,0 5 0 0 0,1 5 0 0 0,-1 3 0 0 0,2-1 0 0 0,0 1 0 0 0,3 3 0 0 0,-1 3 0 0 0,5-3 0 0 0,1-1 0 0 0,-3 0 0 0 0,1-3 0 0 0,-3-1 0 0 0,-1 1 0 0 0,-3 1 0 0 0,-1 2 0 0 0,-2 3 0 0 0,-1 2 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0-1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-6 1 0 0 0,-2 0 0 0 0,0-1 0 0 0,-1-2 0 0 0,1 1 0 0 0,1 2 0 0 0,3 1 0 0 0,1-1 0 0 0,-1-2 0 0 0,-1-2 0 0 0,-2-3 0 0 0,1 0 0 0 0,-3-2 0 0 0,1 0 0 0 0,2 2 0 0 0,1 5 0 0 0,-1 0 0 0 0,1-1 0 0 0,-2-1 0 0 0,-3-4 0 0 0,-6-4 0 0 0,-3 0 0 0 0,-1 0 0 0 0,-1-2 0 0 0,1-1 0 0 0,1-2 0 0 0,0 0 0 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-4 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,1 3 0 0 0,1 1 0 0 0,0-1 0 0 0,-3 1 0 0 0,3 1 0 0 0,1 0 0 0 0,3 3 0 0 0,1-1 0 0 0,0-1 0 0 0,-1-2 0 0 0,-1-1 0 0 0,-1-2 0 0 0,0 0 0 0 0,-2-1 0 0 0,1 0 0 0 0,-1-1 0 0 0,3-2 0 0 0,4-4 0 0 0,1-4 0 0 0,2 0 0 0 0</inkml:trace>
+</inkml:ink>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2946,31 +3084,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{627306E8-967B-437C-B97A-A3AA7E6942D3}">
   <dimension ref="A1:N265"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="1.7265625" customWidth="1"/>
-    <col min="2" max="2" width="3.7265625" customWidth="1"/>
-    <col min="3" max="3" width="4.54296875" customWidth="1"/>
-    <col min="4" max="4" width="48.1796875" customWidth="1"/>
+    <col min="1" max="1" width="1.7109375" customWidth="1"/>
+    <col min="2" max="2" width="3.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" customWidth="1"/>
+    <col min="4" max="4" width="48.140625" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="37.453125" customWidth="1"/>
-    <col min="7" max="7" width="36.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.81640625" customWidth="1"/>
-    <col min="10" max="10" width="11.81640625" customWidth="1"/>
-    <col min="12" max="12" width="16.453125" customWidth="1"/>
-    <col min="13" max="13" width="15.54296875" customWidth="1"/>
-    <col min="14" max="14" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.7265625" customWidth="1"/>
+    <col min="6" max="6" width="37.42578125" customWidth="1"/>
+    <col min="7" max="7" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" customWidth="1"/>
+    <col min="12" max="12" width="16.42578125" customWidth="1"/>
+    <col min="13" max="13" width="15.5703125" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" ht="52.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" s="2" customFormat="1" ht="52.5" customHeight="1">
       <c r="A1" s="1"/>
       <c r="C1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" ht="21" customHeight="1">
       <c r="C5" s="16"/>
       <c r="D5" s="17" t="s">
         <v>1</v>
@@ -2983,7 +3121,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" ht="21" customHeight="1">
       <c r="C6" s="10">
         <v>1</v>
       </c>
@@ -3001,7 +3139,7 @@
       <c r="J6" s="6"/>
       <c r="N6" s="4"/>
     </row>
-    <row r="7" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" ht="21" customHeight="1">
       <c r="C7" s="12">
         <v>2</v>
       </c>
@@ -3017,7 +3155,7 @@
       <c r="J7" s="6"/>
       <c r="N7" s="4"/>
     </row>
-    <row r="8" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" ht="21" customHeight="1">
       <c r="C8" s="12">
         <v>3</v>
       </c>
@@ -3035,7 +3173,7 @@
       <c r="J8" s="6"/>
       <c r="N8" s="4"/>
     </row>
-    <row r="9" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" ht="21" customHeight="1">
       <c r="C9" s="12">
         <v>4</v>
       </c>
@@ -3051,7 +3189,7 @@
       <c r="J9" s="6"/>
       <c r="N9" s="4"/>
     </row>
-    <row r="10" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" ht="21" customHeight="1">
       <c r="C10" s="12">
         <v>5</v>
       </c>
@@ -3069,7 +3207,7 @@
       <c r="J10" s="6"/>
       <c r="N10" s="4"/>
     </row>
-    <row r="11" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" ht="21" customHeight="1">
       <c r="C11" s="12">
         <v>6</v>
       </c>
@@ -3085,7 +3223,7 @@
       <c r="J11" s="6"/>
       <c r="N11" s="4"/>
     </row>
-    <row r="12" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" ht="21" customHeight="1">
       <c r="C12" s="12">
         <v>7</v>
       </c>
@@ -3103,7 +3241,7 @@
       <c r="J12" s="6"/>
       <c r="N12" s="4"/>
     </row>
-    <row r="13" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" ht="21" customHeight="1">
       <c r="C13" s="18">
         <v>8</v>
       </c>
@@ -3119,7 +3257,7 @@
       <c r="J13" s="6"/>
       <c r="N13" s="4"/>
     </row>
-    <row r="14" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" ht="21" customHeight="1">
       <c r="C14" s="18">
         <v>9</v>
       </c>
@@ -3137,7 +3275,7 @@
       <c r="J14" s="6"/>
       <c r="N14" s="4"/>
     </row>
-    <row r="15" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" ht="29.1">
       <c r="C15" s="21">
         <v>10</v>
       </c>
@@ -3155,1252 +3293,1252 @@
       <c r="J15" s="6"/>
       <c r="N15" s="4"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14">
       <c r="H16" s="5"/>
       <c r="J16" s="6"/>
       <c r="N16" s="4"/>
     </row>
-    <row r="17" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="8:14">
       <c r="H17" s="5"/>
       <c r="J17" s="6"/>
       <c r="N17" s="4"/>
     </row>
-    <row r="18" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="8:14">
       <c r="H18" s="5"/>
       <c r="J18" s="6"/>
       <c r="N18" s="4"/>
     </row>
-    <row r="19" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="8:14">
       <c r="H19" s="5"/>
       <c r="J19" s="6"/>
       <c r="N19" s="4"/>
     </row>
-    <row r="20" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="8:14">
       <c r="H20" s="5"/>
       <c r="J20" s="6"/>
       <c r="N20" s="4"/>
     </row>
-    <row r="21" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="8:14">
       <c r="H21" s="5"/>
       <c r="J21" s="6"/>
       <c r="N21" s="4"/>
     </row>
-    <row r="22" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="8:14">
       <c r="H22" s="5"/>
       <c r="J22" s="6"/>
       <c r="N22" s="4"/>
     </row>
-    <row r="23" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="8:14">
       <c r="H23" s="5"/>
       <c r="J23" s="6"/>
       <c r="N23" s="4"/>
     </row>
-    <row r="24" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="8:14">
       <c r="H24" s="5"/>
       <c r="J24" s="6"/>
       <c r="N24" s="4"/>
     </row>
-    <row r="25" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="8:14">
       <c r="H25" s="5"/>
       <c r="J25" s="6"/>
       <c r="N25" s="4"/>
     </row>
-    <row r="26" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="26" spans="8:14">
       <c r="H26" s="5"/>
       <c r="J26" s="6"/>
       <c r="N26" s="4"/>
     </row>
-    <row r="27" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="27" spans="8:14">
       <c r="H27" s="5"/>
       <c r="J27" s="6"/>
       <c r="N27" s="4"/>
     </row>
-    <row r="28" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="28" spans="8:14">
       <c r="H28" s="5"/>
       <c r="J28" s="6"/>
       <c r="N28" s="4"/>
     </row>
-    <row r="29" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="29" spans="8:14">
       <c r="H29" s="5"/>
       <c r="J29" s="6"/>
       <c r="N29" s="4"/>
     </row>
-    <row r="30" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="30" spans="8:14">
       <c r="H30" s="5"/>
       <c r="J30" s="6"/>
       <c r="N30" s="4"/>
     </row>
-    <row r="31" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="31" spans="8:14">
       <c r="H31" s="5"/>
       <c r="J31" s="6"/>
       <c r="N31" s="4"/>
     </row>
-    <row r="32" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="32" spans="8:14">
       <c r="H32" s="5"/>
       <c r="J32" s="6"/>
       <c r="N32" s="4"/>
     </row>
-    <row r="33" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="8:14">
       <c r="H33" s="5"/>
       <c r="J33" s="6"/>
       <c r="N33" s="4"/>
     </row>
-    <row r="34" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="8:14">
       <c r="H34" s="5"/>
       <c r="J34" s="6"/>
       <c r="N34" s="4"/>
     </row>
-    <row r="35" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="8:14">
       <c r="H35" s="5"/>
       <c r="J35" s="6"/>
       <c r="N35" s="4"/>
     </row>
-    <row r="36" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="8:14">
       <c r="H36" s="5"/>
       <c r="J36" s="6"/>
       <c r="N36" s="4"/>
     </row>
-    <row r="37" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="8:14">
       <c r="H37" s="5"/>
       <c r="J37" s="6"/>
       <c r="N37" s="4"/>
     </row>
-    <row r="38" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="8:14">
       <c r="H38" s="5"/>
       <c r="J38" s="6"/>
       <c r="N38" s="4"/>
     </row>
-    <row r="39" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="8:14">
       <c r="H39" s="5"/>
       <c r="J39" s="6"/>
       <c r="N39" s="4"/>
     </row>
-    <row r="40" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="8:14">
       <c r="H40" s="5"/>
       <c r="J40" s="6"/>
       <c r="N40" s="4"/>
     </row>
-    <row r="41" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="41" spans="8:14">
       <c r="H41" s="5"/>
       <c r="J41" s="6"/>
       <c r="N41" s="4"/>
     </row>
-    <row r="42" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="42" spans="8:14">
       <c r="H42" s="5"/>
       <c r="J42" s="6"/>
       <c r="N42" s="4"/>
     </row>
-    <row r="43" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="43" spans="8:14">
       <c r="H43" s="5"/>
       <c r="J43" s="6"/>
       <c r="N43" s="4"/>
     </row>
-    <row r="44" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="44" spans="8:14">
       <c r="H44" s="5"/>
       <c r="J44" s="6"/>
       <c r="N44" s="4"/>
     </row>
-    <row r="45" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="45" spans="8:14">
       <c r="H45" s="5"/>
       <c r="J45" s="6"/>
       <c r="N45" s="4"/>
     </row>
-    <row r="46" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="46" spans="8:14">
       <c r="H46" s="5"/>
       <c r="J46" s="6"/>
       <c r="N46" s="4"/>
     </row>
-    <row r="47" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="47" spans="8:14">
       <c r="H47" s="5"/>
       <c r="J47" s="6"/>
       <c r="N47" s="4"/>
     </row>
-    <row r="48" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="48" spans="8:14">
       <c r="H48" s="5"/>
       <c r="J48" s="6"/>
       <c r="N48" s="4"/>
     </row>
-    <row r="49" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="49" spans="8:14">
       <c r="H49" s="5"/>
       <c r="J49" s="6"/>
       <c r="N49" s="4"/>
     </row>
-    <row r="50" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="50" spans="8:14">
       <c r="H50" s="5"/>
       <c r="J50" s="6"/>
       <c r="N50" s="4"/>
     </row>
-    <row r="51" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="51" spans="8:14">
       <c r="H51" s="5"/>
       <c r="J51" s="6"/>
       <c r="N51" s="4"/>
     </row>
-    <row r="52" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="52" spans="8:14">
       <c r="H52" s="5"/>
       <c r="J52" s="6"/>
       <c r="N52" s="4"/>
     </row>
-    <row r="53" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="53" spans="8:14">
       <c r="H53" s="5"/>
       <c r="J53" s="6"/>
       <c r="N53" s="4"/>
     </row>
-    <row r="54" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="54" spans="8:14">
       <c r="H54" s="5"/>
       <c r="J54" s="6"/>
       <c r="N54" s="4"/>
     </row>
-    <row r="55" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="55" spans="8:14">
       <c r="H55" s="5"/>
       <c r="J55" s="6"/>
       <c r="N55" s="4"/>
     </row>
-    <row r="56" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="56" spans="8:14">
       <c r="H56" s="5"/>
       <c r="J56" s="6"/>
       <c r="N56" s="4"/>
     </row>
-    <row r="57" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="57" spans="8:14">
       <c r="H57" s="5"/>
       <c r="J57" s="6"/>
       <c r="N57" s="4"/>
     </row>
-    <row r="58" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="58" spans="8:14">
       <c r="H58" s="5"/>
       <c r="J58" s="6"/>
       <c r="N58" s="4"/>
     </row>
-    <row r="59" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="59" spans="8:14">
       <c r="H59" s="5"/>
       <c r="J59" s="6"/>
       <c r="N59" s="4"/>
     </row>
-    <row r="60" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="60" spans="8:14">
       <c r="H60" s="5"/>
       <c r="J60" s="6"/>
       <c r="N60" s="4"/>
     </row>
-    <row r="61" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="61" spans="8:14">
       <c r="H61" s="5"/>
       <c r="J61" s="6"/>
       <c r="N61" s="4"/>
     </row>
-    <row r="62" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="62" spans="8:14">
       <c r="H62" s="5"/>
       <c r="J62" s="6"/>
       <c r="N62" s="4"/>
     </row>
-    <row r="63" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="63" spans="8:14">
       <c r="H63" s="5"/>
       <c r="J63" s="6"/>
       <c r="N63" s="4"/>
     </row>
-    <row r="64" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="64" spans="8:14">
       <c r="H64" s="5"/>
       <c r="J64" s="6"/>
       <c r="N64" s="4"/>
     </row>
-    <row r="65" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="65" spans="8:14">
       <c r="H65" s="5"/>
       <c r="J65" s="6"/>
       <c r="N65" s="4"/>
     </row>
-    <row r="66" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="66" spans="8:14">
       <c r="H66" s="5"/>
       <c r="J66" s="6"/>
       <c r="N66" s="4"/>
     </row>
-    <row r="67" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="67" spans="8:14">
       <c r="H67" s="5"/>
       <c r="J67" s="6"/>
       <c r="N67" s="4"/>
     </row>
-    <row r="68" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="68" spans="8:14">
       <c r="H68" s="5"/>
       <c r="J68" s="6"/>
       <c r="N68" s="4"/>
     </row>
-    <row r="69" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="69" spans="8:14">
       <c r="H69" s="5"/>
       <c r="J69" s="6"/>
       <c r="N69" s="4"/>
     </row>
-    <row r="70" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="70" spans="8:14">
       <c r="H70" s="5"/>
       <c r="J70" s="6"/>
       <c r="N70" s="4"/>
     </row>
-    <row r="71" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="71" spans="8:14">
       <c r="H71" s="5"/>
       <c r="J71" s="6"/>
       <c r="N71" s="4"/>
     </row>
-    <row r="72" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="72" spans="8:14">
       <c r="H72" s="5"/>
       <c r="J72" s="6"/>
       <c r="N72" s="4"/>
     </row>
-    <row r="73" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="73" spans="8:14">
       <c r="H73" s="5"/>
       <c r="J73" s="6"/>
       <c r="N73" s="4"/>
     </row>
-    <row r="74" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="74" spans="8:14">
       <c r="H74" s="5"/>
       <c r="J74" s="6"/>
       <c r="N74" s="4"/>
     </row>
-    <row r="75" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="75" spans="8:14">
       <c r="H75" s="5"/>
       <c r="J75" s="6"/>
       <c r="N75" s="4"/>
     </row>
-    <row r="76" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="76" spans="8:14">
       <c r="H76" s="5"/>
       <c r="J76" s="6"/>
       <c r="N76" s="4"/>
     </row>
-    <row r="77" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="77" spans="8:14">
       <c r="H77" s="5"/>
       <c r="J77" s="6"/>
       <c r="N77" s="4"/>
     </row>
-    <row r="78" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="78" spans="8:14">
       <c r="H78" s="5"/>
       <c r="J78" s="6"/>
       <c r="N78" s="4"/>
     </row>
-    <row r="79" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="79" spans="8:14">
       <c r="H79" s="5"/>
       <c r="J79" s="6"/>
       <c r="N79" s="4"/>
     </row>
-    <row r="80" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="80" spans="8:14">
       <c r="H80" s="5"/>
       <c r="J80" s="6"/>
       <c r="N80" s="4"/>
     </row>
-    <row r="81" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="81" spans="8:14">
       <c r="H81" s="5"/>
       <c r="J81" s="6"/>
       <c r="N81" s="4"/>
     </row>
-    <row r="82" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="82" spans="8:14">
       <c r="H82" s="5"/>
       <c r="J82" s="6"/>
       <c r="N82" s="4"/>
     </row>
-    <row r="83" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="83" spans="8:14">
       <c r="H83" s="5"/>
       <c r="J83" s="6"/>
       <c r="N83" s="4"/>
     </row>
-    <row r="84" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="84" spans="8:14">
       <c r="H84" s="5"/>
       <c r="J84" s="6"/>
       <c r="N84" s="4"/>
     </row>
-    <row r="85" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="85" spans="8:14">
       <c r="H85" s="5"/>
       <c r="J85" s="6"/>
       <c r="N85" s="4"/>
     </row>
-    <row r="86" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="86" spans="8:14">
       <c r="H86" s="5"/>
       <c r="J86" s="6"/>
       <c r="N86" s="4"/>
     </row>
-    <row r="87" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="87" spans="8:14">
       <c r="H87" s="5"/>
       <c r="J87" s="6"/>
       <c r="N87" s="4"/>
     </row>
-    <row r="88" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="88" spans="8:14">
       <c r="H88" s="5"/>
       <c r="J88" s="6"/>
       <c r="N88" s="4"/>
     </row>
-    <row r="89" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="89" spans="8:14">
       <c r="H89" s="5"/>
       <c r="J89" s="6"/>
       <c r="N89" s="4"/>
     </row>
-    <row r="90" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="90" spans="8:14">
       <c r="H90" s="5"/>
       <c r="J90" s="6"/>
       <c r="N90" s="4"/>
     </row>
-    <row r="91" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="91" spans="8:14">
       <c r="H91" s="5"/>
       <c r="J91" s="6"/>
       <c r="N91" s="4"/>
     </row>
-    <row r="92" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="92" spans="8:14">
       <c r="H92" s="5"/>
       <c r="J92" s="6"/>
       <c r="N92" s="4"/>
     </row>
-    <row r="93" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="93" spans="8:14">
       <c r="H93" s="5"/>
       <c r="J93" s="6"/>
       <c r="N93" s="4"/>
     </row>
-    <row r="94" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="94" spans="8:14">
       <c r="H94" s="5"/>
       <c r="J94" s="6"/>
       <c r="N94" s="4"/>
     </row>
-    <row r="95" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="95" spans="8:14">
       <c r="H95" s="5"/>
       <c r="J95" s="6"/>
       <c r="N95" s="4"/>
     </row>
-    <row r="96" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="96" spans="8:14">
       <c r="H96" s="5"/>
       <c r="J96" s="6"/>
       <c r="N96" s="4"/>
     </row>
-    <row r="97" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="97" spans="8:14">
       <c r="H97" s="5"/>
       <c r="J97" s="6"/>
       <c r="N97" s="4"/>
     </row>
-    <row r="98" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="98" spans="8:14">
       <c r="H98" s="5"/>
       <c r="J98" s="6"/>
       <c r="N98" s="4"/>
     </row>
-    <row r="99" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="99" spans="8:14">
       <c r="H99" s="5"/>
       <c r="J99" s="6"/>
       <c r="N99" s="4"/>
     </row>
-    <row r="100" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="100" spans="8:14">
       <c r="H100" s="5"/>
       <c r="J100" s="6"/>
       <c r="N100" s="4"/>
     </row>
-    <row r="101" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="101" spans="8:14">
       <c r="H101" s="5"/>
       <c r="J101" s="6"/>
       <c r="N101" s="4"/>
     </row>
-    <row r="102" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="102" spans="8:14">
       <c r="H102" s="5"/>
       <c r="J102" s="6"/>
       <c r="N102" s="4"/>
     </row>
-    <row r="103" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="103" spans="8:14">
       <c r="H103" s="5"/>
       <c r="J103" s="6"/>
       <c r="N103" s="4"/>
     </row>
-    <row r="104" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="104" spans="8:14">
       <c r="H104" s="5"/>
       <c r="J104" s="6"/>
       <c r="N104" s="4"/>
     </row>
-    <row r="105" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="105" spans="8:14">
       <c r="H105" s="5"/>
       <c r="J105" s="6"/>
       <c r="N105" s="4"/>
     </row>
-    <row r="106" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="106" spans="8:14">
       <c r="H106" s="5"/>
       <c r="J106" s="6"/>
       <c r="N106" s="4"/>
     </row>
-    <row r="107" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="107" spans="8:14">
       <c r="H107" s="5"/>
       <c r="J107" s="6"/>
       <c r="N107" s="4"/>
     </row>
-    <row r="108" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="108" spans="8:14">
       <c r="H108" s="5"/>
       <c r="J108" s="6"/>
       <c r="N108" s="4"/>
     </row>
-    <row r="109" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="109" spans="8:14">
       <c r="H109" s="5"/>
       <c r="J109" s="6"/>
       <c r="N109" s="4"/>
     </row>
-    <row r="110" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="110" spans="8:14">
       <c r="H110" s="5"/>
       <c r="J110" s="6"/>
       <c r="N110" s="4"/>
     </row>
-    <row r="111" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="111" spans="8:14">
       <c r="H111" s="5"/>
       <c r="J111" s="6"/>
       <c r="N111" s="4"/>
     </row>
-    <row r="112" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="112" spans="8:14">
       <c r="H112" s="5"/>
       <c r="J112" s="6"/>
       <c r="N112" s="4"/>
     </row>
-    <row r="113" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="113" spans="8:14">
       <c r="H113" s="5"/>
       <c r="J113" s="6"/>
       <c r="N113" s="4"/>
     </row>
-    <row r="114" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="114" spans="8:14">
       <c r="H114" s="5"/>
       <c r="J114" s="6"/>
       <c r="N114" s="4"/>
     </row>
-    <row r="115" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="115" spans="8:14">
       <c r="H115" s="5"/>
       <c r="J115" s="6"/>
       <c r="N115" s="4"/>
     </row>
-    <row r="116" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="116" spans="8:14">
       <c r="H116" s="5"/>
       <c r="J116" s="6"/>
       <c r="N116" s="4"/>
     </row>
-    <row r="117" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="117" spans="8:14">
       <c r="H117" s="5"/>
       <c r="J117" s="6"/>
       <c r="N117" s="4"/>
     </row>
-    <row r="118" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="118" spans="8:14">
       <c r="H118" s="5"/>
       <c r="J118" s="6"/>
       <c r="N118" s="4"/>
     </row>
-    <row r="119" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="119" spans="8:14">
       <c r="H119" s="5"/>
       <c r="J119" s="6"/>
       <c r="N119" s="4"/>
     </row>
-    <row r="120" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="120" spans="8:14">
       <c r="H120" s="5"/>
       <c r="J120" s="6"/>
       <c r="N120" s="4"/>
     </row>
-    <row r="121" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="121" spans="8:14">
       <c r="H121" s="5"/>
       <c r="J121" s="6"/>
       <c r="N121" s="4"/>
     </row>
-    <row r="122" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="122" spans="8:14">
       <c r="H122" s="5"/>
       <c r="J122" s="6"/>
       <c r="N122" s="4"/>
     </row>
-    <row r="123" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="123" spans="8:14">
       <c r="H123" s="5"/>
       <c r="J123" s="6"/>
       <c r="N123" s="4"/>
     </row>
-    <row r="124" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="124" spans="8:14">
       <c r="H124" s="5"/>
       <c r="J124" s="6"/>
       <c r="N124" s="4"/>
     </row>
-    <row r="125" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="125" spans="8:14">
       <c r="H125" s="5"/>
       <c r="J125" s="6"/>
       <c r="N125" s="4"/>
     </row>
-    <row r="126" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="126" spans="8:14">
       <c r="H126" s="5"/>
       <c r="J126" s="6"/>
       <c r="N126" s="4"/>
     </row>
-    <row r="127" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="127" spans="8:14">
       <c r="H127" s="5"/>
       <c r="J127" s="6"/>
       <c r="N127" s="4"/>
     </row>
-    <row r="128" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="128" spans="8:14">
       <c r="H128" s="5"/>
       <c r="J128" s="6"/>
       <c r="N128" s="4"/>
     </row>
-    <row r="129" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="129" spans="8:14">
       <c r="H129" s="5"/>
       <c r="J129" s="6"/>
       <c r="N129" s="4"/>
     </row>
-    <row r="130" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="130" spans="8:14">
       <c r="H130" s="5"/>
       <c r="J130" s="6"/>
       <c r="N130" s="4"/>
     </row>
-    <row r="131" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="131" spans="8:14">
       <c r="H131" s="5"/>
       <c r="J131" s="6"/>
       <c r="N131" s="4"/>
     </row>
-    <row r="132" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="132" spans="8:14">
       <c r="H132" s="5"/>
       <c r="J132" s="6"/>
       <c r="N132" s="4"/>
     </row>
-    <row r="133" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="133" spans="8:14">
       <c r="H133" s="5"/>
       <c r="J133" s="6"/>
       <c r="N133" s="4"/>
     </row>
-    <row r="134" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="134" spans="8:14">
       <c r="H134" s="5"/>
       <c r="J134" s="6"/>
       <c r="N134" s="4"/>
     </row>
-    <row r="135" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="135" spans="8:14">
       <c r="H135" s="5"/>
       <c r="J135" s="6"/>
       <c r="N135" s="4"/>
     </row>
-    <row r="136" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="136" spans="8:14">
       <c r="H136" s="5"/>
       <c r="J136" s="6"/>
       <c r="N136" s="4"/>
     </row>
-    <row r="137" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="137" spans="8:14">
       <c r="H137" s="5"/>
       <c r="J137" s="6"/>
       <c r="N137" s="4"/>
     </row>
-    <row r="138" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="138" spans="8:14">
       <c r="H138" s="5"/>
       <c r="J138" s="6"/>
       <c r="N138" s="4"/>
     </row>
-    <row r="139" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="139" spans="8:14">
       <c r="H139" s="5"/>
       <c r="J139" s="6"/>
       <c r="N139" s="4"/>
     </row>
-    <row r="140" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="140" spans="8:14">
       <c r="H140" s="5"/>
       <c r="J140" s="6"/>
       <c r="N140" s="4"/>
     </row>
-    <row r="141" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="141" spans="8:14">
       <c r="H141" s="5"/>
       <c r="J141" s="6"/>
       <c r="N141" s="4"/>
     </row>
-    <row r="142" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="142" spans="8:14">
       <c r="H142" s="5"/>
       <c r="J142" s="6"/>
       <c r="N142" s="4"/>
     </row>
-    <row r="143" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="143" spans="8:14">
       <c r="H143" s="5"/>
       <c r="J143" s="6"/>
       <c r="N143" s="4"/>
     </row>
-    <row r="144" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="144" spans="8:14">
       <c r="H144" s="5"/>
       <c r="J144" s="6"/>
       <c r="N144" s="4"/>
     </row>
-    <row r="145" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="145" spans="8:14">
       <c r="H145" s="5"/>
       <c r="J145" s="6"/>
       <c r="N145" s="4"/>
     </row>
-    <row r="146" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="146" spans="8:14">
       <c r="H146" s="5"/>
       <c r="J146" s="6"/>
       <c r="N146" s="4"/>
     </row>
-    <row r="147" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="147" spans="8:14">
       <c r="H147" s="5"/>
       <c r="J147" s="6"/>
       <c r="N147" s="4"/>
     </row>
-    <row r="148" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="148" spans="8:14">
       <c r="H148" s="5"/>
       <c r="J148" s="6"/>
       <c r="N148" s="4"/>
     </row>
-    <row r="149" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="149" spans="8:14">
       <c r="H149" s="5"/>
       <c r="J149" s="6"/>
       <c r="N149" s="4"/>
     </row>
-    <row r="150" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="150" spans="8:14">
       <c r="H150" s="5"/>
       <c r="J150" s="6"/>
       <c r="N150" s="4"/>
     </row>
-    <row r="151" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="151" spans="8:14">
       <c r="H151" s="5"/>
       <c r="J151" s="6"/>
       <c r="N151" s="4"/>
     </row>
-    <row r="152" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="152" spans="8:14">
       <c r="H152" s="5"/>
       <c r="J152" s="6"/>
       <c r="N152" s="4"/>
     </row>
-    <row r="153" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="153" spans="8:14">
       <c r="H153" s="5"/>
       <c r="J153" s="6"/>
       <c r="N153" s="4"/>
     </row>
-    <row r="154" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="154" spans="8:14">
       <c r="H154" s="5"/>
       <c r="J154" s="6"/>
       <c r="N154" s="4"/>
     </row>
-    <row r="155" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="155" spans="8:14">
       <c r="H155" s="5"/>
       <c r="J155" s="6"/>
       <c r="N155" s="4"/>
     </row>
-    <row r="156" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="156" spans="8:14">
       <c r="H156" s="5"/>
       <c r="J156" s="6"/>
       <c r="N156" s="4"/>
     </row>
-    <row r="157" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="157" spans="8:14">
       <c r="H157" s="5"/>
       <c r="J157" s="6"/>
       <c r="N157" s="4"/>
     </row>
-    <row r="158" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="158" spans="8:14">
       <c r="H158" s="5"/>
       <c r="J158" s="6"/>
       <c r="N158" s="4"/>
     </row>
-    <row r="159" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="159" spans="8:14">
       <c r="H159" s="5"/>
       <c r="J159" s="6"/>
       <c r="N159" s="4"/>
     </row>
-    <row r="160" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="160" spans="8:14">
       <c r="H160" s="5"/>
       <c r="J160" s="6"/>
       <c r="N160" s="4"/>
     </row>
-    <row r="161" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="161" spans="8:14">
       <c r="H161" s="5"/>
       <c r="J161" s="6"/>
       <c r="N161" s="4"/>
     </row>
-    <row r="162" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="162" spans="8:14">
       <c r="H162" s="5"/>
       <c r="J162" s="6"/>
       <c r="N162" s="4"/>
     </row>
-    <row r="163" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="163" spans="8:14">
       <c r="H163" s="5"/>
       <c r="J163" s="6"/>
       <c r="N163" s="4"/>
     </row>
-    <row r="164" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="164" spans="8:14">
       <c r="H164" s="5"/>
       <c r="J164" s="6"/>
       <c r="N164" s="4"/>
     </row>
-    <row r="165" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="165" spans="8:14">
       <c r="H165" s="5"/>
       <c r="J165" s="6"/>
       <c r="N165" s="4"/>
     </row>
-    <row r="166" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="166" spans="8:14">
       <c r="H166" s="5"/>
       <c r="J166" s="6"/>
       <c r="N166" s="4"/>
     </row>
-    <row r="167" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="167" spans="8:14">
       <c r="H167" s="5"/>
       <c r="J167" s="6"/>
       <c r="N167" s="4"/>
     </row>
-    <row r="168" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="168" spans="8:14">
       <c r="H168" s="5"/>
       <c r="J168" s="6"/>
       <c r="N168" s="4"/>
     </row>
-    <row r="169" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="169" spans="8:14">
       <c r="H169" s="5"/>
       <c r="J169" s="6"/>
       <c r="N169" s="4"/>
     </row>
-    <row r="170" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="170" spans="8:14">
       <c r="H170" s="5"/>
       <c r="J170" s="6"/>
       <c r="N170" s="4"/>
     </row>
-    <row r="171" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="171" spans="8:14">
       <c r="H171" s="5"/>
       <c r="J171" s="6"/>
       <c r="N171" s="4"/>
     </row>
-    <row r="172" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="172" spans="8:14">
       <c r="H172" s="5"/>
       <c r="J172" s="6"/>
       <c r="N172" s="4"/>
     </row>
-    <row r="173" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="173" spans="8:14">
       <c r="H173" s="5"/>
       <c r="J173" s="6"/>
       <c r="N173" s="4"/>
     </row>
-    <row r="174" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="174" spans="8:14">
       <c r="H174" s="5"/>
       <c r="J174" s="6"/>
       <c r="N174" s="4"/>
     </row>
-    <row r="175" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="175" spans="8:14">
       <c r="H175" s="5"/>
       <c r="J175" s="6"/>
       <c r="N175" s="4"/>
     </row>
-    <row r="176" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="176" spans="8:14">
       <c r="H176" s="5"/>
       <c r="J176" s="6"/>
       <c r="N176" s="4"/>
     </row>
-    <row r="177" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="177" spans="8:14">
       <c r="H177" s="5"/>
       <c r="J177" s="6"/>
       <c r="N177" s="4"/>
     </row>
-    <row r="178" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="178" spans="8:14">
       <c r="H178" s="5"/>
       <c r="J178" s="6"/>
       <c r="N178" s="4"/>
     </row>
-    <row r="179" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="179" spans="8:14">
       <c r="H179" s="5"/>
       <c r="J179" s="6"/>
       <c r="N179" s="4"/>
     </row>
-    <row r="180" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="180" spans="8:14">
       <c r="H180" s="5"/>
       <c r="J180" s="6"/>
       <c r="N180" s="4"/>
     </row>
-    <row r="181" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="181" spans="8:14">
       <c r="H181" s="5"/>
       <c r="J181" s="6"/>
       <c r="N181" s="4"/>
     </row>
-    <row r="182" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="182" spans="8:14">
       <c r="H182" s="5"/>
       <c r="J182" s="6"/>
       <c r="N182" s="4"/>
     </row>
-    <row r="183" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="183" spans="8:14">
       <c r="H183" s="5"/>
       <c r="J183" s="6"/>
       <c r="N183" s="4"/>
     </row>
-    <row r="184" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="184" spans="8:14">
       <c r="H184" s="5"/>
       <c r="J184" s="6"/>
       <c r="N184" s="4"/>
     </row>
-    <row r="185" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="185" spans="8:14">
       <c r="H185" s="5"/>
       <c r="J185" s="6"/>
       <c r="N185" s="4"/>
     </row>
-    <row r="186" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="186" spans="8:14">
       <c r="H186" s="5"/>
       <c r="J186" s="6"/>
       <c r="N186" s="4"/>
     </row>
-    <row r="187" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="187" spans="8:14">
       <c r="H187" s="5"/>
       <c r="J187" s="6"/>
       <c r="N187" s="4"/>
     </row>
-    <row r="188" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="188" spans="8:14">
       <c r="H188" s="5"/>
       <c r="J188" s="6"/>
       <c r="N188" s="4"/>
     </row>
-    <row r="189" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="189" spans="8:14">
       <c r="H189" s="5"/>
       <c r="J189" s="6"/>
       <c r="N189" s="4"/>
     </row>
-    <row r="190" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="190" spans="8:14">
       <c r="H190" s="5"/>
       <c r="J190" s="6"/>
       <c r="N190" s="4"/>
     </row>
-    <row r="191" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="191" spans="8:14">
       <c r="H191" s="5"/>
       <c r="J191" s="6"/>
       <c r="N191" s="4"/>
     </row>
-    <row r="192" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="192" spans="8:14">
       <c r="H192" s="5"/>
       <c r="J192" s="6"/>
       <c r="N192" s="4"/>
     </row>
-    <row r="193" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="193" spans="8:14">
       <c r="H193" s="5"/>
       <c r="J193" s="6"/>
       <c r="N193" s="4"/>
     </row>
-    <row r="194" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="194" spans="8:14">
       <c r="H194" s="5"/>
       <c r="J194" s="6"/>
       <c r="N194" s="4"/>
     </row>
-    <row r="195" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="195" spans="8:14">
       <c r="H195" s="5"/>
       <c r="J195" s="6"/>
       <c r="N195" s="4"/>
     </row>
-    <row r="196" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="196" spans="8:14">
       <c r="H196" s="5"/>
       <c r="J196" s="6"/>
       <c r="N196" s="4"/>
     </row>
-    <row r="197" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="197" spans="8:14">
       <c r="H197" s="5"/>
       <c r="J197" s="6"/>
       <c r="N197" s="4"/>
     </row>
-    <row r="198" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="198" spans="8:14">
       <c r="H198" s="5"/>
       <c r="J198" s="6"/>
       <c r="N198" s="4"/>
     </row>
-    <row r="199" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="199" spans="8:14">
       <c r="H199" s="5"/>
       <c r="J199" s="6"/>
       <c r="N199" s="4"/>
     </row>
-    <row r="200" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="200" spans="8:14">
       <c r="H200" s="5"/>
       <c r="J200" s="6"/>
       <c r="N200" s="4"/>
     </row>
-    <row r="201" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="201" spans="8:14">
       <c r="H201" s="5"/>
       <c r="J201" s="6"/>
       <c r="N201" s="4"/>
     </row>
-    <row r="202" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="202" spans="8:14">
       <c r="H202" s="5"/>
       <c r="J202" s="6"/>
       <c r="N202" s="4"/>
     </row>
-    <row r="203" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="203" spans="8:14">
       <c r="H203" s="5"/>
       <c r="J203" s="6"/>
       <c r="N203" s="4"/>
     </row>
-    <row r="204" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="204" spans="8:14">
       <c r="H204" s="5"/>
       <c r="J204" s="6"/>
       <c r="N204" s="4"/>
     </row>
-    <row r="205" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="205" spans="8:14">
       <c r="H205" s="5"/>
       <c r="J205" s="6"/>
       <c r="N205" s="4"/>
     </row>
-    <row r="206" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="206" spans="8:14">
       <c r="H206" s="5"/>
       <c r="J206" s="6"/>
       <c r="N206" s="4"/>
     </row>
-    <row r="207" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="207" spans="8:14">
       <c r="H207" s="5"/>
       <c r="J207" s="6"/>
       <c r="N207" s="4"/>
     </row>
-    <row r="208" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="208" spans="8:14">
       <c r="H208" s="5"/>
       <c r="J208" s="6"/>
       <c r="N208" s="4"/>
     </row>
-    <row r="209" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="209" spans="8:14">
       <c r="H209" s="5"/>
       <c r="J209" s="6"/>
       <c r="N209" s="4"/>
     </row>
-    <row r="210" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="210" spans="8:14">
       <c r="H210" s="5"/>
       <c r="J210" s="6"/>
       <c r="N210" s="4"/>
     </row>
-    <row r="211" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="211" spans="8:14">
       <c r="H211" s="5"/>
       <c r="J211" s="6"/>
       <c r="N211" s="4"/>
     </row>
-    <row r="212" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="212" spans="8:14">
       <c r="H212" s="5"/>
       <c r="J212" s="6"/>
       <c r="N212" s="4"/>
     </row>
-    <row r="213" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="213" spans="8:14">
       <c r="H213" s="5"/>
       <c r="J213" s="6"/>
       <c r="N213" s="4"/>
     </row>
-    <row r="214" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="214" spans="8:14">
       <c r="H214" s="5"/>
       <c r="J214" s="6"/>
       <c r="N214" s="4"/>
     </row>
-    <row r="215" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="215" spans="8:14">
       <c r="H215" s="5"/>
       <c r="J215" s="6"/>
       <c r="N215" s="4"/>
     </row>
-    <row r="216" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="216" spans="8:14">
       <c r="H216" s="5"/>
       <c r="J216" s="6"/>
       <c r="N216" s="4"/>
     </row>
-    <row r="217" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="217" spans="8:14">
       <c r="H217" s="5"/>
       <c r="J217" s="6"/>
       <c r="N217" s="4"/>
     </row>
-    <row r="218" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="218" spans="8:14">
       <c r="H218" s="5"/>
       <c r="J218" s="6"/>
       <c r="N218" s="4"/>
     </row>
-    <row r="219" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="219" spans="8:14">
       <c r="H219" s="5"/>
       <c r="J219" s="6"/>
       <c r="N219" s="4"/>
     </row>
-    <row r="220" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="220" spans="8:14">
       <c r="H220" s="5"/>
       <c r="J220" s="6"/>
       <c r="N220" s="4"/>
     </row>
-    <row r="221" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="221" spans="8:14">
       <c r="H221" s="5"/>
       <c r="J221" s="6"/>
       <c r="N221" s="4"/>
     </row>
-    <row r="222" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="222" spans="8:14">
       <c r="H222" s="5"/>
       <c r="J222" s="6"/>
       <c r="N222" s="4"/>
     </row>
-    <row r="223" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="223" spans="8:14">
       <c r="H223" s="5"/>
       <c r="J223" s="6"/>
       <c r="N223" s="4"/>
     </row>
-    <row r="224" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="224" spans="8:14">
       <c r="H224" s="5"/>
       <c r="J224" s="6"/>
       <c r="N224" s="4"/>
     </row>
-    <row r="225" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="225" spans="8:14">
       <c r="H225" s="5"/>
       <c r="J225" s="6"/>
       <c r="N225" s="4"/>
     </row>
-    <row r="226" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="226" spans="8:14">
       <c r="H226" s="5"/>
       <c r="J226" s="6"/>
       <c r="N226" s="4"/>
     </row>
-    <row r="227" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="227" spans="8:14">
       <c r="H227" s="5"/>
       <c r="J227" s="6"/>
       <c r="N227" s="4"/>
     </row>
-    <row r="228" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="228" spans="8:14">
       <c r="H228" s="5"/>
       <c r="J228" s="6"/>
       <c r="N228" s="4"/>
     </row>
-    <row r="229" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="229" spans="8:14">
       <c r="H229" s="5"/>
       <c r="J229" s="6"/>
       <c r="N229" s="4"/>
     </row>
-    <row r="230" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="230" spans="8:14">
       <c r="H230" s="5"/>
       <c r="J230" s="6"/>
       <c r="N230" s="4"/>
     </row>
-    <row r="231" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="231" spans="8:14">
       <c r="H231" s="5"/>
       <c r="J231" s="6"/>
       <c r="N231" s="4"/>
     </row>
-    <row r="232" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="232" spans="8:14">
       <c r="H232" s="5"/>
       <c r="J232" s="6"/>
       <c r="N232" s="4"/>
     </row>
-    <row r="233" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="233" spans="8:14">
       <c r="H233" s="5"/>
       <c r="J233" s="6"/>
       <c r="N233" s="4"/>
     </row>
-    <row r="234" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="234" spans="8:14">
       <c r="H234" s="5"/>
       <c r="J234" s="6"/>
       <c r="N234" s="4"/>
     </row>
-    <row r="235" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="235" spans="8:14">
       <c r="H235" s="5"/>
       <c r="J235" s="6"/>
       <c r="N235" s="4"/>
     </row>
-    <row r="236" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="236" spans="8:14">
       <c r="H236" s="5"/>
       <c r="J236" s="6"/>
       <c r="N236" s="4"/>
     </row>
-    <row r="237" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="237" spans="8:14">
       <c r="H237" s="5"/>
       <c r="J237" s="6"/>
       <c r="N237" s="4"/>
     </row>
-    <row r="238" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="238" spans="8:14">
       <c r="H238" s="5"/>
       <c r="J238" s="6"/>
       <c r="N238" s="4"/>
     </row>
-    <row r="239" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="239" spans="8:14">
       <c r="H239" s="5"/>
       <c r="J239" s="6"/>
       <c r="N239" s="4"/>
     </row>
-    <row r="240" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="240" spans="8:14">
       <c r="H240" s="5"/>
       <c r="J240" s="6"/>
       <c r="N240" s="4"/>
     </row>
-    <row r="241" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="241" spans="8:14">
       <c r="H241" s="5"/>
       <c r="J241" s="6"/>
       <c r="N241" s="4"/>
     </row>
-    <row r="242" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="242" spans="8:14">
       <c r="H242" s="5"/>
       <c r="J242" s="6"/>
       <c r="N242" s="4"/>
     </row>
-    <row r="243" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="243" spans="8:14">
       <c r="H243" s="5"/>
       <c r="J243" s="6"/>
       <c r="N243" s="4"/>
     </row>
-    <row r="244" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="244" spans="8:14">
       <c r="H244" s="5"/>
       <c r="J244" s="6"/>
       <c r="N244" s="4"/>
     </row>
-    <row r="245" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="245" spans="8:14">
       <c r="H245" s="5"/>
       <c r="J245" s="6"/>
       <c r="N245" s="4"/>
     </row>
-    <row r="246" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="246" spans="8:14">
       <c r="H246" s="5"/>
       <c r="J246" s="6"/>
       <c r="N246" s="4"/>
     </row>
-    <row r="247" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="247" spans="8:14">
       <c r="H247" s="5"/>
       <c r="J247" s="6"/>
       <c r="N247" s="4"/>
     </row>
-    <row r="248" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="248" spans="8:14">
       <c r="H248" s="5"/>
       <c r="J248" s="6"/>
       <c r="N248" s="4"/>
     </row>
-    <row r="249" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="249" spans="8:14">
       <c r="H249" s="5"/>
       <c r="J249" s="6"/>
       <c r="N249" s="4"/>
     </row>
-    <row r="250" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="250" spans="8:14">
       <c r="H250" s="5"/>
       <c r="J250" s="6"/>
       <c r="N250" s="4"/>
     </row>
-    <row r="251" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="251" spans="8:14">
       <c r="H251" s="5"/>
       <c r="J251" s="6"/>
       <c r="N251" s="4"/>
     </row>
-    <row r="252" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="252" spans="8:14">
       <c r="H252" s="5"/>
       <c r="J252" s="6"/>
       <c r="N252" s="4"/>
     </row>
-    <row r="253" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="253" spans="8:14">
       <c r="H253" s="5"/>
       <c r="J253" s="6"/>
       <c r="N253" s="4"/>
     </row>
-    <row r="254" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="254" spans="8:14">
       <c r="H254" s="5"/>
       <c r="J254" s="6"/>
       <c r="N254" s="4"/>
     </row>
-    <row r="255" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="255" spans="8:14">
       <c r="H255" s="5"/>
       <c r="J255" s="6"/>
       <c r="N255" s="4"/>
     </row>
-    <row r="256" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="256" spans="8:14">
       <c r="H256" s="5"/>
       <c r="J256" s="6"/>
       <c r="N256" s="4"/>
     </row>
-    <row r="257" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="257" spans="8:14">
       <c r="H257" s="5"/>
       <c r="J257" s="6"/>
       <c r="N257" s="4"/>
     </row>
-    <row r="258" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="258" spans="8:14">
       <c r="H258" s="5"/>
       <c r="J258" s="6"/>
       <c r="N258" s="4"/>
     </row>
-    <row r="259" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="259" spans="8:14">
       <c r="H259" s="5"/>
       <c r="J259" s="6"/>
       <c r="N259" s="4"/>
     </row>
-    <row r="260" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="260" spans="8:14">
       <c r="H260" s="5"/>
       <c r="J260" s="6"/>
       <c r="N260" s="4"/>
     </row>
-    <row r="261" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="261" spans="8:14">
       <c r="H261" s="5"/>
       <c r="J261" s="6"/>
       <c r="N261" s="4"/>
     </row>
-    <row r="262" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="262" spans="8:14">
       <c r="H262" s="5"/>
       <c r="J262" s="6"/>
       <c r="N262" s="4"/>
     </row>
-    <row r="263" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="263" spans="8:14">
       <c r="H263" s="5"/>
       <c r="J263" s="6"/>
       <c r="N263" s="4"/>
     </row>
-    <row r="264" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="264" spans="8:14">
       <c r="H264" s="5"/>
       <c r="J264" s="6"/>
       <c r="N264" s="4"/>
     </row>
-    <row r="265" spans="8:14" x14ac:dyDescent="0.35">
+    <row r="265" spans="8:14">
       <c r="H265" s="5"/>
       <c r="J265" s="6"/>
       <c r="N265" s="4"/>
@@ -4413,31 +4551,31 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE182796-6443-4558-9B87-909B73329DFC}">
   <dimension ref="A1:O267"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="1.7265625" customWidth="1"/>
-    <col min="2" max="2" width="3.7265625" customWidth="1"/>
-    <col min="3" max="3" width="12.54296875" customWidth="1"/>
-    <col min="4" max="4" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.81640625" customWidth="1"/>
-    <col min="10" max="10" width="11.81640625" customWidth="1"/>
-    <col min="12" max="12" width="16.453125" customWidth="1"/>
-    <col min="13" max="13" width="23.81640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.7265625" customWidth="1"/>
+    <col min="1" max="1" width="1.7109375" customWidth="1"/>
+    <col min="2" max="2" width="3.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" customWidth="1"/>
+    <col min="12" max="12" width="16.42578125" customWidth="1"/>
+    <col min="13" max="13" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="2" customFormat="1" ht="52.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" s="2" customFormat="1" ht="52.5" customHeight="1">
       <c r="A1" s="1"/>
       <c r="C1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15">
       <c r="C7" t="s">
         <v>29</v>
       </c>
@@ -4478,7 +4616,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15">
       <c r="C8" t="s">
         <v>42</v>
       </c>
@@ -4519,7 +4657,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15">
       <c r="C9" t="s">
         <v>51</v>
       </c>
@@ -4560,7 +4698,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15">
       <c r="C10" t="s">
         <v>57</v>
       </c>
@@ -4601,7 +4739,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15">
       <c r="C11" t="s">
         <v>57</v>
       </c>
@@ -4642,7 +4780,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15">
       <c r="C12" t="s">
         <v>61</v>
       </c>
@@ -4683,7 +4821,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15">
       <c r="C13" t="s">
         <v>68</v>
       </c>
@@ -4724,7 +4862,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15">
       <c r="C14" t="s">
         <v>72</v>
       </c>
@@ -4765,7 +4903,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15">
       <c r="C15" t="s">
         <v>75</v>
       </c>
@@ -4806,7 +4944,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15">
       <c r="C16" t="s">
         <v>79</v>
       </c>
@@ -4847,7 +4985,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:15">
       <c r="C17" t="s">
         <v>83</v>
       </c>
@@ -4888,7 +5026,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="3:15">
       <c r="C18" t="s">
         <v>87</v>
       </c>
@@ -4929,7 +5067,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:15">
       <c r="C19" t="s">
         <v>90</v>
       </c>
@@ -4970,7 +5108,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="3:15">
       <c r="C20" t="s">
         <v>94</v>
       </c>
@@ -5011,7 +5149,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:15">
       <c r="C21" t="s">
         <v>98</v>
       </c>
@@ -5052,7 +5190,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="3:15">
       <c r="C22" t="s">
         <v>102</v>
       </c>
@@ -5093,7 +5231,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="3:15">
       <c r="C23" t="s">
         <v>106</v>
       </c>
@@ -5134,7 +5272,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="3:15">
       <c r="C24" t="s">
         <v>110</v>
       </c>
@@ -5175,7 +5313,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="3:15">
       <c r="C25" t="s">
         <v>113</v>
       </c>
@@ -5216,7 +5354,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="3:15">
       <c r="C26" t="s">
         <v>117</v>
       </c>
@@ -5257,7 +5395,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="3:15">
       <c r="C27" t="s">
         <v>120</v>
       </c>
@@ -5298,7 +5436,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="3:15">
       <c r="C28" t="s">
         <v>124</v>
       </c>
@@ -5339,7 +5477,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="3:15">
       <c r="C29" t="s">
         <v>127</v>
       </c>
@@ -5380,7 +5518,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="3:15">
       <c r="C30" t="s">
         <v>130</v>
       </c>
@@ -5421,7 +5559,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="3:15">
       <c r="C31" t="s">
         <v>133</v>
       </c>
@@ -5462,7 +5600,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="3:15">
       <c r="C32" t="s">
         <v>133</v>
       </c>
@@ -5503,7 +5641,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="33" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:15">
       <c r="C33" t="s">
         <v>136</v>
       </c>
@@ -5544,7 +5682,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="34" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="34" spans="3:15">
       <c r="C34" t="s">
         <v>139</v>
       </c>
@@ -5585,7 +5723,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="35" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="35" spans="3:15">
       <c r="C35" t="s">
         <v>142</v>
       </c>
@@ -5626,7 +5764,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="36" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="36" spans="3:15">
       <c r="C36" t="s">
         <v>146</v>
       </c>
@@ -5667,7 +5805,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="37" spans="3:15">
       <c r="C37" t="s">
         <v>149</v>
       </c>
@@ -5708,7 +5846,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="38" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="38" spans="3:15">
       <c r="C38" t="s">
         <v>152</v>
       </c>
@@ -5749,7 +5887,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="39" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="39" spans="3:15">
       <c r="C39" t="s">
         <v>156</v>
       </c>
@@ -5790,7 +5928,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="40" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="40" spans="3:15">
       <c r="C40" t="s">
         <v>159</v>
       </c>
@@ -5831,7 +5969,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="41" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="41" spans="3:15">
       <c r="C41" t="s">
         <v>162</v>
       </c>
@@ -5872,7 +6010,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="42" spans="3:15">
       <c r="C42" t="s">
         <v>165</v>
       </c>
@@ -5913,7 +6051,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="43" spans="3:15">
       <c r="C43" t="s">
         <v>168</v>
       </c>
@@ -5954,7 +6092,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="44" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="44" spans="3:15">
       <c r="C44" t="s">
         <v>171</v>
       </c>
@@ -5995,7 +6133,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="45" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="45" spans="3:15">
       <c r="C45" t="s">
         <v>174</v>
       </c>
@@ -6036,7 +6174,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="46" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="46" spans="3:15">
       <c r="C46" t="s">
         <v>177</v>
       </c>
@@ -6077,7 +6215,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="47" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="47" spans="3:15">
       <c r="C47" t="s">
         <v>180</v>
       </c>
@@ -6118,7 +6256,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="48" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="48" spans="3:15">
       <c r="C48" t="s">
         <v>183</v>
       </c>
@@ -6159,7 +6297,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="49" spans="3:15">
       <c r="C49" t="s">
         <v>186</v>
       </c>
@@ -6200,7 +6338,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="50" spans="3:15">
       <c r="C50" t="s">
         <v>189</v>
       </c>
@@ -6241,7 +6379,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="51" spans="3:15">
       <c r="C51" t="s">
         <v>192</v>
       </c>
@@ -6282,7 +6420,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="52" spans="3:15">
       <c r="C52" t="s">
         <v>192</v>
       </c>
@@ -6323,7 +6461,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="53" spans="3:15">
       <c r="C53" t="s">
         <v>197</v>
       </c>
@@ -6364,7 +6502,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="54" spans="3:15">
       <c r="C54" t="s">
         <v>200</v>
       </c>
@@ -6405,7 +6543,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="55" spans="3:15">
       <c r="C55" t="s">
         <v>203</v>
       </c>
@@ -6446,7 +6584,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="56" spans="3:15">
       <c r="C56" t="s">
         <v>206</v>
       </c>
@@ -6487,7 +6625,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="57" spans="3:15">
       <c r="C57" t="s">
         <v>209</v>
       </c>
@@ -6528,7 +6666,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="58" spans="3:15">
       <c r="C58" t="s">
         <v>210</v>
       </c>
@@ -6569,7 +6707,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="59" spans="3:15">
       <c r="C59" t="s">
         <v>213</v>
       </c>
@@ -6610,7 +6748,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="60" spans="3:15">
       <c r="C60" t="s">
         <v>216</v>
       </c>
@@ -6651,7 +6789,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="61" spans="3:15">
       <c r="C61" t="s">
         <v>220</v>
       </c>
@@ -6692,7 +6830,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="62" spans="3:15">
       <c r="C62" t="s">
         <v>223</v>
       </c>
@@ -6733,7 +6871,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="63" spans="3:15">
       <c r="C63" t="s">
         <v>226</v>
       </c>
@@ -6774,7 +6912,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="64" spans="3:15">
       <c r="C64" t="s">
         <v>229</v>
       </c>
@@ -6815,7 +6953,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="65" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="65" spans="3:15">
       <c r="C65" t="s">
         <v>232</v>
       </c>
@@ -6856,7 +6994,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="66" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="66" spans="3:15">
       <c r="C66" t="s">
         <v>235</v>
       </c>
@@ -6897,7 +7035,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="67" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="67" spans="3:15">
       <c r="C67" t="s">
         <v>238</v>
       </c>
@@ -6938,7 +7076,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="68" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="68" spans="3:15">
       <c r="C68" t="s">
         <v>241</v>
       </c>
@@ -6979,7 +7117,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="69" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="69" spans="3:15">
       <c r="C69" t="s">
         <v>244</v>
       </c>
@@ -7020,7 +7158,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="70" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="70" spans="3:15">
       <c r="C70" t="s">
         <v>247</v>
       </c>
@@ -7061,7 +7199,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="71" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="71" spans="3:15">
       <c r="C71" t="s">
         <v>248</v>
       </c>
@@ -7102,7 +7240,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="72" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="72" spans="3:15">
       <c r="C72" t="s">
         <v>251</v>
       </c>
@@ -7143,7 +7281,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="73" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="73" spans="3:15">
       <c r="C73" t="s">
         <v>254</v>
       </c>
@@ -7184,7 +7322,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="74" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="74" spans="3:15">
       <c r="C74" t="s">
         <v>257</v>
       </c>
@@ -7225,7 +7363,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="75" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="75" spans="3:15">
       <c r="C75" t="s">
         <v>260</v>
       </c>
@@ -7266,7 +7404,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="76" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="76" spans="3:15">
       <c r="C76" t="s">
         <v>260</v>
       </c>
@@ -7307,7 +7445,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="77" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="77" spans="3:15">
       <c r="C77" t="s">
         <v>265</v>
       </c>
@@ -7348,7 +7486,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="78" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="78" spans="3:15">
       <c r="C78" t="s">
         <v>268</v>
       </c>
@@ -7389,7 +7527,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="79" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="79" spans="3:15">
       <c r="C79" t="s">
         <v>271</v>
       </c>
@@ -7430,7 +7568,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="80" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="80" spans="3:15">
       <c r="C80" t="s">
         <v>274</v>
       </c>
@@ -7471,7 +7609,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="81" spans="3:15">
       <c r="C81" t="s">
         <v>277</v>
       </c>
@@ -7512,7 +7650,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="82" spans="3:15">
       <c r="C82" t="s">
         <v>280</v>
       </c>
@@ -7553,7 +7691,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="83" spans="3:15">
       <c r="C83" t="s">
         <v>283</v>
       </c>
@@ -7594,7 +7732,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="84" spans="3:15">
       <c r="C84" t="s">
         <v>286</v>
       </c>
@@ -7635,7 +7773,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="85" spans="3:15">
       <c r="C85" t="s">
         <v>289</v>
       </c>
@@ -7676,7 +7814,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="86" spans="3:15">
       <c r="C86" t="s">
         <v>292</v>
       </c>
@@ -7717,7 +7855,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="87" spans="3:15">
       <c r="C87" t="s">
         <v>295</v>
       </c>
@@ -7758,7 +7896,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="88" spans="3:15">
       <c r="C88" t="s">
         <v>298</v>
       </c>
@@ -7799,7 +7937,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="89" spans="3:15">
       <c r="C89" t="s">
         <v>301</v>
       </c>
@@ -7840,7 +7978,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="90" spans="3:15">
       <c r="C90" t="s">
         <v>304</v>
       </c>
@@ -7881,7 +8019,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="91" spans="3:15">
       <c r="C91" t="s">
         <v>304</v>
       </c>
@@ -7922,7 +8060,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="92" spans="3:15">
       <c r="C92" t="s">
         <v>309</v>
       </c>
@@ -7963,7 +8101,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="93" spans="3:15">
       <c r="C93" t="s">
         <v>309</v>
       </c>
@@ -8004,7 +8142,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="94" spans="3:15">
       <c r="C94" t="s">
         <v>312</v>
       </c>
@@ -8045,7 +8183,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="95" spans="3:15">
       <c r="C95" t="s">
         <v>315</v>
       </c>
@@ -8086,7 +8224,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="96" spans="3:15">
       <c r="C96" t="s">
         <v>318</v>
       </c>
@@ -8127,7 +8265,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="97" spans="3:15">
       <c r="C97" t="s">
         <v>321</v>
       </c>
@@ -8168,7 +8306,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="98" spans="3:15">
       <c r="C98" t="s">
         <v>324</v>
       </c>
@@ -8209,7 +8347,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="99" spans="3:15">
       <c r="C99" t="s">
         <v>327</v>
       </c>
@@ -8250,7 +8388,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="100" spans="3:15">
       <c r="C100" t="s">
         <v>330</v>
       </c>
@@ -8291,7 +8429,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="101" spans="3:15">
       <c r="C101" t="s">
         <v>333</v>
       </c>
@@ -8332,7 +8470,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="102" spans="3:15">
       <c r="C102" t="s">
         <v>333</v>
       </c>
@@ -8373,7 +8511,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="103" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="103" spans="3:15">
       <c r="C103" t="s">
         <v>336</v>
       </c>
@@ -8414,7 +8552,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="104" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="104" spans="3:15">
       <c r="C104" t="s">
         <v>339</v>
       </c>
@@ -8455,7 +8593,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="105" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="105" spans="3:15">
       <c r="C105" t="s">
         <v>342</v>
       </c>
@@ -8496,7 +8634,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="106" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="106" spans="3:15">
       <c r="C106" t="s">
         <v>345</v>
       </c>
@@ -8537,7 +8675,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="107" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="107" spans="3:15">
       <c r="C107" t="s">
         <v>348</v>
       </c>
@@ -8578,7 +8716,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="108" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="108" spans="3:15">
       <c r="C108" t="s">
         <v>351</v>
       </c>
@@ -8619,7 +8757,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="109" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="109" spans="3:15">
       <c r="C109" t="s">
         <v>354</v>
       </c>
@@ -8660,7 +8798,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="110" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="110" spans="3:15">
       <c r="C110" t="s">
         <v>354</v>
       </c>
@@ -8701,7 +8839,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="111" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="111" spans="3:15">
       <c r="C111" t="s">
         <v>357</v>
       </c>
@@ -8742,7 +8880,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="112" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="112" spans="3:15">
       <c r="C112" t="s">
         <v>360</v>
       </c>
@@ -8783,7 +8921,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="113" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="113" spans="3:15">
       <c r="C113" t="s">
         <v>363</v>
       </c>
@@ -8824,7 +8962,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="114" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="114" spans="3:15">
       <c r="C114" t="s">
         <v>366</v>
       </c>
@@ -8865,7 +9003,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="115" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="115" spans="3:15">
       <c r="C115" t="s">
         <v>366</v>
       </c>
@@ -8906,7 +9044,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="116" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="116" spans="3:15">
       <c r="C116" t="s">
         <v>369</v>
       </c>
@@ -8947,7 +9085,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="117" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="117" spans="3:15">
       <c r="C117" t="s">
         <v>372</v>
       </c>
@@ -8988,7 +9126,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="118" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="118" spans="3:15">
       <c r="C118" t="s">
         <v>375</v>
       </c>
@@ -9029,7 +9167,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="119" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="119" spans="3:15">
       <c r="C119" t="s">
         <v>378</v>
       </c>
@@ -9070,7 +9208,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="120" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="120" spans="3:15">
       <c r="C120" t="s">
         <v>381</v>
       </c>
@@ -9111,7 +9249,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="121" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="121" spans="3:15">
       <c r="C121" t="s">
         <v>384</v>
       </c>
@@ -9152,7 +9290,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="122" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="122" spans="3:15">
       <c r="C122" t="s">
         <v>387</v>
       </c>
@@ -9193,7 +9331,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="123" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="123" spans="3:15">
       <c r="C123" t="s">
         <v>390</v>
       </c>
@@ -9234,7 +9372,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="124" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="124" spans="3:15">
       <c r="C124" t="s">
         <v>393</v>
       </c>
@@ -9275,7 +9413,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="125" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="125" spans="3:15">
       <c r="C125" t="s">
         <v>396</v>
       </c>
@@ -9316,7 +9454,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="126" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="126" spans="3:15">
       <c r="C126" t="s">
         <v>399</v>
       </c>
@@ -9357,7 +9495,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="127" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="127" spans="3:15">
       <c r="C127" t="s">
         <v>402</v>
       </c>
@@ -9398,7 +9536,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="128" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="128" spans="3:15">
       <c r="C128" t="s">
         <v>405</v>
       </c>
@@ -9439,7 +9577,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="129" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="129" spans="3:15">
       <c r="C129" t="s">
         <v>408</v>
       </c>
@@ -9480,7 +9618,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="130" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="130" spans="3:15">
       <c r="C130" t="s">
         <v>411</v>
       </c>
@@ -9521,7 +9659,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="131" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="131" spans="3:15">
       <c r="C131" t="s">
         <v>414</v>
       </c>
@@ -9562,7 +9700,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="132" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="132" spans="3:15">
       <c r="C132" t="s">
         <v>417</v>
       </c>
@@ -9603,7 +9741,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="133" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="133" spans="3:15">
       <c r="C133" t="s">
         <v>420</v>
       </c>
@@ -9644,7 +9782,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="134" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="134" spans="3:15">
       <c r="C134" t="s">
         <v>420</v>
       </c>
@@ -9685,7 +9823,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="135" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="135" spans="3:15">
       <c r="C135" t="s">
         <v>425</v>
       </c>
@@ -9726,7 +9864,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="136" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="136" spans="3:15">
       <c r="C136" t="s">
         <v>428</v>
       </c>
@@ -9767,7 +9905,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="137" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="137" spans="3:15">
       <c r="C137" t="s">
         <v>431</v>
       </c>
@@ -9808,7 +9946,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="138" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="138" spans="3:15">
       <c r="C138" t="s">
         <v>434</v>
       </c>
@@ -9849,7 +9987,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="139" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="139" spans="3:15">
       <c r="C139" t="s">
         <v>437</v>
       </c>
@@ -9890,7 +10028,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="140" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="140" spans="3:15">
       <c r="C140" t="s">
         <v>440</v>
       </c>
@@ -9931,7 +10069,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="141" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="141" spans="3:15">
       <c r="C141" t="s">
         <v>443</v>
       </c>
@@ -9972,7 +10110,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="142" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="142" spans="3:15">
       <c r="C142" t="s">
         <v>446</v>
       </c>
@@ -10013,7 +10151,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="143" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="143" spans="3:15">
       <c r="C143" t="s">
         <v>446</v>
       </c>
@@ -10054,7 +10192,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="144" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="144" spans="3:15">
       <c r="C144" t="s">
         <v>449</v>
       </c>
@@ -10095,7 +10233,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="145" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="145" spans="3:15">
       <c r="C145" t="s">
         <v>452</v>
       </c>
@@ -10136,7 +10274,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="146" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="146" spans="3:15">
       <c r="C146" t="s">
         <v>455</v>
       </c>
@@ -10177,7 +10315,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="147" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="147" spans="3:15">
       <c r="C147" t="s">
         <v>458</v>
       </c>
@@ -10218,7 +10356,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="148" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="148" spans="3:15">
       <c r="C148" t="s">
         <v>458</v>
       </c>
@@ -10259,7 +10397,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="149" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="149" spans="3:15">
       <c r="C149" t="s">
         <v>463</v>
       </c>
@@ -10300,7 +10438,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="150" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="150" spans="3:15">
       <c r="C150" t="s">
         <v>466</v>
       </c>
@@ -10341,7 +10479,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="151" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="151" spans="3:15">
       <c r="C151" t="s">
         <v>469</v>
       </c>
@@ -10382,7 +10520,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="152" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="152" spans="3:15">
       <c r="C152" t="s">
         <v>472</v>
       </c>
@@ -10423,7 +10561,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="153" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="153" spans="3:15">
       <c r="C153" t="s">
         <v>475</v>
       </c>
@@ -10464,7 +10602,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="154" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="154" spans="3:15">
       <c r="C154" t="s">
         <v>475</v>
       </c>
@@ -10505,7 +10643,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="155" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="155" spans="3:15">
       <c r="C155" t="s">
         <v>478</v>
       </c>
@@ -10546,7 +10684,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="156" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="156" spans="3:15">
       <c r="C156" t="s">
         <v>481</v>
       </c>
@@ -10587,7 +10725,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="157" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="157" spans="3:15">
       <c r="C157" t="s">
         <v>484</v>
       </c>
@@ -10628,7 +10766,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="158" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="158" spans="3:15">
       <c r="C158" t="s">
         <v>484</v>
       </c>
@@ -10669,7 +10807,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="159" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="159" spans="3:15">
       <c r="C159" t="s">
         <v>487</v>
       </c>
@@ -10710,7 +10848,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="160" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="160" spans="3:15">
       <c r="C160" t="s">
         <v>490</v>
       </c>
@@ -10751,7 +10889,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="161" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="161" spans="3:15">
       <c r="C161" t="s">
         <v>491</v>
       </c>
@@ -10792,7 +10930,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="162" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="162" spans="3:15">
       <c r="C162" t="s">
         <v>494</v>
       </c>
@@ -10833,7 +10971,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="163" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="163" spans="3:15">
       <c r="C163" t="s">
         <v>497</v>
       </c>
@@ -10874,7 +11012,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="164" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="164" spans="3:15">
       <c r="C164" t="s">
         <v>500</v>
       </c>
@@ -10915,7 +11053,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="165" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="165" spans="3:15">
       <c r="C165" t="s">
         <v>503</v>
       </c>
@@ -10956,7 +11094,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="166" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="166" spans="3:15">
       <c r="C166" t="s">
         <v>503</v>
       </c>
@@ -10997,7 +11135,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="167" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="167" spans="3:15">
       <c r="C167" t="s">
         <v>506</v>
       </c>
@@ -11038,7 +11176,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="168" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="168" spans="3:15">
       <c r="C168" t="s">
         <v>506</v>
       </c>
@@ -11079,7 +11217,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="169" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="169" spans="3:15">
       <c r="C169" t="s">
         <v>509</v>
       </c>
@@ -11120,7 +11258,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="170" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="170" spans="3:15">
       <c r="C170" t="s">
         <v>512</v>
       </c>
@@ -11161,7 +11299,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="171" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="171" spans="3:15">
       <c r="C171" t="s">
         <v>515</v>
       </c>
@@ -11202,7 +11340,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="172" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="172" spans="3:15">
       <c r="C172" t="s">
         <v>518</v>
       </c>
@@ -11243,7 +11381,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="173" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="173" spans="3:15">
       <c r="C173" t="s">
         <v>521</v>
       </c>
@@ -11284,7 +11422,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="174" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="174" spans="3:15">
       <c r="C174" t="s">
         <v>524</v>
       </c>
@@ -11325,7 +11463,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="175" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="175" spans="3:15">
       <c r="C175" t="s">
         <v>524</v>
       </c>
@@ -11366,7 +11504,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="176" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="176" spans="3:15">
       <c r="C176" t="s">
         <v>528</v>
       </c>
@@ -11407,7 +11545,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="177" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="177" spans="3:15">
       <c r="C177" t="s">
         <v>532</v>
       </c>
@@ -11448,7 +11586,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="178" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="178" spans="3:15">
       <c r="C178" t="s">
         <v>535</v>
       </c>
@@ -11489,7 +11627,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="179" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="179" spans="3:15">
       <c r="C179" t="s">
         <v>535</v>
       </c>
@@ -11530,7 +11668,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="180" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="180" spans="3:15">
       <c r="C180" t="s">
         <v>538</v>
       </c>
@@ -11571,7 +11709,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="181" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="181" spans="3:15">
       <c r="C181" t="s">
         <v>541</v>
       </c>
@@ -11612,7 +11750,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="182" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="182" spans="3:15">
       <c r="C182" t="s">
         <v>542</v>
       </c>
@@ -11653,7 +11791,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="183" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="183" spans="3:15">
       <c r="C183" t="s">
         <v>545</v>
       </c>
@@ -11694,7 +11832,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="184" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="184" spans="3:15">
       <c r="C184" t="s">
         <v>548</v>
       </c>
@@ -11735,7 +11873,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="185" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="185" spans="3:15">
       <c r="C185" t="s">
         <v>548</v>
       </c>
@@ -11776,7 +11914,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="186" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="186" spans="3:15">
       <c r="C186" t="s">
         <v>551</v>
       </c>
@@ -11817,7 +11955,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="187" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="187" spans="3:15">
       <c r="C187" t="s">
         <v>551</v>
       </c>
@@ -11858,7 +11996,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="188" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="188" spans="3:15">
       <c r="C188" t="s">
         <v>556</v>
       </c>
@@ -11899,7 +12037,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="189" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="189" spans="3:15">
       <c r="C189" t="s">
         <v>559</v>
       </c>
@@ -11940,7 +12078,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="190" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="190" spans="3:15">
       <c r="C190" t="s">
         <v>562</v>
       </c>
@@ -11981,7 +12119,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="191" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="191" spans="3:15">
       <c r="C191" t="s">
         <v>565</v>
       </c>
@@ -12022,7 +12160,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="192" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="192" spans="3:15">
       <c r="C192" t="s">
         <v>568</v>
       </c>
@@ -12063,7 +12201,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="193" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="193" spans="3:15">
       <c r="C193" t="s">
         <v>571</v>
       </c>
@@ -12104,7 +12242,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="194" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="194" spans="3:15">
       <c r="C194" t="s">
         <v>574</v>
       </c>
@@ -12145,7 +12283,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="195" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="195" spans="3:15">
       <c r="C195" t="s">
         <v>574</v>
       </c>
@@ -12186,7 +12324,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="196" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="196" spans="3:15">
       <c r="C196" t="s">
         <v>576</v>
       </c>
@@ -12227,7 +12365,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="197" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="197" spans="3:15">
       <c r="C197" t="s">
         <v>579</v>
       </c>
@@ -12268,7 +12406,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="198" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="198" spans="3:15">
       <c r="C198" t="s">
         <v>582</v>
       </c>
@@ -12309,7 +12447,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="199" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="199" spans="3:15">
       <c r="C199" t="s">
         <v>585</v>
       </c>
@@ -12350,7 +12488,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="200" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="200" spans="3:15">
       <c r="C200" t="s">
         <v>588</v>
       </c>
@@ -12391,7 +12529,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="201" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="201" spans="3:15">
       <c r="C201" t="s">
         <v>591</v>
       </c>
@@ -12432,7 +12570,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="202" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="202" spans="3:15">
       <c r="C202" t="s">
         <v>594</v>
       </c>
@@ -12473,7 +12611,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="203" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="203" spans="3:15">
       <c r="C203" t="s">
         <v>596</v>
       </c>
@@ -12514,7 +12652,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="204" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="204" spans="3:15">
       <c r="C204" t="s">
         <v>599</v>
       </c>
@@ -12555,7 +12693,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="205" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="205" spans="3:15">
       <c r="C205" t="s">
         <v>602</v>
       </c>
@@ -12596,7 +12734,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="206" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="206" spans="3:15">
       <c r="C206" t="s">
         <v>602</v>
       </c>
@@ -12637,7 +12775,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="207" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="207" spans="3:15">
       <c r="C207" t="s">
         <v>605</v>
       </c>
@@ -12678,7 +12816,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="208" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="208" spans="3:15">
       <c r="C208" t="s">
         <v>608</v>
       </c>
@@ -12719,7 +12857,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="209" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="209" spans="3:15">
       <c r="C209" t="s">
         <v>611</v>
       </c>
@@ -12760,7 +12898,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="210" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="210" spans="3:15">
       <c r="C210" t="s">
         <v>614</v>
       </c>
@@ -12801,7 +12939,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="211" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="211" spans="3:15">
       <c r="C211" t="s">
         <v>617</v>
       </c>
@@ -12842,7 +12980,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="212" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="212" spans="3:15">
       <c r="C212" t="s">
         <v>620</v>
       </c>
@@ -12883,7 +13021,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="213" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="213" spans="3:15">
       <c r="C213" t="s">
         <v>623</v>
       </c>
@@ -12924,7 +13062,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="214" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="214" spans="3:15">
       <c r="C214" t="s">
         <v>626</v>
       </c>
@@ -12965,7 +13103,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="215" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="215" spans="3:15">
       <c r="C215" t="s">
         <v>629</v>
       </c>
@@ -13006,7 +13144,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="216" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="216" spans="3:15">
       <c r="C216" t="s">
         <v>629</v>
       </c>
@@ -13047,7 +13185,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="217" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="217" spans="3:15">
       <c r="C217" t="s">
         <v>634</v>
       </c>
@@ -13088,7 +13226,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="218" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="218" spans="3:15">
       <c r="C218" t="s">
         <v>637</v>
       </c>
@@ -13129,7 +13267,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="219" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="219" spans="3:15">
       <c r="C219" t="s">
         <v>640</v>
       </c>
@@ -13170,7 +13308,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="220" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="220" spans="3:15">
       <c r="C220" t="s">
         <v>643</v>
       </c>
@@ -13211,7 +13349,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="221" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="221" spans="3:15">
       <c r="C221" t="s">
         <v>646</v>
       </c>
@@ -13252,7 +13390,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="222" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="222" spans="3:15">
       <c r="C222" t="s">
         <v>649</v>
       </c>
@@ -13293,7 +13431,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="223" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="223" spans="3:15">
       <c r="C223" t="s">
         <v>649</v>
       </c>
@@ -13334,7 +13472,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="224" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="224" spans="3:15">
       <c r="C224" t="s">
         <v>652</v>
       </c>
@@ -13375,7 +13513,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="225" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="225" spans="3:15">
       <c r="C225" t="s">
         <v>655</v>
       </c>
@@ -13416,7 +13554,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="226" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="226" spans="3:15">
       <c r="C226" t="s">
         <v>658</v>
       </c>
@@ -13457,7 +13595,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="227" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="227" spans="3:15">
       <c r="C227" t="s">
         <v>662</v>
       </c>
@@ -13498,7 +13636,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="228" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="228" spans="3:15">
       <c r="C228" t="s">
         <v>662</v>
       </c>
@@ -13539,7 +13677,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="229" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="229" spans="3:15">
       <c r="C229" t="s">
         <v>665</v>
       </c>
@@ -13580,7 +13718,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="230" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="230" spans="3:15">
       <c r="C230" t="s">
         <v>668</v>
       </c>
@@ -13621,7 +13759,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="231" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="231" spans="3:15">
       <c r="C231" t="s">
         <v>668</v>
       </c>
@@ -13662,7 +13800,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="232" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="232" spans="3:15">
       <c r="C232" t="s">
         <v>671</v>
       </c>
@@ -13703,7 +13841,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="233" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="233" spans="3:15">
       <c r="C233" t="s">
         <v>674</v>
       </c>
@@ -13744,7 +13882,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="234" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="234" spans="3:15">
       <c r="C234" t="s">
         <v>677</v>
       </c>
@@ -13785,7 +13923,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="235" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="235" spans="3:15">
       <c r="C235" t="s">
         <v>680</v>
       </c>
@@ -13826,7 +13964,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="236" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="236" spans="3:15">
       <c r="C236" t="s">
         <v>683</v>
       </c>
@@ -13867,7 +14005,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="237" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="237" spans="3:15">
       <c r="C237" t="s">
         <v>686</v>
       </c>
@@ -13908,7 +14046,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="238" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="238" spans="3:15">
       <c r="C238" t="s">
         <v>689</v>
       </c>
@@ -13949,7 +14087,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="239" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="239" spans="3:15">
       <c r="C239" t="s">
         <v>692</v>
       </c>
@@ -13990,7 +14128,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="240" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="240" spans="3:15">
       <c r="C240" t="s">
         <v>695</v>
       </c>
@@ -14031,7 +14169,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="241" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="241" spans="3:15">
       <c r="C241" t="s">
         <v>695</v>
       </c>
@@ -14072,7 +14210,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="242" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="242" spans="3:15">
       <c r="C242" t="s">
         <v>698</v>
       </c>
@@ -14113,7 +14251,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="243" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="243" spans="3:15">
       <c r="C243" t="s">
         <v>701</v>
       </c>
@@ -14154,7 +14292,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="244" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="244" spans="3:15">
       <c r="C244" t="s">
         <v>701</v>
       </c>
@@ -14195,7 +14333,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="245" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="245" spans="3:15">
       <c r="C245" t="s">
         <v>704</v>
       </c>
@@ -14236,7 +14374,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="246" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="246" spans="3:15">
       <c r="C246" t="s">
         <v>707</v>
       </c>
@@ -14277,7 +14415,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="247" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="247" spans="3:15">
       <c r="C247" t="s">
         <v>710</v>
       </c>
@@ -14318,7 +14456,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="248" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="248" spans="3:15">
       <c r="C248" t="s">
         <v>713</v>
       </c>
@@ -14359,7 +14497,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="249" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="249" spans="3:15">
       <c r="C249" t="s">
         <v>716</v>
       </c>
@@ -14400,7 +14538,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="250" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="250" spans="3:15">
       <c r="C250" t="s">
         <v>719</v>
       </c>
@@ -14441,7 +14579,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="251" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="251" spans="3:15">
       <c r="C251" t="s">
         <v>722</v>
       </c>
@@ -14482,7 +14620,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="252" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="252" spans="3:15">
       <c r="C252" t="s">
         <v>725</v>
       </c>
@@ -14523,7 +14661,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="253" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="253" spans="3:15">
       <c r="C253" t="s">
         <v>725</v>
       </c>
@@ -14564,7 +14702,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="254" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="254" spans="3:15">
       <c r="C254" t="s">
         <v>728</v>
       </c>
@@ -14605,7 +14743,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="255" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="255" spans="3:15">
       <c r="C255" t="s">
         <v>728</v>
       </c>
@@ -14646,7 +14784,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="256" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="256" spans="3:15">
       <c r="C256" t="s">
         <v>733</v>
       </c>
@@ -14687,7 +14825,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="257" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="257" spans="3:15">
       <c r="C257" t="s">
         <v>736</v>
       </c>
@@ -14728,7 +14866,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="258" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="258" spans="3:15">
       <c r="C258" t="s">
         <v>739</v>
       </c>
@@ -14769,7 +14907,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="259" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="259" spans="3:15">
       <c r="C259" t="s">
         <v>739</v>
       </c>
@@ -14810,7 +14948,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="260" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="260" spans="3:15">
       <c r="C260" t="s">
         <v>744</v>
       </c>
@@ -14851,7 +14989,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="261" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="261" spans="3:15">
       <c r="C261" t="s">
         <v>747</v>
       </c>
@@ -14892,7 +15030,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="262" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="262" spans="3:15">
       <c r="C262" t="s">
         <v>750</v>
       </c>
@@ -14933,7 +15071,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="263" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="263" spans="3:15">
       <c r="C263" t="s">
         <v>753</v>
       </c>
@@ -14974,7 +15112,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="264" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="264" spans="3:15">
       <c r="C264" t="s">
         <v>756</v>
       </c>
@@ -15015,7 +15153,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="265" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="265" spans="3:15">
       <c r="C265" t="s">
         <v>759</v>
       </c>
@@ -15056,7 +15194,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="266" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="266" spans="3:15">
       <c r="C266" t="s">
         <v>762</v>
       </c>
@@ -15097,7 +15235,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="267" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="267" spans="3:15">
       <c r="C267" t="s">
         <v>765</v>
       </c>
@@ -15149,15 +15287,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FBD73F0-C549-4241-BD10-5A8B871CAB21}">
   <dimension ref="C3:F15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="3" max="3" width="28.54296875" customWidth="1"/>
-    <col min="4" max="4" width="15.453125" customWidth="1"/>
-    <col min="5" max="5" width="18.453125" customWidth="1"/>
-    <col min="6" max="6" width="24.81640625" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" customWidth="1"/>
+    <col min="6" max="6" width="24.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="3:6" ht="15.6">
       <c r="C3" s="26" t="s">
         <v>33</v>
       </c>
@@ -15171,7 +15309,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="4" spans="3:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="3:6">
       <c r="C4" t="s">
         <v>54</v>
       </c>
@@ -15188,7 +15326,7 @@
         <v>79781.805769230778</v>
       </c>
     </row>
-    <row r="5" spans="3:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="3:6">
       <c r="C5" t="s">
         <v>65</v>
       </c>
@@ -15205,7 +15343,7 @@
         <v>81976.441923076913</v>
       </c>
     </row>
-    <row r="6" spans="3:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="3:6">
       <c r="C6" t="s">
         <v>71</v>
       </c>
@@ -15222,7 +15360,7 @@
         <v>64441.299999999996</v>
       </c>
     </row>
-    <row r="7" spans="3:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="3:6">
       <c r="C7" t="s">
         <v>78</v>
       </c>
@@ -15239,7 +15377,7 @@
         <v>67242.51761904762</v>
       </c>
     </row>
-    <row r="8" spans="3:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="3:6">
       <c r="C8" t="s">
         <v>82</v>
       </c>
@@ -15256,7 +15394,7 @@
         <v>69806.945769230777</v>
       </c>
     </row>
-    <row r="9" spans="3:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="3:6">
       <c r="C9" t="s">
         <v>93</v>
       </c>
@@ -15273,7 +15411,7 @@
         <v>73109.377727272746</v>
       </c>
     </row>
-    <row r="10" spans="3:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="3:6">
       <c r="C10" t="s">
         <v>97</v>
       </c>
@@ -15290,7 +15428,7 @@
         <v>66910.765555555554</v>
       </c>
     </row>
-    <row r="11" spans="3:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="3:6">
       <c r="C11" t="s">
         <v>116</v>
       </c>
@@ -15307,7 +15445,7 @@
         <v>74673.974761904756</v>
       </c>
     </row>
-    <row r="12" spans="3:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="3:6">
       <c r="C12" t="s">
         <v>123</v>
       </c>
@@ -15324,7 +15462,7 @@
         <v>75179.064482758593</v>
       </c>
     </row>
-    <row r="13" spans="3:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="3:6">
       <c r="C13" t="s">
         <v>145</v>
       </c>
@@ -15341,7 +15479,7 @@
         <v>66432.455882352937</v>
       </c>
     </row>
-    <row r="14" spans="3:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="3:6">
       <c r="C14" t="s">
         <v>46</v>
       </c>
@@ -15358,7 +15496,7 @@
         <v>83883.965000000011</v>
       </c>
     </row>
-    <row r="15" spans="3:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="3:6">
       <c r="C15" t="s">
         <v>155</v>
       </c>
@@ -15383,22 +15521,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542A702F-F40A-46D4-8AE4-447BF9FAB70F}">
   <dimension ref="B2:N49"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="13.1796875" customWidth="1"/>
-    <col min="6" max="6" width="15.7265625" customWidth="1"/>
-    <col min="7" max="7" width="13.453125" customWidth="1"/>
-    <col min="8" max="8" width="14.7265625" customWidth="1"/>
-    <col min="9" max="9" width="16.1796875" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" customWidth="1"/>
+    <col min="9" max="9" width="16.140625" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="13.7265625" customWidth="1"/>
-    <col min="12" max="12" width="14.81640625" customWidth="1"/>
-    <col min="13" max="13" width="12.7265625" customWidth="1"/>
-    <col min="14" max="14" width="12.81640625" customWidth="1"/>
+    <col min="11" max="11" width="13.7109375" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:14">
       <c r="B2" s="28" t="str" cm="1">
         <f t="array" ref="B2:N2">staff[#Headers]</f>
         <v>Emp ID</v>
@@ -15440,7 +15578,7 @@
         <v>Work Type</v>
       </c>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:14">
       <c r="B3" t="str" cm="1">
         <f t="array" ref="B3:N49">_xlfn._xlws.FILTER(staff[],staff[Salary]&gt;100000)</f>
         <v>PR00147</v>
@@ -15482,7 +15620,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:14">
       <c r="B4" t="str">
         <v>PR00746</v>
       </c>
@@ -15523,7 +15661,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:14">
       <c r="B5" t="str">
         <v>PR01159</v>
       </c>
@@ -15564,7 +15702,7 @@
         <v>Part time</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:14">
       <c r="B6" t="str">
         <v>PR02010</v>
       </c>
@@ -15605,7 +15743,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:14">
       <c r="B7" t="str">
         <v>PR02208</v>
       </c>
@@ -15646,7 +15784,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:14">
       <c r="B8" t="str">
         <v>PR02288</v>
       </c>
@@ -15687,7 +15825,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:14">
       <c r="B9" t="str">
         <v>PR03886</v>
       </c>
@@ -15728,7 +15866,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:14">
       <c r="B10" t="str">
         <v>PR04601</v>
       </c>
@@ -15769,7 +15907,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:14">
       <c r="B11" t="str">
         <v>SQ00022</v>
       </c>
@@ -15810,7 +15948,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:14">
       <c r="B12" t="str">
         <v>SQ00144</v>
       </c>
@@ -15851,7 +15989,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:14">
       <c r="B13" t="str">
         <v>SQ00498</v>
       </c>
@@ -15892,7 +16030,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:14">
       <c r="B14" t="str">
         <v>SQ01620</v>
       </c>
@@ -15933,7 +16071,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:14">
       <c r="B15" t="str">
         <v>SQ02035</v>
       </c>
@@ -15974,7 +16112,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:14">
       <c r="B16" t="str">
         <v>SQ02035</v>
       </c>
@@ -16015,7 +16153,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:14">
       <c r="B17" t="str">
         <v>SQ02174</v>
       </c>
@@ -16056,7 +16194,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:14">
       <c r="B18" t="str">
         <v>SQ02624</v>
       </c>
@@ -16097,7 +16235,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:14">
       <c r="B19" t="str">
         <v>SQ02703</v>
       </c>
@@ -16138,7 +16276,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:14">
       <c r="B20" t="str">
         <v>SQ03116</v>
       </c>
@@ -16179,7 +16317,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:14">
       <c r="B21" t="str">
         <v>SQ03387</v>
       </c>
@@ -16220,7 +16358,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:14">
       <c r="B22" t="str">
         <v>SQ03476</v>
       </c>
@@ -16261,7 +16399,7 @@
         <v>Part time</v>
       </c>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:14">
       <c r="B23" t="str">
         <v>SQ03491</v>
       </c>
@@ -16302,7 +16440,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:14">
       <c r="B24" t="str">
         <v>SQ03733</v>
       </c>
@@ -16343,7 +16481,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:14">
       <c r="B25" t="str">
         <v>SQ04603</v>
       </c>
@@ -16384,7 +16522,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:14">
       <c r="B26" t="str">
         <v>SQ04612</v>
       </c>
@@ -16425,7 +16563,7 @@
         <v>Part time</v>
       </c>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:14">
       <c r="B27" t="str">
         <v>SQ04665</v>
       </c>
@@ -16466,7 +16604,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:14">
       <c r="B28" t="str">
         <v>TN00579</v>
       </c>
@@ -16507,7 +16645,7 @@
         <v>Part time</v>
       </c>
     </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:14">
       <c r="B29" t="str">
         <v>TN01281</v>
       </c>
@@ -16548,7 +16686,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:14">
       <c r="B30" t="str">
         <v>TN04058</v>
       </c>
@@ -16589,7 +16727,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:14">
       <c r="B31" t="str">
         <v>TN04058</v>
       </c>
@@ -16630,7 +16768,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:14">
       <c r="B32" t="str">
         <v>TN04246</v>
       </c>
@@ -16671,7 +16809,7 @@
         <v>Part time</v>
       </c>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:14">
       <c r="B33" t="str">
         <v>TN04740</v>
       </c>
@@ -16712,7 +16850,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:14">
       <c r="B34" t="str">
         <v>VT01684</v>
       </c>
@@ -16753,7 +16891,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:14">
       <c r="B35" t="str">
         <v>VT01762</v>
       </c>
@@ -16794,7 +16932,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="36" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:14">
       <c r="B36" t="str">
         <v>VT01893</v>
       </c>
@@ -16835,7 +16973,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:14">
       <c r="B37" t="str">
         <v>VT01893</v>
       </c>
@@ -16876,7 +17014,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:14">
       <c r="B38" t="str">
         <v>VT02491</v>
       </c>
@@ -16917,7 +17055,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:14">
       <c r="B39" t="str">
         <v>VT02801</v>
       </c>
@@ -16958,7 +17096,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:14">
       <c r="B40" t="str">
         <v>VT03421</v>
       </c>
@@ -16999,7 +17137,7 @@
         <v>Part time</v>
       </c>
     </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:14">
       <c r="B41" t="str">
         <v>VT03421</v>
       </c>
@@ -17040,7 +17178,7 @@
         <v>Part time</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:14">
       <c r="B42" t="str">
         <v>VT04028</v>
       </c>
@@ -17081,7 +17219,7 @@
         <v>Part time</v>
       </c>
     </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:14">
       <c r="B43" t="str">
         <v>VT04028</v>
       </c>
@@ -17122,7 +17260,7 @@
         <v>Part time</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:14">
       <c r="B44" t="str">
         <v>VT04093</v>
       </c>
@@ -17163,7 +17301,7 @@
         <v>Part time</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:14">
       <c r="B45" t="str">
         <v>VT04093</v>
       </c>
@@ -17204,7 +17342,7 @@
         <v>Part time</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:14">
       <c r="B46" t="str">
         <v>VT04350</v>
       </c>
@@ -17245,7 +17383,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:14">
       <c r="B47" t="str">
         <v>VT04350</v>
       </c>
@@ -17286,7 +17424,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:14">
       <c r="B48" t="str">
         <v>VT04552</v>
       </c>
@@ -17327,7 +17465,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="49" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:14">
       <c r="B49" t="str">
         <v>VT04681</v>
       </c>
@@ -17376,14 +17514,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3C23D95-7BCA-47B4-B1F6-E87B5F2EC2A8}">
   <dimension ref="B4:N47"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="36.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="8" max="8" width="14.26953125" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:14">
       <c r="B4" s="28" t="str" cm="1">
         <f t="array" ref="B4:N4">staff[#Headers]</f>
         <v>Emp ID</v>
@@ -17425,7 +17563,7 @@
         <v>Work Type</v>
       </c>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:14">
       <c r="B5" s="31" t="str" cm="1">
         <f t="array" ref="B5:N22">_xlfn._xlws.FILTER(staff[],(staff[Salary]&gt;100000)*(staff[Gender]="Female"))</f>
         <v>PR00746</v>
@@ -17467,7 +17605,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:14">
       <c r="B6" t="str">
         <v>PR02208</v>
       </c>
@@ -17508,7 +17646,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:14">
       <c r="B7" t="str">
         <v>SQ00498</v>
       </c>
@@ -17549,7 +17687,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:14">
       <c r="B8" t="str">
         <v>SQ02174</v>
       </c>
@@ -17590,7 +17728,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:14">
       <c r="B9" t="str">
         <v>SQ02624</v>
       </c>
@@ -17631,7 +17769,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:14">
       <c r="B10" t="str">
         <v>SQ02703</v>
       </c>
@@ -17672,7 +17810,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:14">
       <c r="B11" t="str">
         <v>SQ03387</v>
       </c>
@@ -17713,7 +17851,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:14">
       <c r="B12" t="str">
         <v>SQ03491</v>
       </c>
@@ -17754,7 +17892,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:14">
       <c r="B13" t="str">
         <v>SQ04612</v>
       </c>
@@ -17795,7 +17933,7 @@
         <v>Part time</v>
       </c>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:14">
       <c r="B14" t="str">
         <v>TN00579</v>
       </c>
@@ -17836,7 +17974,7 @@
         <v>Part time</v>
       </c>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:14">
       <c r="B15" t="str">
         <v>TN01281</v>
       </c>
@@ -17877,7 +18015,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:14">
       <c r="B16" t="str">
         <v>TN04246</v>
       </c>
@@ -17918,7 +18056,7 @@
         <v>Part time</v>
       </c>
     </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:14">
       <c r="B17" t="str">
         <v>TN04740</v>
       </c>
@@ -17959,7 +18097,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:14">
       <c r="B18" t="str">
         <v>VT01684</v>
       </c>
@@ -18000,7 +18138,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:14">
       <c r="B19" t="str">
         <v>VT04093</v>
       </c>
@@ -18041,7 +18179,7 @@
         <v>Part time</v>
       </c>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:14">
       <c r="B20" t="str">
         <v>VT04093</v>
       </c>
@@ -18082,7 +18220,7 @@
         <v>Part time</v>
       </c>
     </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:14">
       <c r="B21" t="str">
         <v>VT04552</v>
       </c>
@@ -18123,7 +18261,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:14">
       <c r="B22" t="str">
         <v>VT04681</v>
       </c>
@@ -18164,7 +18302,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:14">
       <c r="B29" s="28" t="str" cm="1">
         <f t="array" ref="B29:F29">_xlfn.CHOOSECOLS(staff[#Headers],1,2,3,5,6)</f>
         <v>Emp ID</v>
@@ -18182,7 +18320,7 @@
         <v>Salary</v>
       </c>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:14">
       <c r="B30" t="str" cm="1">
         <f t="array" ref="B30:F47">_xlfn.CHOOSECOLS(_xlfn._xlws.FILTER(staff[],(staff[Salary]&gt;100000)*(staff[Gender]="Female")),1,2,3,5,6)</f>
         <v>PR00746</v>
@@ -18200,7 +18338,7 @@
         <v>114177.23</v>
       </c>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:14">
       <c r="B31" t="str">
         <v>PR02208</v>
       </c>
@@ -18217,7 +18355,7 @@
         <v>102934.09</v>
       </c>
     </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:14">
       <c r="B32" t="str">
         <v>SQ00498</v>
       </c>
@@ -18234,7 +18372,7 @@
         <v>111049.84</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:6">
       <c r="B33" t="str">
         <v>SQ02174</v>
       </c>
@@ -18251,7 +18389,7 @@
         <v>118442.54</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:6">
       <c r="B34" t="str">
         <v>SQ02624</v>
       </c>
@@ -18268,7 +18406,7 @@
         <v>114772.32</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:6">
       <c r="B35" t="str">
         <v>SQ02703</v>
       </c>
@@ -18285,7 +18423,7 @@
         <v>104903.79</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:6">
       <c r="B36" t="str">
         <v>SQ03387</v>
       </c>
@@ -18302,7 +18440,7 @@
         <v>100731.95</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:6">
       <c r="B37" t="str">
         <v>SQ03491</v>
       </c>
@@ -18319,7 +18457,7 @@
         <v>102129.37</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:6">
       <c r="B38" t="str">
         <v>SQ04612</v>
       </c>
@@ -18336,7 +18474,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:6">
       <c r="B39" t="str">
         <v>TN00579</v>
       </c>
@@ -18353,7 +18491,7 @@
         <v>109163.39</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:6">
       <c r="B40" t="str">
         <v>TN01281</v>
       </c>
@@ -18370,7 +18508,7 @@
         <v>114425.19</v>
       </c>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:6">
       <c r="B41" t="str">
         <v>TN04246</v>
       </c>
@@ -18387,7 +18525,7 @@
         <v>100371.31</v>
       </c>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:6">
       <c r="B42" t="str">
         <v>TN04740</v>
       </c>
@@ -18404,7 +18542,7 @@
         <v>104038.9</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:6">
       <c r="B43" t="str">
         <v>VT01684</v>
       </c>
@@ -18421,7 +18559,7 @@
         <v>101187.36</v>
       </c>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:6">
       <c r="B44" t="str">
         <v>VT04093</v>
       </c>
@@ -18438,7 +18576,7 @@
         <v>116767.63</v>
       </c>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:6">
       <c r="B45" t="str">
         <v>VT04093</v>
       </c>
@@ -18455,7 +18593,7 @@
         <v>116767.63</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:6">
       <c r="B46" t="str">
         <v>VT04552</v>
       </c>
@@ -18472,7 +18610,7 @@
         <v>106665.67</v>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:6">
       <c r="B47" t="str">
         <v>VT04681</v>
       </c>
@@ -18487,6 +18625,317 @@
       </c>
       <c r="F47">
         <v>110906.35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10E1DD1C-27F2-4532-84C9-74C784316368}">
+  <dimension ref="C3:I16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="3" width="19.140625" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="9" max="9" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:9">
+      <c r="D3" s="32" t="s">
+        <v>771</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="3:9">
+      <c r="C4" t="s">
+        <v>772</v>
+      </c>
+      <c r="D4" s="29">
+        <f>MIN(staff[Salary])</f>
+        <v>28160.79</v>
+      </c>
+      <c r="E4" s="29">
+        <f>_xlfn.MINIFS(staff[Salary],staff[Gender],E$3)</f>
+        <v>28160.79</v>
+      </c>
+      <c r="F4" s="29">
+        <f>_xlfn.MINIFS(staff[Salary],staff[Gender],F$3)</f>
+        <v>28305.08</v>
+      </c>
+    </row>
+    <row r="5" spans="3:9">
+      <c r="C5" t="s">
+        <v>773</v>
+      </c>
+      <c r="D5" s="29">
+        <f>MAX(staff[Salary])</f>
+        <v>120000</v>
+      </c>
+      <c r="E5" s="29">
+        <f>_xlfn.MAXIFS(staff[Salary],staff[Gender],E$3)</f>
+        <v>120000</v>
+      </c>
+      <c r="F5" s="29">
+        <f>_xlfn.MAXIFS(staff[Salary],staff[Gender],F$3)</f>
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="6" spans="3:9">
+      <c r="C6" t="s">
+        <v>774</v>
+      </c>
+      <c r="D6" s="29">
+        <f>LARGE(staff[Salary],H6)</f>
+        <v>120000</v>
+      </c>
+      <c r="E6" s="29" cm="1">
+        <f t="array" ref="E6">LARGE(_xlfn._xlws.FILTER(staff[Salary],staff[Gender]=E$3),H6)</f>
+        <v>120000</v>
+      </c>
+      <c r="F6" s="29" cm="1">
+        <f t="array" ref="F6">LARGE(_xlfn._xlws.FILTER(staff[Salary],staff[Gender]=F$3),H6)</f>
+        <v>120000</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="3:9">
+      <c r="D7" s="29">
+        <f>LARGE(staff[Salary],H7)</f>
+        <v>120000</v>
+      </c>
+      <c r="E7" s="29" cm="1">
+        <f t="array" ref="E7">LARGE(_xlfn._xlws.FILTER(staff[Salary],staff[Gender]=E$3),H7)</f>
+        <v>119022.49</v>
+      </c>
+      <c r="F7" s="29" cm="1">
+        <f t="array" ref="F7">LARGE(_xlfn._xlws.FILTER(staff[Salary],staff[Gender]=F$3),H7)</f>
+        <v>118442.54</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="3:9">
+      <c r="D8" s="29">
+        <f>LARGE(staff[Salary],H8)</f>
+        <v>119022.49</v>
+      </c>
+      <c r="E8" s="29" cm="1">
+        <f t="array" ref="E8">LARGE(_xlfn._xlws.FILTER(staff[Salary],staff[Gender]=E$3),H8)</f>
+        <v>118976.16</v>
+      </c>
+      <c r="F8" s="29" cm="1">
+        <f t="array" ref="F8">LARGE(_xlfn._xlws.FILTER(staff[Salary],staff[Gender]=F$3),H8)</f>
+        <v>116767.63</v>
+      </c>
+      <c r="H8">
+        <v>3</v>
+      </c>
+      <c r="I8" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="9" spans="3:9">
+      <c r="D9" s="29">
+        <f>LARGE(staff[Salary],H9)</f>
+        <v>118976.16</v>
+      </c>
+      <c r="E9" s="29" cm="1">
+        <f t="array" ref="E9">LARGE(_xlfn._xlws.FILTER(staff[Salary],staff[Gender]=E$3),H9)</f>
+        <v>115191.38</v>
+      </c>
+      <c r="F9" s="29" cm="1">
+        <f t="array" ref="F9">LARGE(_xlfn._xlws.FILTER(staff[Salary],staff[Gender]=F$3),H9)</f>
+        <v>116767.63</v>
+      </c>
+      <c r="H9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="3:9">
+      <c r="D10" s="29">
+        <f>LARGE(staff[Salary],H10)</f>
+        <v>118442.54</v>
+      </c>
+      <c r="E10" s="29" cm="1">
+        <f t="array" ref="E10">LARGE(_xlfn._xlws.FILTER(staff[Salary],staff[Gender]=E$3),H10)</f>
+        <v>114691.03</v>
+      </c>
+      <c r="F10" s="29" cm="1">
+        <f t="array" ref="F10">LARGE(_xlfn._xlws.FILTER(staff[Salary],staff[Gender]=F$3),H10)</f>
+        <v>114772.32</v>
+      </c>
+      <c r="H10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="3:9" ht="30.75">
+      <c r="C12" t="s">
+        <v>774</v>
+      </c>
+      <c r="D12" s="29" cm="1">
+        <f t="array" ref="D12:D16">_xlfn.TAKE(_xlfn._xlws.SORT(staff[Salary],,-1),H12)</f>
+        <v>120000</v>
+      </c>
+      <c r="E12" s="29" cm="1">
+        <f t="array" ref="E12:E16">_xlfn.TAKE(_xlfn._xlws.SORT((_xlfn._xlws.FILTER(staff[Salary],staff[Gender]=E$3)),,-1),H12)</f>
+        <v>120000</v>
+      </c>
+      <c r="F12" s="29" cm="1">
+        <f t="array" ref="F12:F16">_xlfn.TAKE(_xlfn._xlws.SORT((_xlfn._xlws.FILTER(staff[Salary],staff[Gender]=F$3)),,-1),H12)</f>
+        <v>120000</v>
+      </c>
+      <c r="H12">
+        <v>5</v>
+      </c>
+      <c r="I12" s="31" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="13" spans="3:9">
+      <c r="C13" t="s">
+        <v>777</v>
+      </c>
+      <c r="D13" s="29">
+        <v>120000</v>
+      </c>
+      <c r="E13" s="29">
+        <v>119022.49</v>
+      </c>
+      <c r="F13" s="29">
+        <v>118442.54</v>
+      </c>
+    </row>
+    <row r="14" spans="3:9">
+      <c r="D14" s="29">
+        <v>119022.49</v>
+      </c>
+      <c r="E14" s="29">
+        <v>118976.16</v>
+      </c>
+      <c r="F14" s="29">
+        <v>116767.63</v>
+      </c>
+    </row>
+    <row r="15" spans="3:9">
+      <c r="D15" s="29">
+        <v>118976.16</v>
+      </c>
+      <c r="E15" s="29">
+        <v>115191.38</v>
+      </c>
+      <c r="F15" s="29">
+        <v>116767.63</v>
+      </c>
+    </row>
+    <row r="16" spans="3:9">
+      <c r="D16" s="29">
+        <v>118442.54</v>
+      </c>
+      <c r="E16" s="29">
+        <v>114691.03</v>
+      </c>
+      <c r="F16" s="29">
+        <v>114772.32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{758305EA-77F4-4B34-809F-57E28923060F}">
+  <dimension ref="B3:F15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="32.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:6">
+      <c r="B3" s="33" t="s">
+        <v>778</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>779</v>
+      </c>
+      <c r="F3">
+        <f>COUNTA(_xlfn.ANCHORARRAY(B4))</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6">
+      <c r="B4" t="str" cm="1">
+        <f t="array" ref="B4:B15">_xlfn._xlws.SORT(_xlfn.UNIQUE(staff[Department]))</f>
+        <v>Accounting</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6">
+      <c r="B5" t="str">
+        <v>Business Development</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6">
+      <c r="B6" t="str">
+        <v>Engineering</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6">
+      <c r="B7" t="str">
+        <v>Human Resources</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6">
+      <c r="B8" t="str">
+        <v>Legal</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6">
+      <c r="B9" t="str">
+        <v>Marketing</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6">
+      <c r="B10" t="str">
+        <v>Product Management</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6">
+      <c r="B11" t="str">
+        <v>Research and Development</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6">
+      <c r="B12" t="str">
+        <v>Sales</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6">
+      <c r="B13" t="str">
+        <v>Services</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6">
+      <c r="B14" t="str">
+        <v>Support</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6">
+      <c r="B15" t="str">
+        <v>Training</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/02Functions_Formulas/sample-data-fx.blank.xlsx
+++ b/Excel/02Functions_Formulas/sample-data-fx.blank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30117"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30125"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell 7490\Documents\PythonClassSF\DataAnalytics01\Excel\02Functions_Formulas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF60EF9A-8E98-425F-BFB5-280FCDC9DB38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A233740C-1439-4F45-B7E8-4294C7E27348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="6" xr2:uid="{26D4546B-D2A1-4444-8EAF-A6228F96F0C1}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="8" activeTab="10" xr2:uid="{26D4546B-D2A1-4444-8EAF-A6228F96F0C1}"/>
   </bookViews>
   <sheets>
     <sheet name="Concepts" sheetId="2" r:id="rId1"/>
@@ -20,6 +20,10 @@
     <sheet name="Task 03" sheetId="5" r:id="rId5"/>
     <sheet name="Task 04" sheetId="6" r:id="rId6"/>
     <sheet name="Task 05" sheetId="7" r:id="rId7"/>
+    <sheet name="Task 06" sheetId="8" r:id="rId8"/>
+    <sheet name="Task 07" sheetId="9" r:id="rId9"/>
+    <sheet name="Task 08" sheetId="10" r:id="rId10"/>
+    <sheet name="Task 09" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -64,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2412" uniqueCount="780">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2444" uniqueCount="791">
   <si>
     <t>Essential Excel Functions &amp; Formulas</t>
   </si>
@@ -2404,6 +2408,39 @@
   </si>
   <si>
     <t>Count:</t>
+  </si>
+  <si>
+    <t>Employee Id</t>
+  </si>
+  <si>
+    <t>Employee ID</t>
+  </si>
+  <si>
+    <t>First name</t>
+  </si>
+  <si>
+    <t>Last name</t>
+  </si>
+  <si>
+    <t>Entire Data horizantally</t>
+  </si>
+  <si>
+    <t>Entire Data Vertically</t>
+  </si>
+  <si>
+    <t>Entire All Data Get by last name using Filter</t>
+  </si>
+  <si>
+    <t>Max Salary</t>
+  </si>
+  <si>
+    <t>One Person</t>
+  </si>
+  <si>
+    <t>All Persons</t>
+  </si>
+  <si>
+    <t>All Persons in one cell</t>
   </si>
 </sst>
 </file>
@@ -2415,7 +2452,7 @@
     <numFmt numFmtId="164" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2465,8 +2502,16 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2500,6 +2545,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2554,7 +2605,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -2633,6 +2684,16 @@
     </xf>
     <xf numFmtId="165" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2676,8 +2737,8 @@
       <xdr:row>9</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="5" name="">
@@ -2696,7 +2757,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="5" name="">
@@ -2751,6 +2812,7 @@
           <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
         </inkml:channelProperties>
       </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-05-22T01:50:00.741"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.1" units="cm"/>
@@ -2763,7 +2825,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{71B18D4F-F180-46A4-9272-AD02F8205A18}" name="staff" displayName="staff" ref="C7:O267" totalsRowShown="0">
-  <autoFilter ref="C7:O267" xr:uid="{71B18D4F-F180-46A4-9272-AD02F8205A18}"/>
+  <autoFilter ref="C7:O267" xr:uid="{71B18D4F-F180-46A4-9272-AD02F8205A18}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Tuxwell"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C8:O267">
     <sortCondition ref="C7:C267"/>
   </sortState>
@@ -4548,6 +4616,3793 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DA0DA60-8DD2-4304-9D73-1D30DBAF95DD}">
+  <dimension ref="B3:C14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="14.28515625" customWidth="1"/>
+    <col min="3" max="3" width="47.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:3">
+      <c r="B3" s="28" t="s">
+        <v>787</v>
+      </c>
+      <c r="C3">
+        <f>MAX(staff[Salary])</f>
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" ht="19.5" customHeight="1">
+      <c r="B6" s="28" t="s">
+        <v>788</v>
+      </c>
+      <c r="C6" s="31" t="str" cm="1">
+        <f t="array" ref="C6">_xlfn.XLOOKUP(MAX(staff[Salary]), staff[Salary], staff[First Name]&amp;" "&amp;staff[Last Name])</f>
+        <v>Minerva Ricardot</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3">
+      <c r="B10" s="28" t="s">
+        <v>789</v>
+      </c>
+      <c r="C10" t="str" cm="1">
+        <f t="array" ref="C10:C11">_xlfn._xlws.FILTER(staff[First Name]&amp;" "&amp;staff[Last Name], staff[Salary]=MAX(staff[Salary]))</f>
+        <v>Minerva Ricardot</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3">
+      <c r="C11" t="str">
+        <v>Mick Spraberry</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" ht="30.75">
+      <c r="B14" s="37" t="s">
+        <v>790</v>
+      </c>
+      <c r="C14" s="31" t="str" cm="1">
+        <f t="array" ref="C14">_xlfn.TEXTJOIN(",",,_xlfn._xlws.FILTER(staff[First Name]&amp;" "&amp;staff[Last Name], staff[Salary]=MAX(staff[Salary])))</f>
+        <v>Minerva Ricardot,Mick Spraberry</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BE30797-3B4B-4C30-8236-A3EC81863B5B}">
+  <dimension ref="B3:N136"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="24.42578125" customWidth="1"/>
+    <col min="4" max="4" width="25.28515625" customWidth="1"/>
+    <col min="9" max="9" width="11.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:14">
+      <c r="B3" s="38" t="str" cm="1">
+        <f t="array" ref="B3:N3">staff[#Headers]</f>
+        <v>Emp ID</v>
+      </c>
+      <c r="C3" s="38" t="str">
+        <v>First Name</v>
+      </c>
+      <c r="D3" s="38" t="str">
+        <v>Last Name</v>
+      </c>
+      <c r="E3" s="38" t="str">
+        <v>Gender</v>
+      </c>
+      <c r="F3" s="38" t="str">
+        <v>Department</v>
+      </c>
+      <c r="G3" s="38" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="H3" s="38" t="str">
+        <v>Salary Bucket</v>
+      </c>
+      <c r="I3" s="38" t="str">
+        <v>Start Date</v>
+      </c>
+      <c r="J3" s="38" t="str">
+        <v>FTE</v>
+      </c>
+      <c r="K3" s="38" t="str">
+        <v>Employee type</v>
+      </c>
+      <c r="L3" s="38" t="str">
+        <v>Work location</v>
+      </c>
+      <c r="M3" s="38" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="N3" s="38" t="str">
+        <v>Work Type</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14">
+      <c r="B4" t="str" cm="1">
+        <f t="array" ref="B4:N10">_xlfn._xlws.FILTER(staff[], LEFT(staff[First Name],1)="H")</f>
+        <v>PR00246</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Husein</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Augar</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="G4">
+        <v>67905.8</v>
+      </c>
+      <c r="H4" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I4">
+        <v>44194</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M4">
+        <v>3.4794520547945207</v>
+      </c>
+      <c r="N4" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14">
+      <c r="B5" t="str">
+        <v>PR00746</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Hogan</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Iles</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G5">
+        <v>114177.23</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I5">
+        <v>43908</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Wellington, New Zealand</v>
+      </c>
+      <c r="M5">
+        <v>4.2630136986301368</v>
+      </c>
+      <c r="N5" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14">
+      <c r="B6" t="str">
+        <v>SQ04437</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Hephzibah</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Summerell</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Services</v>
+      </c>
+      <c r="G6">
+        <v>28305.08</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I6">
+        <v>43754</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M6">
+        <v>4.6849315068493151</v>
+      </c>
+      <c r="N6" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14">
+      <c r="B7" t="str">
+        <v>TN00214</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Hemavati</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Muthiah</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Training</v>
+      </c>
+      <c r="G7">
+        <v>37902.35</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I7">
+        <v>43823</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="M7">
+        <v>4.4958904109589044</v>
+      </c>
+      <c r="N7" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14">
+      <c r="B8" t="str">
+        <v>TN04175</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Hinda</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Label</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Human Resources</v>
+      </c>
+      <c r="G8">
+        <v>92704.48</v>
+      </c>
+      <c r="H8" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I8">
+        <v>43430</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="M8">
+        <v>5.5726027397260278</v>
+      </c>
+      <c r="N8" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14">
+      <c r="B9" t="str">
+        <v>TN04775</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Hridaynath</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Tendulkar</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Legal</v>
+      </c>
+      <c r="G9">
+        <v>31089.22</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I9">
+        <v>43776</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="M9">
+        <v>4.624657534246575</v>
+      </c>
+      <c r="N9" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14">
+      <c r="B10" t="str">
+        <v>VT01996</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Hali</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Behnecke</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Human Resources</v>
+      </c>
+      <c r="G10">
+        <v>65569.36</v>
+      </c>
+      <c r="H10" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I10">
+        <v>43293</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="L10" t="str">
+        <v>Auckland, New Zealand</v>
+      </c>
+      <c r="M10">
+        <v>5.9479452054794519</v>
+      </c>
+      <c r="N10" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14">
+      <c r="B13" s="28" t="str" cm="1">
+        <f t="array" ref="B13:N13">staff[#Headers]</f>
+        <v>Emp ID</v>
+      </c>
+      <c r="C13" s="28" t="str">
+        <v>First Name</v>
+      </c>
+      <c r="D13" s="28" t="str">
+        <v>Last Name</v>
+      </c>
+      <c r="E13" s="28" t="str">
+        <v>Gender</v>
+      </c>
+      <c r="F13" s="28" t="str">
+        <v>Department</v>
+      </c>
+      <c r="G13" s="28" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="H13" s="28" t="str">
+        <v>Salary Bucket</v>
+      </c>
+      <c r="I13" s="28" t="str">
+        <v>Start Date</v>
+      </c>
+      <c r="J13" s="28" t="str">
+        <v>FTE</v>
+      </c>
+      <c r="K13" s="28" t="str">
+        <v>Employee type</v>
+      </c>
+      <c r="L13" s="28" t="str">
+        <v>Work location</v>
+      </c>
+      <c r="M13" s="28" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="N13" s="28" t="str">
+        <v>Work Type</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14">
+      <c r="B14" t="str" cm="1">
+        <f t="array" ref="B14:N58">_xlfn._xlws.FILTER(staff[],staff[Start Date]&gt;=DATE(2021,1,1))</f>
+        <v>PR00882</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Jill</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Shipsey</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G14">
+        <v>52963.65</v>
+      </c>
+      <c r="H14" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I14" s="30">
+        <v>44288</v>
+      </c>
+      <c r="J14">
+        <v>0.3</v>
+      </c>
+      <c r="K14" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L14" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="M14">
+        <v>3.2219178082191782</v>
+      </c>
+      <c r="N14" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14">
+      <c r="B15" t="str">
+        <v>PR00893</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Vasavi</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Veeravasarapu</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Human Resources</v>
+      </c>
+      <c r="G15">
+        <v>50310.09</v>
+      </c>
+      <c r="H15" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I15" s="30">
+        <v>44285</v>
+      </c>
+      <c r="J15">
+        <v>0.4</v>
+      </c>
+      <c r="K15" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L15" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="M15">
+        <v>3.2301369863013698</v>
+      </c>
+      <c r="N15" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14">
+      <c r="B16" t="str">
+        <v>PR00916</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Inger</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Chapelhow</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Research and Development</v>
+      </c>
+      <c r="G16">
+        <v>84309.95</v>
+      </c>
+      <c r="H16" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I16" s="30">
+        <v>44501</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L16" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M16">
+        <v>2.6383561643835618</v>
+      </c>
+      <c r="N16" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14">
+      <c r="B17" t="str">
+        <v>PR01211</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Enoch</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Dowrey</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G17">
+        <v>91645.04</v>
+      </c>
+      <c r="H17" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I17" s="30">
+        <v>44223</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L17" t="str">
+        <v>Auckland, New Zealand</v>
+      </c>
+      <c r="M17">
+        <v>3.4</v>
+      </c>
+      <c r="N17" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14">
+      <c r="B18" t="str">
+        <v>PR01269</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Eleonore</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Airdrie</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G18">
+        <v>97105.19</v>
+      </c>
+      <c r="H18" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I18" s="30">
+        <v>44425</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L18" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="M18">
+        <v>2.8465753424657536</v>
+      </c>
+      <c r="N18" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14">
+      <c r="B19" t="str">
+        <v>PR01383</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Addi</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Studdeard</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Product Management</v>
+      </c>
+      <c r="G19">
+        <v>72502.61</v>
+      </c>
+      <c r="H19" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I19" s="30">
+        <v>44235</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L19" t="str">
+        <v>Wellington, New Zealand</v>
+      </c>
+      <c r="M19">
+        <v>3.3671232876712329</v>
+      </c>
+      <c r="N19" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14">
+      <c r="B20" t="str">
+        <v>PR02208</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Gowri</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Sankar</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Training</v>
+      </c>
+      <c r="G20">
+        <v>102934.09</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I20" s="30">
+        <v>44315</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L20" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="M20">
+        <v>3.1479452054794521</v>
+      </c>
+      <c r="N20" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14">
+      <c r="B21" t="str">
+        <v>PR03034</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Sreenivasa</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Naik</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="G21">
+        <v>32192.15</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I21" s="30">
+        <v>44473</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L21" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="M21">
+        <v>2.7150684931506848</v>
+      </c>
+      <c r="N21" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14">
+      <c r="B22" t="str">
+        <v>PR03445</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Myrle</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Prandoni</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="G22">
+        <v>62195.47</v>
+      </c>
+      <c r="H22" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I22" s="30">
+        <v>44434</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L22" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M22">
+        <v>2.8219178082191783</v>
+      </c>
+      <c r="N22" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14">
+      <c r="B23" t="str">
+        <v>PR03886</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Edd</v>
+      </c>
+      <c r="D23" t="str">
+        <v>MacKnockiter</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G23">
+        <v>119022.49</v>
+      </c>
+      <c r="H23" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I23" s="30">
+        <v>44431</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L23" t="str">
+        <v>Auckland, New Zealand</v>
+      </c>
+      <c r="M23">
+        <v>2.8301369863013699</v>
+      </c>
+      <c r="N23" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14">
+      <c r="B24" t="str">
+        <v>PR04446</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Sameer</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Shashank</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Research and Development</v>
+      </c>
+      <c r="G24">
+        <v>92336.08</v>
+      </c>
+      <c r="H24" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I24" s="30">
+        <v>44431</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L24" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="M24">
+        <v>2.8301369863013699</v>
+      </c>
+      <c r="N24" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14">
+      <c r="B25" t="str">
+        <v>PR04473</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Wyn</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Treadger</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Business Development</v>
+      </c>
+      <c r="G25">
+        <v>69192.850000000006</v>
+      </c>
+      <c r="H25" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I25" s="30">
+        <v>44305</v>
+      </c>
+      <c r="J25">
+        <v>1</v>
+      </c>
+      <c r="K25" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L25" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="M25">
+        <v>3.1753424657534248</v>
+      </c>
+      <c r="N25" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14">
+      <c r="B26" t="str">
+        <v>PR04601</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Yedukondalu</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Panditula</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Need to check</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Support</v>
+      </c>
+      <c r="G26">
+        <v>104802.63</v>
+      </c>
+      <c r="H26" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I26" s="30">
+        <v>44502</v>
+      </c>
+      <c r="J26">
+        <v>1</v>
+      </c>
+      <c r="K26" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L26" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="M26">
+        <v>2.6356164383561644</v>
+      </c>
+      <c r="N26" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14">
+      <c r="B27" t="str">
+        <v>SQ00286</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Ilesh</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Dasgupta</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Legal</v>
+      </c>
+      <c r="G27">
+        <v>61213.01</v>
+      </c>
+      <c r="H27" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I27" s="30">
+        <v>44365</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
+      <c r="K27" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L27" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="M27">
+        <v>3.010958904109589</v>
+      </c>
+      <c r="N27" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14">
+      <c r="B28" t="str">
+        <v>SQ00498</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Amery</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Ofer</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Legal</v>
+      </c>
+      <c r="G28">
+        <v>111049.84</v>
+      </c>
+      <c r="H28" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I28" s="30">
+        <v>44393</v>
+      </c>
+      <c r="J28">
+        <v>1</v>
+      </c>
+      <c r="K28" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L28" t="str">
+        <v>Wellington, New Zealand</v>
+      </c>
+      <c r="M28">
+        <v>2.9342465753424656</v>
+      </c>
+      <c r="N28" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14">
+      <c r="B29" t="str">
+        <v>SQ01026</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Anumati</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Shyamari</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Product Management</v>
+      </c>
+      <c r="G29">
+        <v>74924.649999999994</v>
+      </c>
+      <c r="H29" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I29" s="30">
+        <v>44239</v>
+      </c>
+      <c r="J29">
+        <v>1</v>
+      </c>
+      <c r="K29" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L29" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="M29">
+        <v>3.3561643835616439</v>
+      </c>
+      <c r="N29" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14">
+      <c r="B30" t="str">
+        <v>SQ01395</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Dennison</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Crosswaite</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Legal</v>
+      </c>
+      <c r="G30">
+        <v>90697.67</v>
+      </c>
+      <c r="H30" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I30" s="30">
+        <v>44221</v>
+      </c>
+      <c r="J30">
+        <v>0.8</v>
+      </c>
+      <c r="K30" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L30" t="str">
+        <v>Seattle, USA</v>
+      </c>
+      <c r="M30">
+        <v>3.4054794520547946</v>
+      </c>
+      <c r="N30" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14">
+      <c r="B31" t="str">
+        <v>SQ01998</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Vanmala</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Shriharsha</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Product Management</v>
+      </c>
+      <c r="G31">
+        <v>40445.29</v>
+      </c>
+      <c r="H31" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I31" s="30">
+        <v>44393</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+      <c r="K31" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L31" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="M31">
+        <v>2.9342465753424656</v>
+      </c>
+      <c r="N31" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="32" spans="2:14">
+      <c r="B32" t="str">
+        <v>SQ01998</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Sahas</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Sanabhi</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Product Management</v>
+      </c>
+      <c r="G32">
+        <v>40445.29</v>
+      </c>
+      <c r="H32" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I32" s="30">
+        <v>44393</v>
+      </c>
+      <c r="J32">
+        <v>1</v>
+      </c>
+      <c r="K32" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L32" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="M32">
+        <v>2.9342465753424656</v>
+      </c>
+      <c r="N32" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14">
+      <c r="B33" t="str">
+        <v>SQ02525</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Mickie</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Dagwell</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G33">
+        <v>50855.53</v>
+      </c>
+      <c r="H33" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I33" s="30">
+        <v>44221</v>
+      </c>
+      <c r="J33">
+        <v>1</v>
+      </c>
+      <c r="K33" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L33" t="str">
+        <v>Wellington, New Zealand</v>
+      </c>
+      <c r="M33">
+        <v>3.4054794520547946</v>
+      </c>
+      <c r="N33" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14">
+      <c r="B34" t="str">
+        <v>SQ02565</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Konstantin</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Timblett</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Training</v>
+      </c>
+      <c r="G34">
+        <v>56253.81</v>
+      </c>
+      <c r="H34" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I34" s="30">
+        <v>44421</v>
+      </c>
+      <c r="J34">
+        <v>1</v>
+      </c>
+      <c r="K34" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L34" t="str">
+        <v>Auckland, New Zealand</v>
+      </c>
+      <c r="M34">
+        <v>2.8575342465753426</v>
+      </c>
+      <c r="N34" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14">
+      <c r="B35" t="str">
+        <v>SQ02624</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Gwenneth</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Fealey</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G35">
+        <v>114772.32</v>
+      </c>
+      <c r="H35" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I35" s="30">
+        <v>44251</v>
+      </c>
+      <c r="J35">
+        <v>1</v>
+      </c>
+      <c r="K35" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L35" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="M35">
+        <v>3.3232876712328765</v>
+      </c>
+      <c r="N35" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="36" spans="2:14">
+      <c r="B36" t="str">
+        <v>SQ03491</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Freda</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Legan</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="G36">
+        <v>102129.37</v>
+      </c>
+      <c r="H36" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I36" s="30">
+        <v>44396</v>
+      </c>
+      <c r="J36">
+        <v>1</v>
+      </c>
+      <c r="K36" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L36" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="M36">
+        <v>2.9260273972602739</v>
+      </c>
+      <c r="N36" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14">
+      <c r="B37" t="str">
+        <v>SQ03546</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Amlankusum</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Rajabhushan</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F37" t="str">
+        <v>Legal</v>
+      </c>
+      <c r="G37">
+        <v>75733.740000000005</v>
+      </c>
+      <c r="H37" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I37" s="30">
+        <v>44382</v>
+      </c>
+      <c r="J37">
+        <v>1</v>
+      </c>
+      <c r="K37" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L37" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="M37">
+        <v>2.9643835616438357</v>
+      </c>
+      <c r="N37" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="38" spans="2:14">
+      <c r="B38" t="str">
+        <v>SQ03626</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Krishnakanta</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Vellanki</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Training</v>
+      </c>
+      <c r="G38">
+        <v>95677.9</v>
+      </c>
+      <c r="H38" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I38" s="30">
+        <v>44396</v>
+      </c>
+      <c r="J38">
+        <v>0.3</v>
+      </c>
+      <c r="K38" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L38" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="M38">
+        <v>2.9260273972602739</v>
+      </c>
+      <c r="N38" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14">
+      <c r="B39" t="str">
+        <v>TN00890</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Mayur</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Kousika</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F39" t="str">
+        <v>Training</v>
+      </c>
+      <c r="G39">
+        <v>71570.990000000005</v>
+      </c>
+      <c r="H39" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I39" s="30">
+        <v>44249</v>
+      </c>
+      <c r="J39">
+        <v>0.5</v>
+      </c>
+      <c r="K39" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L39" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="M39">
+        <v>3.3287671232876712</v>
+      </c>
+      <c r="N39" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="40" spans="2:14">
+      <c r="B40" t="str">
+        <v>TN01601</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Melva</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Jickells</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F40" t="str">
+        <v>Product Management</v>
+      </c>
+      <c r="G40">
+        <v>68795.48</v>
+      </c>
+      <c r="H40" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I40" s="30">
+        <v>44277</v>
+      </c>
+      <c r="J40">
+        <v>0.2</v>
+      </c>
+      <c r="K40" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L40" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M40">
+        <v>3.2520547945205478</v>
+      </c>
+      <c r="N40" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="41" spans="2:14">
+      <c r="B41" t="str">
+        <v>TN01601</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Melva</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Jickells</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F41" t="str">
+        <v>Product Management</v>
+      </c>
+      <c r="G41">
+        <v>68795.48</v>
+      </c>
+      <c r="H41" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I41" s="30">
+        <v>44277</v>
+      </c>
+      <c r="J41">
+        <v>0.2</v>
+      </c>
+      <c r="K41" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L41" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M41">
+        <v>3.2520547945205478</v>
+      </c>
+      <c r="N41" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14">
+      <c r="B42" t="str">
+        <v>TN02674</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Antonetta</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Coggeshall</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F42" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="G42">
+        <v>96753.78</v>
+      </c>
+      <c r="H42" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I42" s="30">
+        <v>44494</v>
+      </c>
+      <c r="J42">
+        <v>1</v>
+      </c>
+      <c r="K42" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L42" t="str">
+        <v>Auckland, New Zealand</v>
+      </c>
+      <c r="M42">
+        <v>2.6575342465753424</v>
+      </c>
+      <c r="N42" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14">
+      <c r="B43" t="str">
+        <v>TN02674</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Antonetta</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Coggeshall</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F43" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="G43">
+        <v>96753.78</v>
+      </c>
+      <c r="H43" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I43" s="30">
+        <v>44494</v>
+      </c>
+      <c r="J43">
+        <v>1</v>
+      </c>
+      <c r="K43" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L43" t="str">
+        <v>Auckland, New Zealand</v>
+      </c>
+      <c r="M43">
+        <v>2.6575342465753424</v>
+      </c>
+      <c r="N43" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14">
+      <c r="B44" t="str">
+        <v>TN02988</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Mahindra</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Sreedharan</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F44" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G44">
+        <v>92943.89</v>
+      </c>
+      <c r="H44" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I44" s="30">
+        <v>44510</v>
+      </c>
+      <c r="J44">
+        <v>1</v>
+      </c>
+      <c r="K44" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L44" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="M44">
+        <v>2.6136986301369864</v>
+      </c>
+      <c r="N44" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14">
+      <c r="B45" t="str">
+        <v>TN03032</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Jaipal</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Potanapudi</v>
+      </c>
+      <c r="E45" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F45" t="str">
+        <v>Research and Development</v>
+      </c>
+      <c r="G45">
+        <v>39700.82</v>
+      </c>
+      <c r="H45" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I45" s="30">
+        <v>44203</v>
+      </c>
+      <c r="J45">
+        <v>0.8</v>
+      </c>
+      <c r="K45" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L45" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="M45">
+        <v>3.4547945205479453</v>
+      </c>
+      <c r="N45" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14">
+      <c r="B46" t="str">
+        <v>TN03032</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Fullara</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Sushanti</v>
+      </c>
+      <c r="E46" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F46" t="str">
+        <v>Research and Development</v>
+      </c>
+      <c r="G46">
+        <v>39700.82</v>
+      </c>
+      <c r="H46" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I46" s="30">
+        <v>44203</v>
+      </c>
+      <c r="J46">
+        <v>0.8</v>
+      </c>
+      <c r="K46" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L46" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="M46">
+        <v>3.4547945205479453</v>
+      </c>
+      <c r="N46" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14">
+      <c r="B47" t="str">
+        <v>TN04265</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Rushil</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Kripa</v>
+      </c>
+      <c r="E47" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F47" t="str">
+        <v>Training</v>
+      </c>
+      <c r="G47">
+        <v>93964.3</v>
+      </c>
+      <c r="H47" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I47" s="30">
+        <v>44454</v>
+      </c>
+      <c r="J47">
+        <v>0.4</v>
+      </c>
+      <c r="K47" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="L47" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="M47">
+        <v>2.7671232876712328</v>
+      </c>
+      <c r="N47" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14">
+      <c r="B48" t="str">
+        <v>VT00194</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Violante</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Courtonne</v>
+      </c>
+      <c r="E48" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F48" t="str">
+        <v>Product Management</v>
+      </c>
+      <c r="G48">
+        <v>49625.64</v>
+      </c>
+      <c r="H48" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I48" s="30">
+        <v>44384</v>
+      </c>
+      <c r="J48">
+        <v>0.5</v>
+      </c>
+      <c r="K48" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="L48" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M48">
+        <v>2.9589041095890409</v>
+      </c>
+      <c r="N48" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="49" spans="2:14">
+      <c r="B49" t="str">
+        <v>VT00578</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Magnum</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Locksley</v>
+      </c>
+      <c r="E49" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F49" t="str">
+        <v>Services</v>
+      </c>
+      <c r="G49">
+        <v>42314.39</v>
+      </c>
+      <c r="H49" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I49" s="30">
+        <v>44487</v>
+      </c>
+      <c r="J49">
+        <v>1</v>
+      </c>
+      <c r="K49" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="L49" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M49">
+        <v>2.6767123287671235</v>
+      </c>
+      <c r="N49" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="50" spans="2:14">
+      <c r="B50" t="str">
+        <v>VT01249</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Brendan</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Edgeller</v>
+      </c>
+      <c r="E50" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F50" t="str">
+        <v>Legal</v>
+      </c>
+      <c r="G50">
+        <v>31042.51</v>
+      </c>
+      <c r="H50" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I50" s="30">
+        <v>44473</v>
+      </c>
+      <c r="J50">
+        <v>0.3</v>
+      </c>
+      <c r="K50" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="L50" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M50">
+        <v>2.7150684931506848</v>
+      </c>
+      <c r="N50" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="51" spans="2:14">
+      <c r="B51" t="str">
+        <v>VT02118</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Oorjit</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Nandanavanam</v>
+      </c>
+      <c r="E51" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F51" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G51">
+        <v>51165.37</v>
+      </c>
+      <c r="H51" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I51" s="30">
+        <v>44237</v>
+      </c>
+      <c r="J51">
+        <v>1</v>
+      </c>
+      <c r="K51" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="L51" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="M51">
+        <v>3.3616438356164382</v>
+      </c>
+      <c r="N51" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="52" spans="2:14">
+      <c r="B52" t="str">
+        <v>VT02663</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Sravanthi</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Chalaki</v>
+      </c>
+      <c r="E52" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F52" t="str">
+        <v>Legal</v>
+      </c>
+      <c r="G52">
+        <v>28481.16</v>
+      </c>
+      <c r="H52" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I52" s="30">
+        <v>44228</v>
+      </c>
+      <c r="J52">
+        <v>1</v>
+      </c>
+      <c r="K52" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="L52" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="M52">
+        <v>3.3863013698630136</v>
+      </c>
+      <c r="N52" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="53" spans="2:14">
+      <c r="B53" t="str">
+        <v>VT03421</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Alic</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Bagg</v>
+      </c>
+      <c r="E53" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F53" t="str">
+        <v>Legal</v>
+      </c>
+      <c r="G53">
+        <v>113747.56</v>
+      </c>
+      <c r="H53" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I53" s="30">
+        <v>44270</v>
+      </c>
+      <c r="J53">
+        <v>0.7</v>
+      </c>
+      <c r="K53" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="L53" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="M53">
+        <v>3.2712328767123289</v>
+      </c>
+      <c r="N53" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="54" spans="2:14">
+      <c r="B54" t="str">
+        <v>VT03421</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Alic</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Bagg</v>
+      </c>
+      <c r="E54" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F54" t="str">
+        <v>Legal</v>
+      </c>
+      <c r="G54">
+        <v>113747.56</v>
+      </c>
+      <c r="H54" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I54" s="30">
+        <v>44270</v>
+      </c>
+      <c r="J54">
+        <v>0.7</v>
+      </c>
+      <c r="K54" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="L54" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="M54">
+        <v>3.2712328767123289</v>
+      </c>
+      <c r="N54" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="55" spans="2:14">
+      <c r="B55" t="str">
+        <v>VT03500</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Shiuli</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Sapna</v>
+      </c>
+      <c r="E55" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F55" t="str">
+        <v>Support</v>
+      </c>
+      <c r="G55">
+        <v>37062.1</v>
+      </c>
+      <c r="H55" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I55" s="30">
+        <v>44357</v>
+      </c>
+      <c r="J55">
+        <v>1</v>
+      </c>
+      <c r="K55" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="L55" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="M55">
+        <v>3.032876712328767</v>
+      </c>
+      <c r="N55" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="56" spans="2:14">
+      <c r="B56" t="str">
+        <v>VT03552</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Kamalakshi</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Mukundan</v>
+      </c>
+      <c r="E56" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F56" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G56">
+        <v>36536.26</v>
+      </c>
+      <c r="H56" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I56" s="30">
+        <v>44358</v>
+      </c>
+      <c r="J56">
+        <v>1</v>
+      </c>
+      <c r="K56" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="L56" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="M56">
+        <v>3.0301369863013701</v>
+      </c>
+      <c r="N56" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="57" spans="2:14">
+      <c r="B57" t="str">
+        <v>VT03993</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Dulce</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Colbeck</v>
+      </c>
+      <c r="E57" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F57" t="str">
+        <v>Human Resources</v>
+      </c>
+      <c r="G57">
+        <v>83396.5</v>
+      </c>
+      <c r="H57" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I57" s="30">
+        <v>44285</v>
+      </c>
+      <c r="J57">
+        <v>1</v>
+      </c>
+      <c r="K57" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="L57" t="str">
+        <v>Auckland, New Zealand</v>
+      </c>
+      <c r="M57">
+        <v>3.2301369863013698</v>
+      </c>
+      <c r="N57" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="58" spans="2:14">
+      <c r="B58" t="str">
+        <v>VT04627</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Yvette</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Bett</v>
+      </c>
+      <c r="E58" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F58" t="str">
+        <v>Human Resources</v>
+      </c>
+      <c r="G58">
+        <v>76320.44</v>
+      </c>
+      <c r="H58" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I58" s="30">
+        <v>44383</v>
+      </c>
+      <c r="J58">
+        <v>0.8</v>
+      </c>
+      <c r="K58" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="L58" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M58">
+        <v>2.9616438356164383</v>
+      </c>
+      <c r="N58" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="59" spans="2:14">
+      <c r="I59" s="30"/>
+    </row>
+    <row r="60" spans="2:14">
+      <c r="I60" s="30"/>
+    </row>
+    <row r="61" spans="2:14">
+      <c r="I61" s="30"/>
+    </row>
+    <row r="62" spans="2:14">
+      <c r="B62" s="28" t="str" cm="1">
+        <f t="array" ref="B62:N62">staff[#Headers]</f>
+        <v>Emp ID</v>
+      </c>
+      <c r="C62" s="28" t="str">
+        <v>First Name</v>
+      </c>
+      <c r="D62" s="28" t="str">
+        <v>Last Name</v>
+      </c>
+      <c r="E62" s="28" t="str">
+        <v>Gender</v>
+      </c>
+      <c r="F62" s="28" t="str">
+        <v>Department</v>
+      </c>
+      <c r="G62" s="28" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="H62" s="28" t="str">
+        <v>Salary Bucket</v>
+      </c>
+      <c r="I62" s="39" t="str">
+        <v>Start Date</v>
+      </c>
+      <c r="J62" s="28" t="str">
+        <v>FTE</v>
+      </c>
+      <c r="K62" s="28" t="str">
+        <v>Employee type</v>
+      </c>
+      <c r="L62" s="28" t="str">
+        <v>Work location</v>
+      </c>
+      <c r="M62" s="28" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="N62" s="28" t="str">
+        <v>Work Type</v>
+      </c>
+    </row>
+    <row r="63" spans="2:14">
+      <c r="B63" t="str" cm="1">
+        <f t="array" ref="B63:N84">_xlfn._xlws.FILTER(staff[],MONTH(staff[Start Date])=3)</f>
+        <v>PR00746</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Hogan</v>
+      </c>
+      <c r="D63" t="str">
+        <v>Iles</v>
+      </c>
+      <c r="E63" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F63" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G63">
+        <v>114177.23</v>
+      </c>
+      <c r="H63" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I63" s="30">
+        <v>43908</v>
+      </c>
+      <c r="J63">
+        <v>1</v>
+      </c>
+      <c r="K63" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L63" t="str">
+        <v>Wellington, New Zealand</v>
+      </c>
+      <c r="M63">
+        <v>4.2630136986301368</v>
+      </c>
+      <c r="N63" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="64" spans="2:14">
+      <c r="B64" t="str">
+        <v>PR00893</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Vasavi</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Veeravasarapu</v>
+      </c>
+      <c r="E64" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F64" t="str">
+        <v>Human Resources</v>
+      </c>
+      <c r="G64">
+        <v>50310.09</v>
+      </c>
+      <c r="H64" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I64" s="30">
+        <v>44285</v>
+      </c>
+      <c r="J64">
+        <v>0.4</v>
+      </c>
+      <c r="K64" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L64" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="M64">
+        <v>3.2301369863013698</v>
+      </c>
+      <c r="N64" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14">
+      <c r="B65" t="str">
+        <v>SQ00022</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Carlin</v>
+      </c>
+      <c r="D65" t="str">
+        <v>Demke</v>
+      </c>
+      <c r="E65" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F65" t="str">
+        <v>Business Development</v>
+      </c>
+      <c r="G65">
+        <v>110042.37</v>
+      </c>
+      <c r="H65" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I65" s="30">
+        <v>43914</v>
+      </c>
+      <c r="J65">
+        <v>1</v>
+      </c>
+      <c r="K65" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L65" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="M65">
+        <v>4.2465753424657535</v>
+      </c>
+      <c r="N65" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14">
+      <c r="B66" t="str">
+        <v>SQ00105</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Sarayu</v>
+      </c>
+      <c r="D66" t="str">
+        <v>Ragunathan</v>
+      </c>
+      <c r="E66" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F66" t="str">
+        <v>Training</v>
+      </c>
+      <c r="G66">
+        <v>86010.54</v>
+      </c>
+      <c r="H66" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I66" s="30">
+        <v>43164</v>
+      </c>
+      <c r="J66">
+        <v>1</v>
+      </c>
+      <c r="K66" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L66" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="M66">
+        <v>6.3013698630136989</v>
+      </c>
+      <c r="N66" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14">
+      <c r="B67" t="str">
+        <v>SQ01519</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Caron</v>
+      </c>
+      <c r="D67" t="str">
+        <v>Kolakovic</v>
+      </c>
+      <c r="E67" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F67" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G67">
+        <v>49915.14</v>
+      </c>
+      <c r="H67" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I67" s="30">
+        <v>43550</v>
+      </c>
+      <c r="J67">
+        <v>1</v>
+      </c>
+      <c r="K67" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L67" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M67">
+        <v>5.2438356164383562</v>
+      </c>
+      <c r="N67" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="68" spans="2:14">
+      <c r="B68" t="str">
+        <v>SQ03112</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Kantimoy</v>
+      </c>
+      <c r="D68" t="str">
+        <v>Pritish</v>
+      </c>
+      <c r="E68" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F68" t="str">
+        <v>Product Management</v>
+      </c>
+      <c r="G68">
+        <v>77743.149999999994</v>
+      </c>
+      <c r="H68" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I68" s="30">
+        <v>43920</v>
+      </c>
+      <c r="J68">
+        <v>1</v>
+      </c>
+      <c r="K68" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L68" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="M68">
+        <v>4.2301369863013702</v>
+      </c>
+      <c r="N68" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14">
+      <c r="B69" t="str">
+        <v>SQ03625</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Fidela</v>
+      </c>
+      <c r="D69" t="str">
+        <v>Artis</v>
+      </c>
+      <c r="E69" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F69" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="G69">
+        <v>78020.39</v>
+      </c>
+      <c r="H69" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I69" s="30">
+        <v>43899</v>
+      </c>
+      <c r="J69">
+        <v>1</v>
+      </c>
+      <c r="K69" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L69" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M69">
+        <v>4.2876712328767121</v>
+      </c>
+      <c r="N69" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14">
+      <c r="B70" t="str">
+        <v>SQ04612</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Mick</v>
+      </c>
+      <c r="D70" t="str">
+        <v>Spraberry</v>
+      </c>
+      <c r="E70" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F70" t="str">
+        <v>Services</v>
+      </c>
+      <c r="G70">
+        <v>120000</v>
+      </c>
+      <c r="H70" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I70" s="30">
+        <v>43902</v>
+      </c>
+      <c r="J70">
+        <v>0.9</v>
+      </c>
+      <c r="K70" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L70" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M70">
+        <v>4.279452054794521</v>
+      </c>
+      <c r="N70" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14">
+      <c r="B71" t="str">
+        <v>TN01256</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Shattesh</v>
+      </c>
+      <c r="D71" t="str">
+        <v>Utpat</v>
+      </c>
+      <c r="E71" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F71" t="str">
+        <v>Legal</v>
+      </c>
+      <c r="G71">
+        <v>28481.16</v>
+      </c>
+      <c r="H71" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I71" s="30">
+        <v>43916</v>
+      </c>
+      <c r="J71">
+        <v>1</v>
+      </c>
+      <c r="K71" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L71" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="M71">
+        <v>4.2410958904109588</v>
+      </c>
+      <c r="N71" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14">
+      <c r="B72" t="str">
+        <v>TN01256</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Sawini</v>
+      </c>
+      <c r="D72" t="str">
+        <v>Chandan</v>
+      </c>
+      <c r="E72" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F72" t="str">
+        <v>Legal</v>
+      </c>
+      <c r="G72">
+        <v>28481.16</v>
+      </c>
+      <c r="H72" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I72" s="30">
+        <v>43916</v>
+      </c>
+      <c r="J72">
+        <v>1</v>
+      </c>
+      <c r="K72" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L72" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="M72">
+        <v>4.2410958904109588</v>
+      </c>
+      <c r="N72" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14">
+      <c r="B73" t="str">
+        <v>TN01601</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Melva</v>
+      </c>
+      <c r="D73" t="str">
+        <v>Jickells</v>
+      </c>
+      <c r="E73" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F73" t="str">
+        <v>Product Management</v>
+      </c>
+      <c r="G73">
+        <v>68795.48</v>
+      </c>
+      <c r="H73" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I73" s="30">
+        <v>44277</v>
+      </c>
+      <c r="J73">
+        <v>0.2</v>
+      </c>
+      <c r="K73" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L73" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M73">
+        <v>3.2520547945205478</v>
+      </c>
+      <c r="N73" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14">
+      <c r="B74" t="str">
+        <v>TN01601</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Melva</v>
+      </c>
+      <c r="D74" t="str">
+        <v>Jickells</v>
+      </c>
+      <c r="E74" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F74" t="str">
+        <v>Product Management</v>
+      </c>
+      <c r="G74">
+        <v>68795.48</v>
+      </c>
+      <c r="H74" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I74" s="30">
+        <v>44277</v>
+      </c>
+      <c r="J74">
+        <v>0.2</v>
+      </c>
+      <c r="K74" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L74" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M74">
+        <v>3.2520547945205478</v>
+      </c>
+      <c r="N74" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14">
+      <c r="B75" t="str">
+        <v>TN04892</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Luca</v>
+      </c>
+      <c r="D75" t="str">
+        <v>Wolstenholme</v>
+      </c>
+      <c r="E75" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F75" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G75">
+        <v>53184.02</v>
+      </c>
+      <c r="H75" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I75" s="30">
+        <v>43180</v>
+      </c>
+      <c r="J75">
+        <v>1</v>
+      </c>
+      <c r="K75" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="L75" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M75">
+        <v>6.2575342465753421</v>
+      </c>
+      <c r="N75" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14">
+      <c r="B76" t="str">
+        <v>VT01762</v>
+      </c>
+      <c r="C76" t="str">
+        <v>Geena</v>
+      </c>
+      <c r="D76" t="str">
+        <v>Raghavanpillai</v>
+      </c>
+      <c r="E76" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F76" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G76">
+        <v>102515.81</v>
+      </c>
+      <c r="H76" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I76" s="30">
+        <v>43902</v>
+      </c>
+      <c r="J76">
+        <v>1</v>
+      </c>
+      <c r="K76" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="L76" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="M76">
+        <v>4.279452054794521</v>
+      </c>
+      <c r="N76" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14">
+      <c r="B77" t="str">
+        <v>VT01803</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Freddy</v>
+      </c>
+      <c r="D77" t="str">
+        <v>Linford</v>
+      </c>
+      <c r="E77" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F77" t="str">
+        <v>Training</v>
+      </c>
+      <c r="G77">
+        <v>93128.34</v>
+      </c>
+      <c r="H77" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I77" s="30">
+        <v>43164</v>
+      </c>
+      <c r="J77">
+        <v>1</v>
+      </c>
+      <c r="K77" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="L77" t="str">
+        <v>Seattle, USA</v>
+      </c>
+      <c r="M77">
+        <v>6.3013698630136989</v>
+      </c>
+      <c r="N77" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="78" spans="2:14">
+      <c r="B78" t="str">
+        <v>VT02417</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Evangelina</v>
+      </c>
+      <c r="D78" t="str">
+        <v>Lergan</v>
+      </c>
+      <c r="E78" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F78" t="str">
+        <v>Support</v>
+      </c>
+      <c r="G78">
+        <v>61214.26</v>
+      </c>
+      <c r="H78" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I78" s="30">
+        <v>43171</v>
+      </c>
+      <c r="J78">
+        <v>1</v>
+      </c>
+      <c r="K78" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="L78" t="str">
+        <v>Auckland, New Zealand</v>
+      </c>
+      <c r="M78">
+        <v>6.2821917808219174</v>
+      </c>
+      <c r="N78" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14">
+      <c r="B79" t="str">
+        <v>VT03421</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Alic</v>
+      </c>
+      <c r="D79" t="str">
+        <v>Bagg</v>
+      </c>
+      <c r="E79" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F79" t="str">
+        <v>Legal</v>
+      </c>
+      <c r="G79">
+        <v>113747.56</v>
+      </c>
+      <c r="H79" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I79" s="30">
+        <v>44270</v>
+      </c>
+      <c r="J79">
+        <v>0.7</v>
+      </c>
+      <c r="K79" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="L79" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="M79">
+        <v>3.2712328767123289</v>
+      </c>
+      <c r="N79" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="80" spans="2:14">
+      <c r="B80" t="str">
+        <v>VT03421</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Alic</v>
+      </c>
+      <c r="D80" t="str">
+        <v>Bagg</v>
+      </c>
+      <c r="E80" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F80" t="str">
+        <v>Legal</v>
+      </c>
+      <c r="G80">
+        <v>113747.56</v>
+      </c>
+      <c r="H80" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I80" s="30">
+        <v>44270</v>
+      </c>
+      <c r="J80">
+        <v>0.7</v>
+      </c>
+      <c r="K80" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="L80" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="M80">
+        <v>3.2712328767123289</v>
+      </c>
+      <c r="N80" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="81" spans="2:14">
+      <c r="B81" t="str">
+        <v>VT03993</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Dulce</v>
+      </c>
+      <c r="D81" t="str">
+        <v>Colbeck</v>
+      </c>
+      <c r="E81" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F81" t="str">
+        <v>Human Resources</v>
+      </c>
+      <c r="G81">
+        <v>83396.5</v>
+      </c>
+      <c r="H81" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I81" s="30">
+        <v>44285</v>
+      </c>
+      <c r="J81">
+        <v>1</v>
+      </c>
+      <c r="K81" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="L81" t="str">
+        <v>Auckland, New Zealand</v>
+      </c>
+      <c r="M81">
+        <v>3.2301369863013698</v>
+      </c>
+      <c r="N81" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="82" spans="2:14">
+      <c r="B82" t="str">
+        <v>VT04028</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Michale</v>
+      </c>
+      <c r="D82" t="str">
+        <v>Rolf</v>
+      </c>
+      <c r="E82" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F82" t="str">
+        <v>Services</v>
+      </c>
+      <c r="G82">
+        <v>111815.49</v>
+      </c>
+      <c r="H82" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I82" s="30">
+        <v>43895</v>
+      </c>
+      <c r="J82">
+        <v>0.7</v>
+      </c>
+      <c r="K82" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="L82" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M82">
+        <v>4.2986301369863016</v>
+      </c>
+      <c r="N82" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="83" spans="2:14">
+      <c r="B83" t="str">
+        <v>VT04028</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Michale</v>
+      </c>
+      <c r="D83" t="str">
+        <v>Rolf</v>
+      </c>
+      <c r="E83" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F83" t="str">
+        <v>Services</v>
+      </c>
+      <c r="G83">
+        <v>111815.49</v>
+      </c>
+      <c r="H83" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I83" s="30">
+        <v>43895</v>
+      </c>
+      <c r="J83">
+        <v>0.7</v>
+      </c>
+      <c r="K83" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="L83" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M83">
+        <v>4.2986301369863016</v>
+      </c>
+      <c r="N83" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="84" spans="2:14">
+      <c r="B84" t="str">
+        <v>VT04415</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Malory</v>
+      </c>
+      <c r="D84" t="str">
+        <v>Biles</v>
+      </c>
+      <c r="E84" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F84" t="str">
+        <v>Training</v>
+      </c>
+      <c r="G84">
+        <v>58744.17</v>
+      </c>
+      <c r="H84" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I84" s="30">
+        <v>43171</v>
+      </c>
+      <c r="J84">
+        <v>1</v>
+      </c>
+      <c r="K84" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="L84" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="M84">
+        <v>6.2821917808219174</v>
+      </c>
+      <c r="N84" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="85" spans="2:14">
+      <c r="I85" s="30"/>
+    </row>
+    <row r="86" spans="2:14">
+      <c r="I86" s="30"/>
+    </row>
+    <row r="87" spans="2:14">
+      <c r="I87" s="30"/>
+    </row>
+    <row r="88" spans="2:14">
+      <c r="B88" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="C88" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="D88" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="I88" s="30"/>
+    </row>
+    <row r="89" spans="2:14">
+      <c r="B89" t="str" cm="1">
+        <f t="array" ref="B89:D110">_xlfn._xlws.FILTER(staff[[Emp ID]:[Last Name]],MONTH(staff[Start Date])=3)</f>
+        <v>PR00746</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Hogan</v>
+      </c>
+      <c r="D89" t="str">
+        <v>Iles</v>
+      </c>
+      <c r="I89" s="30"/>
+    </row>
+    <row r="90" spans="2:14">
+      <c r="B90" t="str">
+        <v>PR00893</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Vasavi</v>
+      </c>
+      <c r="D90" t="str">
+        <v>Veeravasarapu</v>
+      </c>
+      <c r="I90" s="30"/>
+    </row>
+    <row r="91" spans="2:14">
+      <c r="B91" t="str">
+        <v>SQ00022</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Carlin</v>
+      </c>
+      <c r="D91" t="str">
+        <v>Demke</v>
+      </c>
+      <c r="I91" s="30"/>
+    </row>
+    <row r="92" spans="2:14">
+      <c r="B92" t="str">
+        <v>SQ00105</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Sarayu</v>
+      </c>
+      <c r="D92" t="str">
+        <v>Ragunathan</v>
+      </c>
+      <c r="I92" s="30"/>
+    </row>
+    <row r="93" spans="2:14">
+      <c r="B93" t="str">
+        <v>SQ01519</v>
+      </c>
+      <c r="C93" t="str">
+        <v>Caron</v>
+      </c>
+      <c r="D93" t="str">
+        <v>Kolakovic</v>
+      </c>
+      <c r="I93" s="30"/>
+    </row>
+    <row r="94" spans="2:14">
+      <c r="B94" t="str">
+        <v>SQ03112</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Kantimoy</v>
+      </c>
+      <c r="D94" t="str">
+        <v>Pritish</v>
+      </c>
+      <c r="I94" s="30"/>
+    </row>
+    <row r="95" spans="2:14">
+      <c r="B95" t="str">
+        <v>SQ03625</v>
+      </c>
+      <c r="C95" t="str">
+        <v>Fidela</v>
+      </c>
+      <c r="D95" t="str">
+        <v>Artis</v>
+      </c>
+      <c r="I95" s="30"/>
+    </row>
+    <row r="96" spans="2:14">
+      <c r="B96" t="str">
+        <v>SQ04612</v>
+      </c>
+      <c r="C96" t="str">
+        <v>Mick</v>
+      </c>
+      <c r="D96" t="str">
+        <v>Spraberry</v>
+      </c>
+      <c r="I96" s="30"/>
+    </row>
+    <row r="97" spans="2:9">
+      <c r="B97" t="str">
+        <v>TN01256</v>
+      </c>
+      <c r="C97" t="str">
+        <v>Shattesh</v>
+      </c>
+      <c r="D97" t="str">
+        <v>Utpat</v>
+      </c>
+      <c r="I97" s="30"/>
+    </row>
+    <row r="98" spans="2:9">
+      <c r="B98" t="str">
+        <v>TN01256</v>
+      </c>
+      <c r="C98" t="str">
+        <v>Sawini</v>
+      </c>
+      <c r="D98" t="str">
+        <v>Chandan</v>
+      </c>
+      <c r="I98" s="30"/>
+    </row>
+    <row r="99" spans="2:9">
+      <c r="B99" t="str">
+        <v>TN01601</v>
+      </c>
+      <c r="C99" t="str">
+        <v>Melva</v>
+      </c>
+      <c r="D99" t="str">
+        <v>Jickells</v>
+      </c>
+      <c r="I99" s="30"/>
+    </row>
+    <row r="100" spans="2:9">
+      <c r="B100" t="str">
+        <v>TN01601</v>
+      </c>
+      <c r="C100" t="str">
+        <v>Melva</v>
+      </c>
+      <c r="D100" t="str">
+        <v>Jickells</v>
+      </c>
+      <c r="I100" s="30"/>
+    </row>
+    <row r="101" spans="2:9">
+      <c r="B101" t="str">
+        <v>TN04892</v>
+      </c>
+      <c r="C101" t="str">
+        <v>Luca</v>
+      </c>
+      <c r="D101" t="str">
+        <v>Wolstenholme</v>
+      </c>
+      <c r="I101" s="30"/>
+    </row>
+    <row r="102" spans="2:9">
+      <c r="B102" t="str">
+        <v>VT01762</v>
+      </c>
+      <c r="C102" t="str">
+        <v>Geena</v>
+      </c>
+      <c r="D102" t="str">
+        <v>Raghavanpillai</v>
+      </c>
+      <c r="I102" s="30"/>
+    </row>
+    <row r="103" spans="2:9">
+      <c r="B103" t="str">
+        <v>VT01803</v>
+      </c>
+      <c r="C103" t="str">
+        <v>Freddy</v>
+      </c>
+      <c r="D103" t="str">
+        <v>Linford</v>
+      </c>
+      <c r="I103" s="30"/>
+    </row>
+    <row r="104" spans="2:9">
+      <c r="B104" t="str">
+        <v>VT02417</v>
+      </c>
+      <c r="C104" t="str">
+        <v>Evangelina</v>
+      </c>
+      <c r="D104" t="str">
+        <v>Lergan</v>
+      </c>
+      <c r="I104" s="30"/>
+    </row>
+    <row r="105" spans="2:9">
+      <c r="B105" t="str">
+        <v>VT03421</v>
+      </c>
+      <c r="C105" t="str">
+        <v>Alic</v>
+      </c>
+      <c r="D105" t="str">
+        <v>Bagg</v>
+      </c>
+      <c r="I105" s="30"/>
+    </row>
+    <row r="106" spans="2:9">
+      <c r="B106" t="str">
+        <v>VT03421</v>
+      </c>
+      <c r="C106" t="str">
+        <v>Alic</v>
+      </c>
+      <c r="D106" t="str">
+        <v>Bagg</v>
+      </c>
+      <c r="I106" s="30"/>
+    </row>
+    <row r="107" spans="2:9">
+      <c r="B107" t="str">
+        <v>VT03993</v>
+      </c>
+      <c r="C107" t="str">
+        <v>Dulce</v>
+      </c>
+      <c r="D107" t="str">
+        <v>Colbeck</v>
+      </c>
+      <c r="I107" s="30"/>
+    </row>
+    <row r="108" spans="2:9">
+      <c r="B108" t="str">
+        <v>VT04028</v>
+      </c>
+      <c r="C108" t="str">
+        <v>Michale</v>
+      </c>
+      <c r="D108" t="str">
+        <v>Rolf</v>
+      </c>
+      <c r="I108" s="30"/>
+    </row>
+    <row r="109" spans="2:9">
+      <c r="B109" t="str">
+        <v>VT04028</v>
+      </c>
+      <c r="C109" t="str">
+        <v>Michale</v>
+      </c>
+      <c r="D109" t="str">
+        <v>Rolf</v>
+      </c>
+      <c r="I109" s="30"/>
+    </row>
+    <row r="110" spans="2:9">
+      <c r="B110" t="str">
+        <v>VT04415</v>
+      </c>
+      <c r="C110" t="str">
+        <v>Malory</v>
+      </c>
+      <c r="D110" t="str">
+        <v>Biles</v>
+      </c>
+      <c r="I110" s="30"/>
+    </row>
+    <row r="111" spans="2:9">
+      <c r="I111" s="30"/>
+    </row>
+    <row r="114" spans="2:4">
+      <c r="B114" s="28" t="str" cm="1">
+        <f t="array" ref="B114:D114">_xlfn.CHOOSECOLS(staff[#Headers],1,2,8)</f>
+        <v>Emp ID</v>
+      </c>
+      <c r="C114" s="28" t="str">
+        <v>First Name</v>
+      </c>
+      <c r="D114" s="28" t="str">
+        <v>Start Date</v>
+      </c>
+    </row>
+    <row r="115" spans="2:4">
+      <c r="B115" t="str" cm="1">
+        <f t="array" ref="B115:D136">_xlfn._xlws.FILTER(_xlfn.CHOOSECOLS(staff[],1,2,8),MONTH(staff[Start Date])=3)</f>
+        <v>PR00746</v>
+      </c>
+      <c r="C115" t="str">
+        <v>Hogan</v>
+      </c>
+      <c r="D115" s="30">
+        <v>43908</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4">
+      <c r="B116" t="str">
+        <v>PR00893</v>
+      </c>
+      <c r="C116" t="str">
+        <v>Vasavi</v>
+      </c>
+      <c r="D116" s="30">
+        <v>44285</v>
+      </c>
+    </row>
+    <row r="117" spans="2:4">
+      <c r="B117" t="str">
+        <v>SQ00022</v>
+      </c>
+      <c r="C117" t="str">
+        <v>Carlin</v>
+      </c>
+      <c r="D117" s="30">
+        <v>43914</v>
+      </c>
+    </row>
+    <row r="118" spans="2:4">
+      <c r="B118" t="str">
+        <v>SQ00105</v>
+      </c>
+      <c r="C118" t="str">
+        <v>Sarayu</v>
+      </c>
+      <c r="D118" s="30">
+        <v>43164</v>
+      </c>
+    </row>
+    <row r="119" spans="2:4">
+      <c r="B119" t="str">
+        <v>SQ01519</v>
+      </c>
+      <c r="C119" t="str">
+        <v>Caron</v>
+      </c>
+      <c r="D119" s="30">
+        <v>43550</v>
+      </c>
+    </row>
+    <row r="120" spans="2:4">
+      <c r="B120" t="str">
+        <v>SQ03112</v>
+      </c>
+      <c r="C120" t="str">
+        <v>Kantimoy</v>
+      </c>
+      <c r="D120" s="30">
+        <v>43920</v>
+      </c>
+    </row>
+    <row r="121" spans="2:4">
+      <c r="B121" t="str">
+        <v>SQ03625</v>
+      </c>
+      <c r="C121" t="str">
+        <v>Fidela</v>
+      </c>
+      <c r="D121" s="30">
+        <v>43899</v>
+      </c>
+    </row>
+    <row r="122" spans="2:4">
+      <c r="B122" t="str">
+        <v>SQ04612</v>
+      </c>
+      <c r="C122" t="str">
+        <v>Mick</v>
+      </c>
+      <c r="D122" s="30">
+        <v>43902</v>
+      </c>
+    </row>
+    <row r="123" spans="2:4">
+      <c r="B123" t="str">
+        <v>TN01256</v>
+      </c>
+      <c r="C123" t="str">
+        <v>Shattesh</v>
+      </c>
+      <c r="D123" s="30">
+        <v>43916</v>
+      </c>
+    </row>
+    <row r="124" spans="2:4">
+      <c r="B124" t="str">
+        <v>TN01256</v>
+      </c>
+      <c r="C124" t="str">
+        <v>Sawini</v>
+      </c>
+      <c r="D124" s="30">
+        <v>43916</v>
+      </c>
+    </row>
+    <row r="125" spans="2:4">
+      <c r="B125" t="str">
+        <v>TN01601</v>
+      </c>
+      <c r="C125" t="str">
+        <v>Melva</v>
+      </c>
+      <c r="D125" s="30">
+        <v>44277</v>
+      </c>
+    </row>
+    <row r="126" spans="2:4">
+      <c r="B126" t="str">
+        <v>TN01601</v>
+      </c>
+      <c r="C126" t="str">
+        <v>Melva</v>
+      </c>
+      <c r="D126" s="30">
+        <v>44277</v>
+      </c>
+    </row>
+    <row r="127" spans="2:4">
+      <c r="B127" t="str">
+        <v>TN04892</v>
+      </c>
+      <c r="C127" t="str">
+        <v>Luca</v>
+      </c>
+      <c r="D127" s="30">
+        <v>43180</v>
+      </c>
+    </row>
+    <row r="128" spans="2:4">
+      <c r="B128" t="str">
+        <v>VT01762</v>
+      </c>
+      <c r="C128" t="str">
+        <v>Geena</v>
+      </c>
+      <c r="D128" s="30">
+        <v>43902</v>
+      </c>
+    </row>
+    <row r="129" spans="2:4">
+      <c r="B129" t="str">
+        <v>VT01803</v>
+      </c>
+      <c r="C129" t="str">
+        <v>Freddy</v>
+      </c>
+      <c r="D129" s="30">
+        <v>43164</v>
+      </c>
+    </row>
+    <row r="130" spans="2:4">
+      <c r="B130" t="str">
+        <v>VT02417</v>
+      </c>
+      <c r="C130" t="str">
+        <v>Evangelina</v>
+      </c>
+      <c r="D130" s="30">
+        <v>43171</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4">
+      <c r="B131" t="str">
+        <v>VT03421</v>
+      </c>
+      <c r="C131" t="str">
+        <v>Alic</v>
+      </c>
+      <c r="D131" s="30">
+        <v>44270</v>
+      </c>
+    </row>
+    <row r="132" spans="2:4">
+      <c r="B132" t="str">
+        <v>VT03421</v>
+      </c>
+      <c r="C132" t="str">
+        <v>Alic</v>
+      </c>
+      <c r="D132" s="30">
+        <v>44270</v>
+      </c>
+    </row>
+    <row r="133" spans="2:4">
+      <c r="B133" t="str">
+        <v>VT03993</v>
+      </c>
+      <c r="C133" t="str">
+        <v>Dulce</v>
+      </c>
+      <c r="D133" s="30">
+        <v>44285</v>
+      </c>
+    </row>
+    <row r="134" spans="2:4">
+      <c r="B134" t="str">
+        <v>VT04028</v>
+      </c>
+      <c r="C134" t="str">
+        <v>Michale</v>
+      </c>
+      <c r="D134" s="30">
+        <v>43895</v>
+      </c>
+    </row>
+    <row r="135" spans="2:4">
+      <c r="B135" t="str">
+        <v>VT04028</v>
+      </c>
+      <c r="C135" t="str">
+        <v>Michale</v>
+      </c>
+      <c r="D135" s="30">
+        <v>43895</v>
+      </c>
+    </row>
+    <row r="136" spans="2:4">
+      <c r="B136" t="str">
+        <v>VT04415</v>
+      </c>
+      <c r="C136" t="str">
+        <v>Malory</v>
+      </c>
+      <c r="D136" s="30">
+        <v>43171</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE182796-6443-4558-9B87-909B73329DFC}">
   <dimension ref="A1:O267"/>
@@ -4616,7 +8471,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" hidden="1">
       <c r="C8" t="s">
         <v>42</v>
       </c>
@@ -4657,7 +8512,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" hidden="1">
       <c r="C9" t="s">
         <v>51</v>
       </c>
@@ -4780,7 +8635,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" hidden="1">
       <c r="C12" t="s">
         <v>61</v>
       </c>
@@ -4821,7 +8676,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" hidden="1">
       <c r="C13" t="s">
         <v>68</v>
       </c>
@@ -4862,7 +8717,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" hidden="1">
       <c r="C14" t="s">
         <v>72</v>
       </c>
@@ -4903,7 +8758,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" hidden="1">
       <c r="C15" t="s">
         <v>75</v>
       </c>
@@ -4944,7 +8799,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:15" hidden="1">
       <c r="C16" t="s">
         <v>79</v>
       </c>
@@ -4985,7 +8840,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="3:15">
+    <row r="17" spans="3:15" hidden="1">
       <c r="C17" t="s">
         <v>83</v>
       </c>
@@ -5026,7 +8881,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="3:15">
+    <row r="18" spans="3:15" hidden="1">
       <c r="C18" t="s">
         <v>87</v>
       </c>
@@ -5067,7 +8922,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="3:15">
+    <row r="19" spans="3:15" hidden="1">
       <c r="C19" t="s">
         <v>90</v>
       </c>
@@ -5108,7 +8963,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:15">
+    <row r="20" spans="3:15" hidden="1">
       <c r="C20" t="s">
         <v>94</v>
       </c>
@@ -5149,7 +9004,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="3:15">
+    <row r="21" spans="3:15" hidden="1">
       <c r="C21" t="s">
         <v>98</v>
       </c>
@@ -5190,7 +9045,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:15">
+    <row r="22" spans="3:15" hidden="1">
       <c r="C22" t="s">
         <v>102</v>
       </c>
@@ -5231,7 +9086,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="3:15">
+    <row r="23" spans="3:15" hidden="1">
       <c r="C23" t="s">
         <v>106</v>
       </c>
@@ -5272,7 +9127,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="3:15">
+    <row r="24" spans="3:15" hidden="1">
       <c r="C24" t="s">
         <v>110</v>
       </c>
@@ -5313,7 +9168,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="3:15">
+    <row r="25" spans="3:15" hidden="1">
       <c r="C25" t="s">
         <v>113</v>
       </c>
@@ -5354,7 +9209,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="3:15">
+    <row r="26" spans="3:15" hidden="1">
       <c r="C26" t="s">
         <v>117</v>
       </c>
@@ -5395,7 +9250,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="27" spans="3:15">
+    <row r="27" spans="3:15" hidden="1">
       <c r="C27" t="s">
         <v>120</v>
       </c>
@@ -5436,7 +9291,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="3:15">
+    <row r="28" spans="3:15" hidden="1">
       <c r="C28" t="s">
         <v>124</v>
       </c>
@@ -5477,7 +9332,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="3:15">
+    <row r="29" spans="3:15" hidden="1">
       <c r="C29" t="s">
         <v>127</v>
       </c>
@@ -5518,7 +9373,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="3:15">
+    <row r="30" spans="3:15" hidden="1">
       <c r="C30" t="s">
         <v>130</v>
       </c>
@@ -5559,7 +9414,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="31" spans="3:15">
+    <row r="31" spans="3:15" hidden="1">
       <c r="C31" t="s">
         <v>133</v>
       </c>
@@ -5600,7 +9455,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="32" spans="3:15">
+    <row r="32" spans="3:15" hidden="1">
       <c r="C32" t="s">
         <v>133</v>
       </c>
@@ -5641,7 +9496,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="33" spans="3:15">
+    <row r="33" spans="3:15" hidden="1">
       <c r="C33" t="s">
         <v>136</v>
       </c>
@@ -5682,7 +9537,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="34" spans="3:15">
+    <row r="34" spans="3:15" hidden="1">
       <c r="C34" t="s">
         <v>139</v>
       </c>
@@ -5723,7 +9578,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="35" spans="3:15">
+    <row r="35" spans="3:15" hidden="1">
       <c r="C35" t="s">
         <v>142</v>
       </c>
@@ -5764,7 +9619,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="36" spans="3:15">
+    <row r="36" spans="3:15" hidden="1">
       <c r="C36" t="s">
         <v>146</v>
       </c>
@@ -5805,7 +9660,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="3:15">
+    <row r="37" spans="3:15" hidden="1">
       <c r="C37" t="s">
         <v>149</v>
       </c>
@@ -5846,7 +9701,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="38" spans="3:15">
+    <row r="38" spans="3:15" hidden="1">
       <c r="C38" t="s">
         <v>152</v>
       </c>
@@ -5887,7 +9742,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="39" spans="3:15">
+    <row r="39" spans="3:15" hidden="1">
       <c r="C39" t="s">
         <v>156</v>
       </c>
@@ -5928,7 +9783,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="40" spans="3:15">
+    <row r="40" spans="3:15" hidden="1">
       <c r="C40" t="s">
         <v>159</v>
       </c>
@@ -5969,7 +9824,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="41" spans="3:15">
+    <row r="41" spans="3:15" hidden="1">
       <c r="C41" t="s">
         <v>162</v>
       </c>
@@ -6010,7 +9865,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="3:15">
+    <row r="42" spans="3:15" hidden="1">
       <c r="C42" t="s">
         <v>165</v>
       </c>
@@ -6051,7 +9906,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="3:15">
+    <row r="43" spans="3:15" hidden="1">
       <c r="C43" t="s">
         <v>168</v>
       </c>
@@ -6092,7 +9947,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="44" spans="3:15">
+    <row r="44" spans="3:15" hidden="1">
       <c r="C44" t="s">
         <v>171</v>
       </c>
@@ -6133,7 +9988,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="45" spans="3:15">
+    <row r="45" spans="3:15" hidden="1">
       <c r="C45" t="s">
         <v>174</v>
       </c>
@@ -6174,7 +10029,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="46" spans="3:15">
+    <row r="46" spans="3:15" hidden="1">
       <c r="C46" t="s">
         <v>177</v>
       </c>
@@ -6215,7 +10070,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="47" spans="3:15">
+    <row r="47" spans="3:15" hidden="1">
       <c r="C47" t="s">
         <v>180</v>
       </c>
@@ -6256,7 +10111,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="48" spans="3:15">
+    <row r="48" spans="3:15" hidden="1">
       <c r="C48" t="s">
         <v>183</v>
       </c>
@@ -6297,7 +10152,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="49" spans="3:15">
+    <row r="49" spans="3:15" hidden="1">
       <c r="C49" t="s">
         <v>186</v>
       </c>
@@ -6338,7 +10193,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="50" spans="3:15">
+    <row r="50" spans="3:15" hidden="1">
       <c r="C50" t="s">
         <v>189</v>
       </c>
@@ -6379,7 +10234,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="51" spans="3:15">
+    <row r="51" spans="3:15" hidden="1">
       <c r="C51" t="s">
         <v>192</v>
       </c>
@@ -6420,7 +10275,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="52" spans="3:15">
+    <row r="52" spans="3:15" hidden="1">
       <c r="C52" t="s">
         <v>192</v>
       </c>
@@ -6461,7 +10316,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="53" spans="3:15">
+    <row r="53" spans="3:15" hidden="1">
       <c r="C53" t="s">
         <v>197</v>
       </c>
@@ -6502,7 +10357,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="54" spans="3:15">
+    <row r="54" spans="3:15" hidden="1">
       <c r="C54" t="s">
         <v>200</v>
       </c>
@@ -6543,7 +10398,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="3:15">
+    <row r="55" spans="3:15" hidden="1">
       <c r="C55" t="s">
         <v>203</v>
       </c>
@@ -6584,7 +10439,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="56" spans="3:15">
+    <row r="56" spans="3:15" hidden="1">
       <c r="C56" t="s">
         <v>206</v>
       </c>
@@ -6666,7 +10521,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="58" spans="3:15">
+    <row r="58" spans="3:15" hidden="1">
       <c r="C58" t="s">
         <v>210</v>
       </c>
@@ -6707,7 +10562,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="59" spans="3:15">
+    <row r="59" spans="3:15" hidden="1">
       <c r="C59" t="s">
         <v>213</v>
       </c>
@@ -6748,7 +10603,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="60" spans="3:15">
+    <row r="60" spans="3:15" hidden="1">
       <c r="C60" t="s">
         <v>216</v>
       </c>
@@ -6789,7 +10644,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="61" spans="3:15">
+    <row r="61" spans="3:15" hidden="1">
       <c r="C61" t="s">
         <v>220</v>
       </c>
@@ -6830,7 +10685,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="62" spans="3:15">
+    <row r="62" spans="3:15" hidden="1">
       <c r="C62" t="s">
         <v>223</v>
       </c>
@@ -6871,7 +10726,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="63" spans="3:15">
+    <row r="63" spans="3:15" hidden="1">
       <c r="C63" t="s">
         <v>226</v>
       </c>
@@ -6912,7 +10767,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="64" spans="3:15">
+    <row r="64" spans="3:15" hidden="1">
       <c r="C64" t="s">
         <v>229</v>
       </c>
@@ -6953,7 +10808,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="65" spans="3:15">
+    <row r="65" spans="3:15" hidden="1">
       <c r="C65" t="s">
         <v>232</v>
       </c>
@@ -6994,7 +10849,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="66" spans="3:15">
+    <row r="66" spans="3:15" hidden="1">
       <c r="C66" t="s">
         <v>235</v>
       </c>
@@ -7035,7 +10890,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="67" spans="3:15">
+    <row r="67" spans="3:15" hidden="1">
       <c r="C67" t="s">
         <v>238</v>
       </c>
@@ -7076,7 +10931,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="68" spans="3:15">
+    <row r="68" spans="3:15" hidden="1">
       <c r="C68" t="s">
         <v>241</v>
       </c>
@@ -7117,7 +10972,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="69" spans="3:15">
+    <row r="69" spans="3:15" hidden="1">
       <c r="C69" t="s">
         <v>244</v>
       </c>
@@ -7158,7 +11013,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="70" spans="3:15">
+    <row r="70" spans="3:15" hidden="1">
       <c r="C70" t="s">
         <v>247</v>
       </c>
@@ -7199,7 +11054,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="71" spans="3:15">
+    <row r="71" spans="3:15" hidden="1">
       <c r="C71" t="s">
         <v>248</v>
       </c>
@@ -7240,7 +11095,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="72" spans="3:15">
+    <row r="72" spans="3:15" hidden="1">
       <c r="C72" t="s">
         <v>251</v>
       </c>
@@ -7281,7 +11136,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="73" spans="3:15">
+    <row r="73" spans="3:15" hidden="1">
       <c r="C73" t="s">
         <v>254</v>
       </c>
@@ -7322,7 +11177,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="74" spans="3:15">
+    <row r="74" spans="3:15" hidden="1">
       <c r="C74" t="s">
         <v>257</v>
       </c>
@@ -7363,7 +11218,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="75" spans="3:15">
+    <row r="75" spans="3:15" hidden="1">
       <c r="C75" t="s">
         <v>260</v>
       </c>
@@ -7404,7 +11259,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="76" spans="3:15">
+    <row r="76" spans="3:15" hidden="1">
       <c r="C76" t="s">
         <v>260</v>
       </c>
@@ -7445,7 +11300,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="77" spans="3:15">
+    <row r="77" spans="3:15" hidden="1">
       <c r="C77" t="s">
         <v>265</v>
       </c>
@@ -7486,7 +11341,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="78" spans="3:15">
+    <row r="78" spans="3:15" hidden="1">
       <c r="C78" t="s">
         <v>268</v>
       </c>
@@ -7527,7 +11382,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="79" spans="3:15">
+    <row r="79" spans="3:15" hidden="1">
       <c r="C79" t="s">
         <v>271</v>
       </c>
@@ -7568,7 +11423,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="80" spans="3:15">
+    <row r="80" spans="3:15" hidden="1">
       <c r="C80" t="s">
         <v>274</v>
       </c>
@@ -7609,7 +11464,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="81" spans="3:15">
+    <row r="81" spans="3:15" hidden="1">
       <c r="C81" t="s">
         <v>277</v>
       </c>
@@ -7650,7 +11505,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="82" spans="3:15">
+    <row r="82" spans="3:15" hidden="1">
       <c r="C82" t="s">
         <v>280</v>
       </c>
@@ -7691,7 +11546,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="83" spans="3:15">
+    <row r="83" spans="3:15" hidden="1">
       <c r="C83" t="s">
         <v>283</v>
       </c>
@@ -7732,7 +11587,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="84" spans="3:15">
+    <row r="84" spans="3:15" hidden="1">
       <c r="C84" t="s">
         <v>286</v>
       </c>
@@ -7773,7 +11628,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="85" spans="3:15">
+    <row r="85" spans="3:15" hidden="1">
       <c r="C85" t="s">
         <v>289</v>
       </c>
@@ -7814,7 +11669,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="86" spans="3:15">
+    <row r="86" spans="3:15" hidden="1">
       <c r="C86" t="s">
         <v>292</v>
       </c>
@@ -7855,7 +11710,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="87" spans="3:15">
+    <row r="87" spans="3:15" hidden="1">
       <c r="C87" t="s">
         <v>295</v>
       </c>
@@ -7896,7 +11751,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="88" spans="3:15">
+    <row r="88" spans="3:15" hidden="1">
       <c r="C88" t="s">
         <v>298</v>
       </c>
@@ -7937,7 +11792,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="89" spans="3:15">
+    <row r="89" spans="3:15" hidden="1">
       <c r="C89" t="s">
         <v>301</v>
       </c>
@@ -7978,7 +11833,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="90" spans="3:15">
+    <row r="90" spans="3:15" hidden="1">
       <c r="C90" t="s">
         <v>304</v>
       </c>
@@ -8019,7 +11874,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="91" spans="3:15">
+    <row r="91" spans="3:15" hidden="1">
       <c r="C91" t="s">
         <v>304</v>
       </c>
@@ -8060,7 +11915,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="92" spans="3:15">
+    <row r="92" spans="3:15" hidden="1">
       <c r="C92" t="s">
         <v>309</v>
       </c>
@@ -8101,7 +11956,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="93" spans="3:15">
+    <row r="93" spans="3:15" hidden="1">
       <c r="C93" t="s">
         <v>309</v>
       </c>
@@ -8142,7 +11997,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="94" spans="3:15">
+    <row r="94" spans="3:15" hidden="1">
       <c r="C94" t="s">
         <v>312</v>
       </c>
@@ -8183,7 +12038,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="95" spans="3:15">
+    <row r="95" spans="3:15" hidden="1">
       <c r="C95" t="s">
         <v>315</v>
       </c>
@@ -8224,7 +12079,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="96" spans="3:15">
+    <row r="96" spans="3:15" hidden="1">
       <c r="C96" t="s">
         <v>318</v>
       </c>
@@ -8265,7 +12120,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="97" spans="3:15">
+    <row r="97" spans="3:15" hidden="1">
       <c r="C97" t="s">
         <v>321</v>
       </c>
@@ -8306,7 +12161,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="98" spans="3:15">
+    <row r="98" spans="3:15" hidden="1">
       <c r="C98" t="s">
         <v>324</v>
       </c>
@@ -8347,7 +12202,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="99" spans="3:15">
+    <row r="99" spans="3:15" hidden="1">
       <c r="C99" t="s">
         <v>327</v>
       </c>
@@ -8388,7 +12243,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="100" spans="3:15">
+    <row r="100" spans="3:15" hidden="1">
       <c r="C100" t="s">
         <v>330</v>
       </c>
@@ -8429,7 +12284,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="101" spans="3:15">
+    <row r="101" spans="3:15" hidden="1">
       <c r="C101" t="s">
         <v>333</v>
       </c>
@@ -8470,7 +12325,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="102" spans="3:15">
+    <row r="102" spans="3:15" hidden="1">
       <c r="C102" t="s">
         <v>333</v>
       </c>
@@ -8511,7 +12366,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="103" spans="3:15">
+    <row r="103" spans="3:15" hidden="1">
       <c r="C103" t="s">
         <v>336</v>
       </c>
@@ -8552,7 +12407,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="104" spans="3:15">
+    <row r="104" spans="3:15" hidden="1">
       <c r="C104" t="s">
         <v>339</v>
       </c>
@@ -8593,7 +12448,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="105" spans="3:15">
+    <row r="105" spans="3:15" hidden="1">
       <c r="C105" t="s">
         <v>342</v>
       </c>
@@ -8634,7 +12489,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="106" spans="3:15">
+    <row r="106" spans="3:15" hidden="1">
       <c r="C106" t="s">
         <v>345</v>
       </c>
@@ -8675,7 +12530,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="107" spans="3:15">
+    <row r="107" spans="3:15" hidden="1">
       <c r="C107" t="s">
         <v>348</v>
       </c>
@@ -8716,7 +12571,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="108" spans="3:15">
+    <row r="108" spans="3:15" hidden="1">
       <c r="C108" t="s">
         <v>351</v>
       </c>
@@ -8757,7 +12612,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="109" spans="3:15">
+    <row r="109" spans="3:15" hidden="1">
       <c r="C109" t="s">
         <v>354</v>
       </c>
@@ -8798,7 +12653,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="110" spans="3:15">
+    <row r="110" spans="3:15" hidden="1">
       <c r="C110" t="s">
         <v>354</v>
       </c>
@@ -8839,7 +12694,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="111" spans="3:15">
+    <row r="111" spans="3:15" hidden="1">
       <c r="C111" t="s">
         <v>357</v>
       </c>
@@ -8880,7 +12735,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="112" spans="3:15">
+    <row r="112" spans="3:15" hidden="1">
       <c r="C112" t="s">
         <v>360</v>
       </c>
@@ -8921,7 +12776,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="113" spans="3:15">
+    <row r="113" spans="3:15" hidden="1">
       <c r="C113" t="s">
         <v>363</v>
       </c>
@@ -8962,7 +12817,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="114" spans="3:15">
+    <row r="114" spans="3:15" hidden="1">
       <c r="C114" t="s">
         <v>366</v>
       </c>
@@ -9003,7 +12858,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="115" spans="3:15">
+    <row r="115" spans="3:15" hidden="1">
       <c r="C115" t="s">
         <v>366</v>
       </c>
@@ -9044,7 +12899,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="116" spans="3:15">
+    <row r="116" spans="3:15" hidden="1">
       <c r="C116" t="s">
         <v>369</v>
       </c>
@@ -9085,7 +12940,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="117" spans="3:15">
+    <row r="117" spans="3:15" hidden="1">
       <c r="C117" t="s">
         <v>372</v>
       </c>
@@ -9126,7 +12981,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="118" spans="3:15">
+    <row r="118" spans="3:15" hidden="1">
       <c r="C118" t="s">
         <v>375</v>
       </c>
@@ -9167,7 +13022,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="119" spans="3:15">
+    <row r="119" spans="3:15" hidden="1">
       <c r="C119" t="s">
         <v>378</v>
       </c>
@@ -9208,7 +13063,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="120" spans="3:15">
+    <row r="120" spans="3:15" hidden="1">
       <c r="C120" t="s">
         <v>381</v>
       </c>
@@ -9249,7 +13104,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="121" spans="3:15">
+    <row r="121" spans="3:15" hidden="1">
       <c r="C121" t="s">
         <v>384</v>
       </c>
@@ -9290,7 +13145,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="122" spans="3:15">
+    <row r="122" spans="3:15" hidden="1">
       <c r="C122" t="s">
         <v>387</v>
       </c>
@@ -9331,7 +13186,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="123" spans="3:15">
+    <row r="123" spans="3:15" hidden="1">
       <c r="C123" t="s">
         <v>390</v>
       </c>
@@ -9372,7 +13227,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="124" spans="3:15">
+    <row r="124" spans="3:15" hidden="1">
       <c r="C124" t="s">
         <v>393</v>
       </c>
@@ -9413,7 +13268,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="125" spans="3:15">
+    <row r="125" spans="3:15" hidden="1">
       <c r="C125" t="s">
         <v>396</v>
       </c>
@@ -9454,7 +13309,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="126" spans="3:15">
+    <row r="126" spans="3:15" hidden="1">
       <c r="C126" t="s">
         <v>399</v>
       </c>
@@ -9495,7 +13350,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="127" spans="3:15">
+    <row r="127" spans="3:15" hidden="1">
       <c r="C127" t="s">
         <v>402</v>
       </c>
@@ -9536,7 +13391,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="128" spans="3:15">
+    <row r="128" spans="3:15" hidden="1">
       <c r="C128" t="s">
         <v>405</v>
       </c>
@@ -9577,7 +13432,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="129" spans="3:15">
+    <row r="129" spans="3:15" hidden="1">
       <c r="C129" t="s">
         <v>408</v>
       </c>
@@ -9618,7 +13473,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="130" spans="3:15">
+    <row r="130" spans="3:15" hidden="1">
       <c r="C130" t="s">
         <v>411</v>
       </c>
@@ -9659,7 +13514,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="131" spans="3:15">
+    <row r="131" spans="3:15" hidden="1">
       <c r="C131" t="s">
         <v>414</v>
       </c>
@@ -9700,7 +13555,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="132" spans="3:15">
+    <row r="132" spans="3:15" hidden="1">
       <c r="C132" t="s">
         <v>417</v>
       </c>
@@ -9741,7 +13596,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="133" spans="3:15">
+    <row r="133" spans="3:15" hidden="1">
       <c r="C133" t="s">
         <v>420</v>
       </c>
@@ -9782,7 +13637,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="134" spans="3:15">
+    <row r="134" spans="3:15" hidden="1">
       <c r="C134" t="s">
         <v>420</v>
       </c>
@@ -9823,7 +13678,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="135" spans="3:15">
+    <row r="135" spans="3:15" hidden="1">
       <c r="C135" t="s">
         <v>425</v>
       </c>
@@ -9864,7 +13719,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="136" spans="3:15">
+    <row r="136" spans="3:15" hidden="1">
       <c r="C136" t="s">
         <v>428</v>
       </c>
@@ -9905,7 +13760,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="137" spans="3:15">
+    <row r="137" spans="3:15" hidden="1">
       <c r="C137" t="s">
         <v>431</v>
       </c>
@@ -9946,7 +13801,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="138" spans="3:15">
+    <row r="138" spans="3:15" hidden="1">
       <c r="C138" t="s">
         <v>434</v>
       </c>
@@ -9987,7 +13842,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="139" spans="3:15">
+    <row r="139" spans="3:15" hidden="1">
       <c r="C139" t="s">
         <v>437</v>
       </c>
@@ -10028,7 +13883,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="140" spans="3:15">
+    <row r="140" spans="3:15" hidden="1">
       <c r="C140" t="s">
         <v>440</v>
       </c>
@@ -10069,7 +13924,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="141" spans="3:15">
+    <row r="141" spans="3:15" hidden="1">
       <c r="C141" t="s">
         <v>443</v>
       </c>
@@ -10110,7 +13965,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="142" spans="3:15">
+    <row r="142" spans="3:15" hidden="1">
       <c r="C142" t="s">
         <v>446</v>
       </c>
@@ -10151,7 +14006,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="143" spans="3:15">
+    <row r="143" spans="3:15" hidden="1">
       <c r="C143" t="s">
         <v>446</v>
       </c>
@@ -10192,7 +14047,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="144" spans="3:15">
+    <row r="144" spans="3:15" hidden="1">
       <c r="C144" t="s">
         <v>449</v>
       </c>
@@ -10233,7 +14088,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="145" spans="3:15">
+    <row r="145" spans="3:15" hidden="1">
       <c r="C145" t="s">
         <v>452</v>
       </c>
@@ -10274,7 +14129,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="146" spans="3:15">
+    <row r="146" spans="3:15" hidden="1">
       <c r="C146" t="s">
         <v>455</v>
       </c>
@@ -10315,7 +14170,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="147" spans="3:15">
+    <row r="147" spans="3:15" hidden="1">
       <c r="C147" t="s">
         <v>458</v>
       </c>
@@ -10356,7 +14211,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="148" spans="3:15">
+    <row r="148" spans="3:15" hidden="1">
       <c r="C148" t="s">
         <v>458</v>
       </c>
@@ -10397,7 +14252,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="149" spans="3:15">
+    <row r="149" spans="3:15" hidden="1">
       <c r="C149" t="s">
         <v>463</v>
       </c>
@@ -10438,7 +14293,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="150" spans="3:15">
+    <row r="150" spans="3:15" hidden="1">
       <c r="C150" t="s">
         <v>466</v>
       </c>
@@ -10479,7 +14334,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="151" spans="3:15">
+    <row r="151" spans="3:15" hidden="1">
       <c r="C151" t="s">
         <v>469</v>
       </c>
@@ -10520,7 +14375,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="152" spans="3:15">
+    <row r="152" spans="3:15" hidden="1">
       <c r="C152" t="s">
         <v>472</v>
       </c>
@@ -10561,7 +14416,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="153" spans="3:15">
+    <row r="153" spans="3:15" hidden="1">
       <c r="C153" t="s">
         <v>475</v>
       </c>
@@ -10602,7 +14457,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="154" spans="3:15">
+    <row r="154" spans="3:15" hidden="1">
       <c r="C154" t="s">
         <v>475</v>
       </c>
@@ -10643,7 +14498,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="155" spans="3:15">
+    <row r="155" spans="3:15" hidden="1">
       <c r="C155" t="s">
         <v>478</v>
       </c>
@@ -10684,7 +14539,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="156" spans="3:15">
+    <row r="156" spans="3:15" hidden="1">
       <c r="C156" t="s">
         <v>481</v>
       </c>
@@ -10725,7 +14580,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="157" spans="3:15">
+    <row r="157" spans="3:15" hidden="1">
       <c r="C157" t="s">
         <v>484</v>
       </c>
@@ -10766,7 +14621,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="158" spans="3:15">
+    <row r="158" spans="3:15" hidden="1">
       <c r="C158" t="s">
         <v>484</v>
       </c>
@@ -10807,7 +14662,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="159" spans="3:15">
+    <row r="159" spans="3:15" hidden="1">
       <c r="C159" t="s">
         <v>487</v>
       </c>
@@ -10848,7 +14703,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="160" spans="3:15">
+    <row r="160" spans="3:15" hidden="1">
       <c r="C160" t="s">
         <v>490</v>
       </c>
@@ -10889,7 +14744,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="161" spans="3:15">
+    <row r="161" spans="3:15" hidden="1">
       <c r="C161" t="s">
         <v>491</v>
       </c>
@@ -10930,7 +14785,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="162" spans="3:15">
+    <row r="162" spans="3:15" hidden="1">
       <c r="C162" t="s">
         <v>494</v>
       </c>
@@ -10971,7 +14826,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="163" spans="3:15">
+    <row r="163" spans="3:15" hidden="1">
       <c r="C163" t="s">
         <v>497</v>
       </c>
@@ -11012,7 +14867,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="164" spans="3:15">
+    <row r="164" spans="3:15" hidden="1">
       <c r="C164" t="s">
         <v>500</v>
       </c>
@@ -11053,7 +14908,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="165" spans="3:15">
+    <row r="165" spans="3:15" hidden="1">
       <c r="C165" t="s">
         <v>503</v>
       </c>
@@ -11094,7 +14949,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="166" spans="3:15">
+    <row r="166" spans="3:15" hidden="1">
       <c r="C166" t="s">
         <v>503</v>
       </c>
@@ -11135,7 +14990,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="167" spans="3:15">
+    <row r="167" spans="3:15" hidden="1">
       <c r="C167" t="s">
         <v>506</v>
       </c>
@@ -11176,7 +15031,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="168" spans="3:15">
+    <row r="168" spans="3:15" hidden="1">
       <c r="C168" t="s">
         <v>506</v>
       </c>
@@ -11217,7 +15072,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="169" spans="3:15">
+    <row r="169" spans="3:15" hidden="1">
       <c r="C169" t="s">
         <v>509</v>
       </c>
@@ -11258,7 +15113,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="170" spans="3:15">
+    <row r="170" spans="3:15" hidden="1">
       <c r="C170" t="s">
         <v>512</v>
       </c>
@@ -11299,7 +15154,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="171" spans="3:15">
+    <row r="171" spans="3:15" hidden="1">
       <c r="C171" t="s">
         <v>515</v>
       </c>
@@ -11340,7 +15195,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="172" spans="3:15">
+    <row r="172" spans="3:15" hidden="1">
       <c r="C172" t="s">
         <v>518</v>
       </c>
@@ -11381,7 +15236,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="173" spans="3:15">
+    <row r="173" spans="3:15" hidden="1">
       <c r="C173" t="s">
         <v>521</v>
       </c>
@@ -11422,7 +15277,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="174" spans="3:15">
+    <row r="174" spans="3:15" hidden="1">
       <c r="C174" t="s">
         <v>524</v>
       </c>
@@ -11463,7 +15318,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="175" spans="3:15">
+    <row r="175" spans="3:15" hidden="1">
       <c r="C175" t="s">
         <v>524</v>
       </c>
@@ -11504,7 +15359,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="176" spans="3:15">
+    <row r="176" spans="3:15" hidden="1">
       <c r="C176" t="s">
         <v>528</v>
       </c>
@@ -11545,7 +15400,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="177" spans="3:15">
+    <row r="177" spans="3:15" hidden="1">
       <c r="C177" t="s">
         <v>532</v>
       </c>
@@ -11586,7 +15441,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="178" spans="3:15">
+    <row r="178" spans="3:15" hidden="1">
       <c r="C178" t="s">
         <v>535</v>
       </c>
@@ -11627,7 +15482,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="179" spans="3:15">
+    <row r="179" spans="3:15" hidden="1">
       <c r="C179" t="s">
         <v>535</v>
       </c>
@@ -11668,7 +15523,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="180" spans="3:15">
+    <row r="180" spans="3:15" hidden="1">
       <c r="C180" t="s">
         <v>538</v>
       </c>
@@ -11709,7 +15564,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="181" spans="3:15">
+    <row r="181" spans="3:15" hidden="1">
       <c r="C181" t="s">
         <v>541</v>
       </c>
@@ -11750,7 +15605,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="182" spans="3:15">
+    <row r="182" spans="3:15" hidden="1">
       <c r="C182" t="s">
         <v>542</v>
       </c>
@@ -11791,7 +15646,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="183" spans="3:15">
+    <row r="183" spans="3:15" hidden="1">
       <c r="C183" t="s">
         <v>545</v>
       </c>
@@ -11832,7 +15687,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="184" spans="3:15">
+    <row r="184" spans="3:15" hidden="1">
       <c r="C184" t="s">
         <v>548</v>
       </c>
@@ -11873,7 +15728,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="185" spans="3:15">
+    <row r="185" spans="3:15" hidden="1">
       <c r="C185" t="s">
         <v>548</v>
       </c>
@@ -11914,7 +15769,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="186" spans="3:15">
+    <row r="186" spans="3:15" hidden="1">
       <c r="C186" t="s">
         <v>551</v>
       </c>
@@ -11955,7 +15810,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="187" spans="3:15">
+    <row r="187" spans="3:15" hidden="1">
       <c r="C187" t="s">
         <v>551</v>
       </c>
@@ -11996,7 +15851,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="188" spans="3:15">
+    <row r="188" spans="3:15" hidden="1">
       <c r="C188" t="s">
         <v>556</v>
       </c>
@@ -12037,7 +15892,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="189" spans="3:15">
+    <row r="189" spans="3:15" hidden="1">
       <c r="C189" t="s">
         <v>559</v>
       </c>
@@ -12078,7 +15933,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="190" spans="3:15">
+    <row r="190" spans="3:15" hidden="1">
       <c r="C190" t="s">
         <v>562</v>
       </c>
@@ -12119,7 +15974,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="191" spans="3:15">
+    <row r="191" spans="3:15" hidden="1">
       <c r="C191" t="s">
         <v>565</v>
       </c>
@@ -12160,7 +16015,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="192" spans="3:15">
+    <row r="192" spans="3:15" hidden="1">
       <c r="C192" t="s">
         <v>568</v>
       </c>
@@ -12201,7 +16056,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="193" spans="3:15">
+    <row r="193" spans="3:15" hidden="1">
       <c r="C193" t="s">
         <v>571</v>
       </c>
@@ -12242,7 +16097,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="194" spans="3:15">
+    <row r="194" spans="3:15" hidden="1">
       <c r="C194" t="s">
         <v>574</v>
       </c>
@@ -12283,7 +16138,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="195" spans="3:15">
+    <row r="195" spans="3:15" hidden="1">
       <c r="C195" t="s">
         <v>574</v>
       </c>
@@ -12324,7 +16179,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="196" spans="3:15">
+    <row r="196" spans="3:15" hidden="1">
       <c r="C196" t="s">
         <v>576</v>
       </c>
@@ -12365,7 +16220,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="197" spans="3:15">
+    <row r="197" spans="3:15" hidden="1">
       <c r="C197" t="s">
         <v>579</v>
       </c>
@@ -12406,7 +16261,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="198" spans="3:15">
+    <row r="198" spans="3:15" hidden="1">
       <c r="C198" t="s">
         <v>582</v>
       </c>
@@ -12447,7 +16302,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="199" spans="3:15">
+    <row r="199" spans="3:15" hidden="1">
       <c r="C199" t="s">
         <v>585</v>
       </c>
@@ -12488,7 +16343,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="200" spans="3:15">
+    <row r="200" spans="3:15" hidden="1">
       <c r="C200" t="s">
         <v>588</v>
       </c>
@@ -12529,7 +16384,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="201" spans="3:15">
+    <row r="201" spans="3:15" hidden="1">
       <c r="C201" t="s">
         <v>591</v>
       </c>
@@ -12570,7 +16425,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="202" spans="3:15">
+    <row r="202" spans="3:15" hidden="1">
       <c r="C202" t="s">
         <v>594</v>
       </c>
@@ -12611,7 +16466,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="203" spans="3:15">
+    <row r="203" spans="3:15" hidden="1">
       <c r="C203" t="s">
         <v>596</v>
       </c>
@@ -12652,7 +16507,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="204" spans="3:15">
+    <row r="204" spans="3:15" hidden="1">
       <c r="C204" t="s">
         <v>599</v>
       </c>
@@ -12693,7 +16548,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="205" spans="3:15">
+    <row r="205" spans="3:15" hidden="1">
       <c r="C205" t="s">
         <v>602</v>
       </c>
@@ -12734,7 +16589,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="206" spans="3:15">
+    <row r="206" spans="3:15" hidden="1">
       <c r="C206" t="s">
         <v>602</v>
       </c>
@@ -12775,7 +16630,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="207" spans="3:15">
+    <row r="207" spans="3:15" hidden="1">
       <c r="C207" t="s">
         <v>605</v>
       </c>
@@ -12816,7 +16671,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="208" spans="3:15">
+    <row r="208" spans="3:15" hidden="1">
       <c r="C208" t="s">
         <v>608</v>
       </c>
@@ -12857,7 +16712,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="209" spans="3:15">
+    <row r="209" spans="3:15" hidden="1">
       <c r="C209" t="s">
         <v>611</v>
       </c>
@@ -12898,7 +16753,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="210" spans="3:15">
+    <row r="210" spans="3:15" hidden="1">
       <c r="C210" t="s">
         <v>614</v>
       </c>
@@ -12939,7 +16794,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="211" spans="3:15">
+    <row r="211" spans="3:15" hidden="1">
       <c r="C211" t="s">
         <v>617</v>
       </c>
@@ -12980,7 +16835,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="212" spans="3:15">
+    <row r="212" spans="3:15" hidden="1">
       <c r="C212" t="s">
         <v>620</v>
       </c>
@@ -13021,7 +16876,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="213" spans="3:15">
+    <row r="213" spans="3:15" hidden="1">
       <c r="C213" t="s">
         <v>623</v>
       </c>
@@ -13062,7 +16917,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="214" spans="3:15">
+    <row r="214" spans="3:15" hidden="1">
       <c r="C214" t="s">
         <v>626</v>
       </c>
@@ -13103,7 +16958,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="215" spans="3:15">
+    <row r="215" spans="3:15" hidden="1">
       <c r="C215" t="s">
         <v>629</v>
       </c>
@@ -13144,7 +16999,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="216" spans="3:15">
+    <row r="216" spans="3:15" hidden="1">
       <c r="C216" t="s">
         <v>629</v>
       </c>
@@ -13185,7 +17040,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="217" spans="3:15">
+    <row r="217" spans="3:15" hidden="1">
       <c r="C217" t="s">
         <v>634</v>
       </c>
@@ -13226,7 +17081,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="218" spans="3:15">
+    <row r="218" spans="3:15" hidden="1">
       <c r="C218" t="s">
         <v>637</v>
       </c>
@@ -13267,7 +17122,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="219" spans="3:15">
+    <row r="219" spans="3:15" hidden="1">
       <c r="C219" t="s">
         <v>640</v>
       </c>
@@ -13308,7 +17163,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="220" spans="3:15">
+    <row r="220" spans="3:15" hidden="1">
       <c r="C220" t="s">
         <v>643</v>
       </c>
@@ -13349,7 +17204,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="221" spans="3:15">
+    <row r="221" spans="3:15" hidden="1">
       <c r="C221" t="s">
         <v>646</v>
       </c>
@@ -13390,7 +17245,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="222" spans="3:15">
+    <row r="222" spans="3:15" hidden="1">
       <c r="C222" t="s">
         <v>649</v>
       </c>
@@ -13431,7 +17286,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="223" spans="3:15">
+    <row r="223" spans="3:15" hidden="1">
       <c r="C223" t="s">
         <v>649</v>
       </c>
@@ -13472,7 +17327,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="224" spans="3:15">
+    <row r="224" spans="3:15" hidden="1">
       <c r="C224" t="s">
         <v>652</v>
       </c>
@@ -13513,7 +17368,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="225" spans="3:15">
+    <row r="225" spans="3:15" hidden="1">
       <c r="C225" t="s">
         <v>655</v>
       </c>
@@ -13554,7 +17409,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="226" spans="3:15">
+    <row r="226" spans="3:15" hidden="1">
       <c r="C226" t="s">
         <v>658</v>
       </c>
@@ -13595,7 +17450,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="227" spans="3:15">
+    <row r="227" spans="3:15" hidden="1">
       <c r="C227" t="s">
         <v>662</v>
       </c>
@@ -13636,7 +17491,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="228" spans="3:15">
+    <row r="228" spans="3:15" hidden="1">
       <c r="C228" t="s">
         <v>662</v>
       </c>
@@ -13677,7 +17532,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="229" spans="3:15">
+    <row r="229" spans="3:15" hidden="1">
       <c r="C229" t="s">
         <v>665</v>
       </c>
@@ -13718,7 +17573,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="230" spans="3:15">
+    <row r="230" spans="3:15" hidden="1">
       <c r="C230" t="s">
         <v>668</v>
       </c>
@@ -13759,7 +17614,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="231" spans="3:15">
+    <row r="231" spans="3:15" hidden="1">
       <c r="C231" t="s">
         <v>668</v>
       </c>
@@ -13800,7 +17655,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="232" spans="3:15">
+    <row r="232" spans="3:15" hidden="1">
       <c r="C232" t="s">
         <v>671</v>
       </c>
@@ -13841,7 +17696,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="233" spans="3:15">
+    <row r="233" spans="3:15" hidden="1">
       <c r="C233" t="s">
         <v>674</v>
       </c>
@@ -13882,7 +17737,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="234" spans="3:15">
+    <row r="234" spans="3:15" hidden="1">
       <c r="C234" t="s">
         <v>677</v>
       </c>
@@ -13923,7 +17778,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="235" spans="3:15">
+    <row r="235" spans="3:15" hidden="1">
       <c r="C235" t="s">
         <v>680</v>
       </c>
@@ -13964,7 +17819,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="236" spans="3:15">
+    <row r="236" spans="3:15" hidden="1">
       <c r="C236" t="s">
         <v>683</v>
       </c>
@@ -14005,7 +17860,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="237" spans="3:15">
+    <row r="237" spans="3:15" hidden="1">
       <c r="C237" t="s">
         <v>686</v>
       </c>
@@ -14046,7 +17901,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="238" spans="3:15">
+    <row r="238" spans="3:15" hidden="1">
       <c r="C238" t="s">
         <v>689</v>
       </c>
@@ -14087,7 +17942,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="239" spans="3:15">
+    <row r="239" spans="3:15" hidden="1">
       <c r="C239" t="s">
         <v>692</v>
       </c>
@@ -14128,7 +17983,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="240" spans="3:15">
+    <row r="240" spans="3:15" hidden="1">
       <c r="C240" t="s">
         <v>695</v>
       </c>
@@ -14169,7 +18024,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="241" spans="3:15">
+    <row r="241" spans="3:15" hidden="1">
       <c r="C241" t="s">
         <v>695</v>
       </c>
@@ -14210,7 +18065,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="242" spans="3:15">
+    <row r="242" spans="3:15" hidden="1">
       <c r="C242" t="s">
         <v>698</v>
       </c>
@@ -14251,7 +18106,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="243" spans="3:15">
+    <row r="243" spans="3:15" hidden="1">
       <c r="C243" t="s">
         <v>701</v>
       </c>
@@ -14292,7 +18147,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="244" spans="3:15">
+    <row r="244" spans="3:15" hidden="1">
       <c r="C244" t="s">
         <v>701</v>
       </c>
@@ -14333,7 +18188,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="245" spans="3:15">
+    <row r="245" spans="3:15" hidden="1">
       <c r="C245" t="s">
         <v>704</v>
       </c>
@@ -14374,7 +18229,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="246" spans="3:15">
+    <row r="246" spans="3:15" hidden="1">
       <c r="C246" t="s">
         <v>707</v>
       </c>
@@ -14415,7 +18270,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="247" spans="3:15">
+    <row r="247" spans="3:15" hidden="1">
       <c r="C247" t="s">
         <v>710</v>
       </c>
@@ -14456,7 +18311,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="248" spans="3:15">
+    <row r="248" spans="3:15" hidden="1">
       <c r="C248" t="s">
         <v>713</v>
       </c>
@@ -14497,7 +18352,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="249" spans="3:15">
+    <row r="249" spans="3:15" hidden="1">
       <c r="C249" t="s">
         <v>716</v>
       </c>
@@ -14538,7 +18393,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="250" spans="3:15">
+    <row r="250" spans="3:15" hidden="1">
       <c r="C250" t="s">
         <v>719</v>
       </c>
@@ -14579,7 +18434,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="251" spans="3:15">
+    <row r="251" spans="3:15" hidden="1">
       <c r="C251" t="s">
         <v>722</v>
       </c>
@@ -14620,7 +18475,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="252" spans="3:15">
+    <row r="252" spans="3:15" hidden="1">
       <c r="C252" t="s">
         <v>725</v>
       </c>
@@ -14661,7 +18516,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="253" spans="3:15">
+    <row r="253" spans="3:15" hidden="1">
       <c r="C253" t="s">
         <v>725</v>
       </c>
@@ -14702,7 +18557,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="254" spans="3:15">
+    <row r="254" spans="3:15" hidden="1">
       <c r="C254" t="s">
         <v>728</v>
       </c>
@@ -14743,7 +18598,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="255" spans="3:15">
+    <row r="255" spans="3:15" hidden="1">
       <c r="C255" t="s">
         <v>728</v>
       </c>
@@ -14784,7 +18639,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="256" spans="3:15">
+    <row r="256" spans="3:15" hidden="1">
       <c r="C256" t="s">
         <v>733</v>
       </c>
@@ -14825,7 +18680,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="257" spans="3:15">
+    <row r="257" spans="3:15" hidden="1">
       <c r="C257" t="s">
         <v>736</v>
       </c>
@@ -14866,7 +18721,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="258" spans="3:15">
+    <row r="258" spans="3:15" hidden="1">
       <c r="C258" t="s">
         <v>739</v>
       </c>
@@ -14907,7 +18762,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="259" spans="3:15">
+    <row r="259" spans="3:15" hidden="1">
       <c r="C259" t="s">
         <v>739</v>
       </c>
@@ -14948,7 +18803,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="260" spans="3:15">
+    <row r="260" spans="3:15" hidden="1">
       <c r="C260" t="s">
         <v>744</v>
       </c>
@@ -14989,7 +18844,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="261" spans="3:15">
+    <row r="261" spans="3:15" hidden="1">
       <c r="C261" t="s">
         <v>747</v>
       </c>
@@ -15030,7 +18885,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="262" spans="3:15">
+    <row r="262" spans="3:15" hidden="1">
       <c r="C262" t="s">
         <v>750</v>
       </c>
@@ -15071,7 +18926,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="263" spans="3:15">
+    <row r="263" spans="3:15" hidden="1">
       <c r="C263" t="s">
         <v>753</v>
       </c>
@@ -15112,7 +18967,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="264" spans="3:15">
+    <row r="264" spans="3:15" hidden="1">
       <c r="C264" t="s">
         <v>756</v>
       </c>
@@ -15153,7 +19008,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="265" spans="3:15">
+    <row r="265" spans="3:15" hidden="1">
       <c r="C265" t="s">
         <v>759</v>
       </c>
@@ -15194,7 +19049,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="266" spans="3:15">
+    <row r="266" spans="3:15" hidden="1">
       <c r="C266" t="s">
         <v>762</v>
       </c>
@@ -15235,7 +19090,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="267" spans="3:15">
+    <row r="267" spans="3:15" hidden="1">
       <c r="C267" t="s">
         <v>765</v>
       </c>
@@ -18941,4 +22796,456 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{056D4C31-6BF7-4F39-B5EE-B0BC201D12D6}">
+  <dimension ref="A4:C22"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="20.5703125" customWidth="1"/>
+    <col min="3" max="3" width="28.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="1:3">
+      <c r="B4" s="28" t="s">
+        <v>780</v>
+      </c>
+      <c r="C4" s="35" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="str">
+        <f>IFERROR(VLOOKUP($C$4,staff[],A6,FALSE),"Not Found")</f>
+        <v>Edd</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="str">
+        <f>IFERROR(VLOOKUP($C$4,staff[],A7,FALSE),"Not Found")</f>
+        <v>MacKnockiter</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="str">
+        <f>IFERROR(VLOOKUP($C$4,staff[],A8,FALSE),"Not Found")</f>
+        <v>Accounting</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9">
+        <f>IFERROR(VLOOKUP($C$4,staff[],A9,FALSE),"Not Found")</f>
+        <v>119022.49</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3">
+      <c r="B17" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="35" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3">
+      <c r="C18">
+        <f>MATCH(C17,staff[Last Name],0)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="B20" s="34" t="s">
+        <v>780</v>
+      </c>
+      <c r="C20" t="str">
+        <f>INDEX(staff[Emp ID],MATCH(C17,staff[Last Name],0))</f>
+        <v>PR00113</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="B21" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" t="str">
+        <f>INDEX(staff[Department],MATCH(C17,staff[Last Name],0))</f>
+        <v>Business Development</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3">
+      <c r="B22" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22">
+        <f>INDEX(staff[Salary],MATCH(C17,staff[Last Name],0))</f>
+        <v>80695.740000000005</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46536243-F308-454E-A744-58FF22B55FB4}">
+  <dimension ref="B4:N44"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="22.140625" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="2:3">
+      <c r="B4" s="28" t="s">
+        <v>781</v>
+      </c>
+      <c r="C4" s="35" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3">
+      <c r="B6" t="s">
+        <v>782</v>
+      </c>
+      <c r="C6" t="str">
+        <f>_xlfn.XLOOKUP(C4,staff[Emp ID],staff[First Name],"Not Found")</f>
+        <v>Edd</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3">
+      <c r="B7" t="s">
+        <v>783</v>
+      </c>
+      <c r="C7" t="str">
+        <f>_xlfn.XLOOKUP(C4,staff[Emp ID],staff[Last Name],"Not Found")</f>
+        <v>MacKnockiter</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3">
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="str">
+        <f>_xlfn.XLOOKUP(C4,staff[Emp ID],staff[Department],"Not Found")</f>
+        <v>Accounting</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3">
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9">
+        <f>_xlfn.XLOOKUP(C4,staff[Emp ID],staff[Salary],"Not Found")</f>
+        <v>119022.49</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3">
+      <c r="B14" s="28" t="s">
+        <v>783</v>
+      </c>
+      <c r="C14" s="35" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14">
+      <c r="B17" s="34" t="s">
+        <v>781</v>
+      </c>
+      <c r="C17" t="str">
+        <f>_xlfn.XLOOKUP(C14,staff[Last Name],staff[Emp ID],"Not Found")</f>
+        <v>PR00113</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14">
+      <c r="B18" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" t="str">
+        <f>_xlfn.XLOOKUP(C14,staff[Last Name],staff[Department],"Not Found")</f>
+        <v>Business Development</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14">
+      <c r="B19" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19">
+        <f>_xlfn.XLOOKUP(C14,staff[Last Name],staff[Salary],"Not Found")</f>
+        <v>80695.740000000005</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14">
+      <c r="B22" s="34" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14">
+      <c r="B23" t="str" cm="1">
+        <f t="array" ref="B23:N23">_xlfn.XLOOKUP(C14,staff[Last Name],staff[],"Not Found")</f>
+        <v>PR00113</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Van</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Tuxwell</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Business Development</v>
+      </c>
+      <c r="G23">
+        <v>80695.740000000005</v>
+      </c>
+      <c r="H23" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I23">
+        <v>43360</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L23" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="M23">
+        <v>5.7643835616438359</v>
+      </c>
+      <c r="N23" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14">
+      <c r="B25" s="34" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14">
+      <c r="B26" t="str" cm="1">
+        <f t="array" ref="B26:B38">TRANSPOSE(_xlfn.XLOOKUP(C14,staff[Last Name],staff[],"Not Found"))</f>
+        <v>PR00113</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14">
+      <c r="B27" t="str">
+        <v>Van</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14">
+      <c r="B28" t="str">
+        <v>Tuxwell</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14">
+      <c r="B29" t="str">
+        <v>Female</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14">
+      <c r="B30" t="str">
+        <v>Business Development</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14">
+      <c r="B31">
+        <v>80695.740000000005</v>
+      </c>
+    </row>
+    <row r="32" spans="2:14">
+      <c r="B32" t="str">
+        <v>50k to 100k</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14">
+      <c r="B33">
+        <v>43360</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14">
+      <c r="B34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14">
+      <c r="B35" t="str">
+        <v>Permanent</v>
+      </c>
+    </row>
+    <row r="36" spans="2:14">
+      <c r="B36" t="str">
+        <v>Columbus, USA</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14">
+      <c r="B37">
+        <v>5.7643835616438359</v>
+      </c>
+    </row>
+    <row r="38" spans="2:14">
+      <c r="B38" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="41" spans="2:14" ht="30.75">
+      <c r="B41" s="36" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14">
+      <c r="B42" t="str" cm="1">
+        <f t="array" ref="B42:N44">_xlfn._xlws.FILTER(staff[], staff[Last Name]=C14)</f>
+        <v>PR00113</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Van</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Tuxwell</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F42" t="str">
+        <v>Business Development</v>
+      </c>
+      <c r="G42">
+        <v>80695.740000000005</v>
+      </c>
+      <c r="H42" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I42">
+        <v>43360</v>
+      </c>
+      <c r="J42">
+        <v>1</v>
+      </c>
+      <c r="K42" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L42" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="M42">
+        <v>5.7643835616438359</v>
+      </c>
+      <c r="N42" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14">
+      <c r="B43" t="str">
+        <v>PR00113</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Van</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Tuxwell</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F43" t="str">
+        <v>Business Development</v>
+      </c>
+      <c r="G43">
+        <v>80695.740000000005</v>
+      </c>
+      <c r="H43" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I43">
+        <v>43360</v>
+      </c>
+      <c r="J43">
+        <v>1</v>
+      </c>
+      <c r="K43" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L43" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="M43">
+        <v>5.7643835616438359</v>
+      </c>
+      <c r="N43" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14">
+      <c r="B44" t="str">
+        <v>PR04380</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Van</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Tuxwell</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F44" t="str">
+        <v>Business Development</v>
+      </c>
+      <c r="G44">
+        <v>80695.740000000005</v>
+      </c>
+      <c r="H44" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I44">
+        <v>43787</v>
+      </c>
+      <c r="J44">
+        <v>0.8</v>
+      </c>
+      <c r="K44" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L44" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="M44">
+        <v>4.5945205479452058</v>
+      </c>
+      <c r="N44" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Excel/02Functions_Formulas/sample-data-fx.blank.xlsx
+++ b/Excel/02Functions_Formulas/sample-data-fx.blank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell 7490\Documents\PythonClassSF\DataAnalytics01\Excel\02Functions_Formulas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A233740C-1439-4F45-B7E8-4294C7E27348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{02B9AFA2-6619-4337-8220-4E391F66BE8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="8" activeTab="10" xr2:uid="{26D4546B-D2A1-4444-8EAF-A6228F96F0C1}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="11" activeTab="11" xr2:uid="{26D4546B-D2A1-4444-8EAF-A6228F96F0C1}"/>
   </bookViews>
   <sheets>
     <sheet name="Concepts" sheetId="2" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="Task 07" sheetId="9" r:id="rId9"/>
     <sheet name="Task 08" sheetId="10" r:id="rId10"/>
     <sheet name="Task 09" sheetId="11" r:id="rId11"/>
+    <sheet name="Task 10" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -68,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2444" uniqueCount="791">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2453" uniqueCount="797">
   <si>
     <t>Essential Excel Functions &amp; Formulas</t>
   </si>
@@ -2441,18 +2442,37 @@
   </si>
   <si>
     <t>All Persons in one cell</t>
+  </si>
+  <si>
+    <t>All Departments</t>
+  </si>
+  <si>
+    <t>Avg. Salary</t>
+  </si>
+  <si>
+    <t>% diff from overall avg</t>
+  </si>
+  <si>
+    <t>Median Salary</t>
+  </si>
+  <si>
+    <t>Female Ratio</t>
+  </si>
+  <si>
+    <t>Total Count Female</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="164" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2510,8 +2530,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2551,6 +2578,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2605,7 +2638,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -2694,6 +2727,11 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2825,13 +2863,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{71B18D4F-F180-46A4-9272-AD02F8205A18}" name="staff" displayName="staff" ref="C7:O267" totalsRowShown="0">
-  <autoFilter ref="C7:O267" xr:uid="{71B18D4F-F180-46A4-9272-AD02F8205A18}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Tuxwell"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="C7:O267" xr:uid="{71B18D4F-F180-46A4-9272-AD02F8205A18}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C8:O267">
     <sortCondition ref="C7:C267"/>
   </sortState>
@@ -8403,6 +8435,1515 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BDD781A-F91A-41D9-A63E-58DF3A36D552}">
+  <dimension ref="B3:N49"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="26.7109375" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="25.140625" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" customWidth="1"/>
+    <col min="7" max="7" width="21.140625" customWidth="1"/>
+    <col min="8" max="8" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:8">
+      <c r="F3" s="41"/>
+    </row>
+    <row r="4" spans="2:8">
+      <c r="B4" s="28" t="s">
+        <v>791</v>
+      </c>
+      <c r="C4" s="28">
+        <f>COUNTA(staff[Emp ID])</f>
+        <v>260</v>
+      </c>
+      <c r="D4" s="40">
+        <f>AVERAGE(staff[Salary])</f>
+        <v>73861.325230769246</v>
+      </c>
+      <c r="E4" s="28"/>
+      <c r="F4" s="40">
+        <f>MAX(staff[Salary])</f>
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8">
+      <c r="B6" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>768</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>792</v>
+      </c>
+      <c r="E6" s="37" t="s">
+        <v>793</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>773</v>
+      </c>
+      <c r="G6" s="28" t="s">
+        <v>794</v>
+      </c>
+      <c r="H6" s="28" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8">
+      <c r="B7" t="str" cm="1">
+        <f t="array" ref="B7:B18">_xlfn._xlws.SORT(_xlfn.UNIQUE(staff[Department]))</f>
+        <v>Accounting</v>
+      </c>
+      <c r="C7" cm="1">
+        <f t="array" ref="C7:C18">COUNTIFS(staff[Department],_xlfn.ANCHORARRAY(B7))</f>
+        <v>26</v>
+      </c>
+      <c r="D7" s="42" cm="1">
+        <f t="array" ref="D7:D18">AVERAGEIFS(staff[Salary],staff[Department],_xlfn.ANCHORARRAY(B7))</f>
+        <v>69806.945769230777</v>
+      </c>
+      <c r="E7" s="42" cm="1">
+        <f t="array" ref="E7:E18">_xlfn.ANCHORARRAY(D7)-D4</f>
+        <v>-4054.3794615384686</v>
+      </c>
+      <c r="F7" s="42" cm="1">
+        <f t="array" ref="F7:F18">_xlfn.MAXIFS(staff[Salary],staff[Department],_xlfn.ANCHORARRAY(B7))</f>
+        <v>119022.49</v>
+      </c>
+      <c r="G7" s="44" cm="1">
+        <f t="array" ref="G7:G18">_xlfn.MAP(_xlfn.ANCHORARRAY(B7),_xlfn.LAMBDA(_xlpm.x,MEDIAN(_xlfn._xlws.FILTER(staff[Salary],staff[Department]=_xlpm.x))))</f>
+        <v>69025.614999999991</v>
+      </c>
+      <c r="H7" cm="1">
+        <f t="array" ref="H7:H18">COUNTIFS(staff[Department],_xlfn.ANCHORARRAY(B7),staff[Gender],"Female")</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8">
+      <c r="B8" t="str">
+        <v>Business Development</v>
+      </c>
+      <c r="C8">
+        <v>26</v>
+      </c>
+      <c r="D8" s="42">
+        <v>79781.805769230778</v>
+      </c>
+      <c r="E8" s="42">
+        <v>5920.480538461532</v>
+      </c>
+      <c r="F8" s="42">
+        <v>110042.37</v>
+      </c>
+      <c r="G8" s="44">
+        <v>80695.740000000005</v>
+      </c>
+      <c r="H8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8">
+      <c r="B9" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="C9">
+        <v>26</v>
+      </c>
+      <c r="D9" s="42">
+        <v>81976.441923076913</v>
+      </c>
+      <c r="E9" s="42">
+        <v>8115.1166923076671</v>
+      </c>
+      <c r="F9" s="42">
+        <v>120000</v>
+      </c>
+      <c r="G9" s="44">
+        <v>85332.304999999993</v>
+      </c>
+      <c r="H9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8">
+      <c r="B10" t="str">
+        <v>Human Resources</v>
+      </c>
+      <c r="C10">
+        <v>22</v>
+      </c>
+      <c r="D10" s="42">
+        <v>73109.377727272746</v>
+      </c>
+      <c r="E10" s="43">
+        <v>-751.94750349649985</v>
+      </c>
+      <c r="F10" s="42">
+        <v>103494.94</v>
+      </c>
+      <c r="G10" s="44">
+        <v>73182.794999999998</v>
+      </c>
+      <c r="H10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8">
+      <c r="B11" t="str">
+        <v>Legal</v>
+      </c>
+      <c r="C11">
+        <v>21</v>
+      </c>
+      <c r="D11" s="42">
+        <v>67242.51761904762</v>
+      </c>
+      <c r="E11" s="43">
+        <v>-6618.807611721626</v>
+      </c>
+      <c r="F11" s="42">
+        <v>113747.56</v>
+      </c>
+      <c r="G11" s="44">
+        <v>66572.58</v>
+      </c>
+      <c r="H11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8">
+      <c r="B12" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="C12">
+        <v>12</v>
+      </c>
+      <c r="D12" s="42">
+        <v>64441.299999999996</v>
+      </c>
+      <c r="E12" s="43">
+        <v>-9420.0252307692499</v>
+      </c>
+      <c r="F12" s="42">
+        <v>104903.79</v>
+      </c>
+      <c r="G12" s="44">
+        <v>66961.489999999991</v>
+      </c>
+      <c r="H12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8">
+      <c r="B13" t="str">
+        <v>Product Management</v>
+      </c>
+      <c r="C13">
+        <v>29</v>
+      </c>
+      <c r="D13" s="42">
+        <v>75179.064482758593</v>
+      </c>
+      <c r="E13" s="43">
+        <v>1317.7392519893474</v>
+      </c>
+      <c r="F13" s="42">
+        <v>115191.38</v>
+      </c>
+      <c r="G13" s="44">
+        <v>72502.61</v>
+      </c>
+      <c r="H13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8">
+      <c r="B14" t="str">
+        <v>Research and Development</v>
+      </c>
+      <c r="C14">
+        <v>18</v>
+      </c>
+      <c r="D14" s="42">
+        <v>66910.765555555554</v>
+      </c>
+      <c r="E14" s="43">
+        <v>-6950.5596752136917</v>
+      </c>
+      <c r="F14" s="42">
+        <v>99683.67</v>
+      </c>
+      <c r="G14" s="44">
+        <v>65995.375</v>
+      </c>
+      <c r="H14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8">
+      <c r="B15" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="C15">
+        <v>18</v>
+      </c>
+      <c r="D15" s="42">
+        <v>71897.095555555556</v>
+      </c>
+      <c r="E15" s="42">
+        <v>-1964.2296752136899</v>
+      </c>
+      <c r="F15" s="42">
+        <v>102129.37</v>
+      </c>
+      <c r="G15" s="44">
+        <v>79396.654999999999</v>
+      </c>
+      <c r="H15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8">
+      <c r="B16" t="str">
+        <v>Services</v>
+      </c>
+      <c r="C16">
+        <v>21</v>
+      </c>
+      <c r="D16" s="42">
+        <v>74673.974761904756</v>
+      </c>
+      <c r="E16" s="42">
+        <v>812.64953113551019</v>
+      </c>
+      <c r="F16" s="42">
+        <v>120000</v>
+      </c>
+      <c r="G16" s="44">
+        <v>77096.05</v>
+      </c>
+      <c r="H16">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14">
+      <c r="B17" t="str">
+        <v>Support</v>
+      </c>
+      <c r="C17">
+        <v>17</v>
+      </c>
+      <c r="D17" s="42">
+        <v>66432.455882352937</v>
+      </c>
+      <c r="E17" s="43">
+        <v>-7428.8693484163086</v>
+      </c>
+      <c r="F17" s="42">
+        <v>104802.63</v>
+      </c>
+      <c r="G17" s="44">
+        <v>61214.26</v>
+      </c>
+      <c r="H17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14">
+      <c r="B18" t="str">
+        <v>Training</v>
+      </c>
+      <c r="C18">
+        <v>24</v>
+      </c>
+      <c r="D18" s="42">
+        <v>83883.965000000011</v>
+      </c>
+      <c r="E18" s="43">
+        <v>10022.639769230766</v>
+      </c>
+      <c r="F18" s="42">
+        <v>116767.63</v>
+      </c>
+      <c r="G18" s="44">
+        <v>89569.44</v>
+      </c>
+      <c r="H18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14">
+      <c r="B19">
+        <f>COUNTA(B7:B18)</f>
+        <v>12</v>
+      </c>
+      <c r="G19" s="28" t="s">
+        <v>796</v>
+      </c>
+      <c r="H19">
+        <f>SUM(H7:H18)</f>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14">
+      <c r="B22" s="28" t="str" cm="1">
+        <f t="array" ref="B22:N22">staff[#Headers]</f>
+        <v>Emp ID</v>
+      </c>
+      <c r="C22" s="28" t="str">
+        <v>First Name</v>
+      </c>
+      <c r="D22" s="28" t="str">
+        <v>Last Name</v>
+      </c>
+      <c r="E22" s="28" t="str">
+        <v>Gender</v>
+      </c>
+      <c r="F22" s="28" t="str">
+        <v>Department</v>
+      </c>
+      <c r="G22" s="28" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="H22" s="28" t="str">
+        <v>Salary Bucket</v>
+      </c>
+      <c r="I22" s="28" t="str">
+        <v>Start Date</v>
+      </c>
+      <c r="J22" s="28" t="str">
+        <v>FTE</v>
+      </c>
+      <c r="K22" s="28" t="str">
+        <v>Employee type</v>
+      </c>
+      <c r="L22" s="28" t="str">
+        <v>Work location</v>
+      </c>
+      <c r="M22" s="28" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="N22" s="28" t="str">
+        <v>Work Type</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14">
+      <c r="B23" t="str" cm="1">
+        <f t="array" ref="B23:N48">_xlfn._xlws.SORT(_xlfn._xlws.FILTER(staff[], staff[Department]="Accounting"),6,1)</f>
+        <v>PR01055</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Devasree</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Fullara</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G23" s="44">
+        <v>35936.31</v>
+      </c>
+      <c r="H23" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I23">
+        <v>43241</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L23" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="M23">
+        <v>6.0904109589041093</v>
+      </c>
+      <c r="N23" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14">
+      <c r="B24" t="str">
+        <v>PR01956</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Jamesy</v>
+      </c>
+      <c r="D24" t="str">
+        <v>O'Ferris</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G24" s="44">
+        <v>36547.58</v>
+      </c>
+      <c r="H24" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I24">
+        <v>43416</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L24" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M24">
+        <v>5.6109589041095891</v>
+      </c>
+      <c r="N24" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14">
+      <c r="B25" t="str">
+        <v>PR01956</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Jamesy</v>
+      </c>
+      <c r="D25" t="str">
+        <v>O'Ferris</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G25" s="44">
+        <v>36547.58</v>
+      </c>
+      <c r="H25" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I25">
+        <v>43416</v>
+      </c>
+      <c r="J25">
+        <v>1</v>
+      </c>
+      <c r="K25" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L25" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M25">
+        <v>5.6109589041095891</v>
+      </c>
+      <c r="N25" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14">
+      <c r="B26" t="str">
+        <v>VT04273</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Brad</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Gumb</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G26" s="44">
+        <v>38825.18</v>
+      </c>
+      <c r="H26" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I26">
+        <v>43696</v>
+      </c>
+      <c r="J26">
+        <v>1</v>
+      </c>
+      <c r="K26" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="L26" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M26">
+        <v>4.8438356164383558</v>
+      </c>
+      <c r="N26" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14">
+      <c r="B27" t="str">
+        <v>SQ02223</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Pippy</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Shepperd</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G27" s="44">
+        <v>44845.33</v>
+      </c>
+      <c r="H27" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I27">
+        <v>43277</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
+      <c r="K27" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L27" t="str">
+        <v>Seattle, USA</v>
+      </c>
+      <c r="M27">
+        <v>5.9917808219178079</v>
+      </c>
+      <c r="N27" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14">
+      <c r="B28" t="str">
+        <v>SQ01519</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Caron</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Kolakovic</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G28" s="44">
+        <v>49915.14</v>
+      </c>
+      <c r="H28" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I28">
+        <v>43550</v>
+      </c>
+      <c r="J28">
+        <v>1</v>
+      </c>
+      <c r="K28" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L28" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M28">
+        <v>5.2438356164383562</v>
+      </c>
+      <c r="N28" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14">
+      <c r="B29" t="str">
+        <v>VT03849</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Leonidas</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Cavaney</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G29" s="44">
+        <v>52246.29</v>
+      </c>
+      <c r="H29" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I29">
+        <v>43573</v>
+      </c>
+      <c r="J29">
+        <v>1</v>
+      </c>
+      <c r="K29" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="L29" t="str">
+        <v>Wellington, New Zealand</v>
+      </c>
+      <c r="M29">
+        <v>5.1808219178082195</v>
+      </c>
+      <c r="N29" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14">
+      <c r="B30" t="str">
+        <v>SQ02424</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Kevalkumar</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Solanki</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G30" s="44">
+        <v>52270.22</v>
+      </c>
+      <c r="H30" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I30">
+        <v>43521</v>
+      </c>
+      <c r="J30">
+        <v>0.3</v>
+      </c>
+      <c r="K30" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L30" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="M30">
+        <v>5.3232876712328769</v>
+      </c>
+      <c r="N30" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14">
+      <c r="B31" t="str">
+        <v>PR00882</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Jill</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Shipsey</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G31" s="44">
+        <v>52963.65</v>
+      </c>
+      <c r="H31" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I31">
+        <v>44288</v>
+      </c>
+      <c r="J31">
+        <v>0.3</v>
+      </c>
+      <c r="K31" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L31" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="M31">
+        <v>3.2219178082191782</v>
+      </c>
+      <c r="N31" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="32" spans="2:14">
+      <c r="B32" t="str">
+        <v>VT01092</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Tabby</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Astall</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G32" s="44">
+        <v>57419.35</v>
+      </c>
+      <c r="H32" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I32">
+        <v>43305</v>
+      </c>
+      <c r="J32">
+        <v>1</v>
+      </c>
+      <c r="K32" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="L32" t="str">
+        <v>Auckland, New Zealand</v>
+      </c>
+      <c r="M32">
+        <v>5.9150684931506845</v>
+      </c>
+      <c r="N32" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14">
+      <c r="B33" t="str">
+        <v>TN01701</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Yves</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Pawlik</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G33" s="44">
+        <v>57925.91</v>
+      </c>
+      <c r="H33" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I33">
+        <v>43572</v>
+      </c>
+      <c r="J33">
+        <v>0.5</v>
+      </c>
+      <c r="K33" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L33" t="str">
+        <v>Wellington, New Zealand</v>
+      </c>
+      <c r="M33">
+        <v>5.183561643835616</v>
+      </c>
+      <c r="N33" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14">
+      <c r="B34" t="str">
+        <v>TN01028</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Alicea</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Pudsall</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G34" s="44">
+        <v>67633.850000000006</v>
+      </c>
+      <c r="H34" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I34">
+        <v>43340</v>
+      </c>
+      <c r="J34">
+        <v>1</v>
+      </c>
+      <c r="K34" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L34" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="M34">
+        <v>5.8191780821917805</v>
+      </c>
+      <c r="N34" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14">
+      <c r="B35" t="str">
+        <v>SQ03321</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Gradey</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Litton</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G35" s="44">
+        <v>68887.839999999997</v>
+      </c>
+      <c r="H35" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I35">
+        <v>43297</v>
+      </c>
+      <c r="J35">
+        <v>1</v>
+      </c>
+      <c r="K35" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L35" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M35">
+        <v>5.9369863013698634</v>
+      </c>
+      <c r="N35" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="36" spans="2:14">
+      <c r="B36" t="str">
+        <v>TN02570</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Grady</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Rochelle</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G36" s="44">
+        <v>69163.39</v>
+      </c>
+      <c r="H36" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I36">
+        <v>43397</v>
+      </c>
+      <c r="J36">
+        <v>1</v>
+      </c>
+      <c r="K36" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L36" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M36">
+        <v>5.6630136986301371</v>
+      </c>
+      <c r="N36" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14">
+      <c r="B37" t="str">
+        <v>TN02570</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Grady</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Rochelle</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F37" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G37" s="44">
+        <v>69163.39</v>
+      </c>
+      <c r="H37" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I37">
+        <v>43397</v>
+      </c>
+      <c r="J37">
+        <v>1</v>
+      </c>
+      <c r="K37" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L37" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M37">
+        <v>5.6630136986301371</v>
+      </c>
+      <c r="N37" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="38" spans="2:14">
+      <c r="B38" t="str">
+        <v>VT02374</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Delphine</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Jewis</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G38" s="44">
+        <v>71823.56</v>
+      </c>
+      <c r="H38" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I38">
+        <v>43374</v>
+      </c>
+      <c r="J38">
+        <v>0.3</v>
+      </c>
+      <c r="K38" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="L38" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M38">
+        <v>5.7260273972602738</v>
+      </c>
+      <c r="N38" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14">
+      <c r="B39" t="str">
+        <v>VT02374</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Delphine</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Jewis</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F39" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G39" s="44">
+        <v>71823.56</v>
+      </c>
+      <c r="H39" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I39">
+        <v>43374</v>
+      </c>
+      <c r="J39">
+        <v>0.3</v>
+      </c>
+      <c r="K39" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="L39" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M39">
+        <v>5.7260273972602738</v>
+      </c>
+      <c r="N39" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="40" spans="2:14">
+      <c r="B40" t="str">
+        <v>VT01610</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Dhruv</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Manjunath</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F40" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G40" s="44">
+        <v>76303.820000000007</v>
+      </c>
+      <c r="H40" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I40">
+        <v>43458</v>
+      </c>
+      <c r="J40">
+        <v>1</v>
+      </c>
+      <c r="K40" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="L40" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="M40">
+        <v>5.4958904109589044</v>
+      </c>
+      <c r="N40" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="41" spans="2:14">
+      <c r="B41" t="str">
+        <v>VT01610</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Kunja</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Prashanta</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F41" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G41" s="44">
+        <v>76303.820000000007</v>
+      </c>
+      <c r="H41" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I41">
+        <v>43458</v>
+      </c>
+      <c r="J41">
+        <v>1</v>
+      </c>
+      <c r="K41" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="L41" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="M41">
+        <v>5.4958904109589044</v>
+      </c>
+      <c r="N41" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14">
+      <c r="B42" t="str">
+        <v>PR01211</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Enoch</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Dowrey</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F42" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G42" s="44">
+        <v>91645.04</v>
+      </c>
+      <c r="H42" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I42">
+        <v>44223</v>
+      </c>
+      <c r="J42">
+        <v>1</v>
+      </c>
+      <c r="K42" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L42" t="str">
+        <v>Auckland, New Zealand</v>
+      </c>
+      <c r="M42">
+        <v>3.4</v>
+      </c>
+      <c r="N42" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14">
+      <c r="B43" t="str">
+        <v>PR02140</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Anjushri</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Chandiramani</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F43" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G43" s="44">
+        <v>95954.02</v>
+      </c>
+      <c r="H43" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I43">
+        <v>43567</v>
+      </c>
+      <c r="J43">
+        <v>0.3</v>
+      </c>
+      <c r="K43" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L43" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="M43">
+        <v>5.1972602739726028</v>
+      </c>
+      <c r="N43" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14">
+      <c r="B44" t="str">
+        <v>TN02377</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Anjela</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Spancock</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Need to check</v>
+      </c>
+      <c r="F44" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G44" s="44">
+        <v>98012.63</v>
+      </c>
+      <c r="H44" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I44">
+        <v>43780</v>
+      </c>
+      <c r="J44">
+        <v>1</v>
+      </c>
+      <c r="K44" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L44" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M44">
+        <v>4.6136986301369864</v>
+      </c>
+      <c r="N44" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14">
+      <c r="B45" t="str">
+        <v>VT01762</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Geena</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Raghavanpillai</v>
+      </c>
+      <c r="E45" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F45" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G45" s="44">
+        <v>102515.81</v>
+      </c>
+      <c r="H45" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I45">
+        <v>43902</v>
+      </c>
+      <c r="J45">
+        <v>1</v>
+      </c>
+      <c r="K45" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="L45" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="M45">
+        <v>4.279452054794521</v>
+      </c>
+      <c r="N45" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14">
+      <c r="B46" t="str">
+        <v>SQ03476</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Ramalingam</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Kothapeta</v>
+      </c>
+      <c r="E46" t="str">
+        <v>Need to check</v>
+      </c>
+      <c r="F46" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G46" s="44">
+        <v>107107.6</v>
+      </c>
+      <c r="H46" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I46">
+        <v>43325</v>
+      </c>
+      <c r="J46">
+        <v>0.9</v>
+      </c>
+      <c r="K46" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L46" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="M46">
+        <v>5.86027397260274</v>
+      </c>
+      <c r="N46" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14">
+      <c r="B47" t="str">
+        <v>PR00746</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Hogan</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Iles</v>
+      </c>
+      <c r="E47" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F47" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G47" s="44">
+        <v>114177.23</v>
+      </c>
+      <c r="H47" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I47">
+        <v>43908</v>
+      </c>
+      <c r="J47">
+        <v>1</v>
+      </c>
+      <c r="K47" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L47" t="str">
+        <v>Wellington, New Zealand</v>
+      </c>
+      <c r="M47">
+        <v>4.2630136986301368</v>
+      </c>
+      <c r="N47" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14">
+      <c r="B48" t="str">
+        <v>PR03886</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Edd</v>
+      </c>
+      <c r="D48" t="str">
+        <v>MacKnockiter</v>
+      </c>
+      <c r="E48" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F48" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G48" s="44">
+        <v>119022.49</v>
+      </c>
+      <c r="H48" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I48">
+        <v>44431</v>
+      </c>
+      <c r="J48">
+        <v>1</v>
+      </c>
+      <c r="K48" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L48" t="str">
+        <v>Auckland, New Zealand</v>
+      </c>
+      <c r="M48">
+        <v>2.8301369863013699</v>
+      </c>
+      <c r="N48" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="49" spans="6:7">
+      <c r="F49">
+        <f>COUNTIF(F23:F48, "Accounting")</f>
+        <v>26</v>
+      </c>
+      <c r="G49">
+        <f>COUNT(G23:G48)</f>
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="E7:E18">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{F62BC468-49DA-4ED9-9010-343A55DAD995}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{F62BC468-49DA-4ED9-9010-343A55DAD995}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E7:E18</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE182796-6443-4558-9B87-909B73329DFC}">
   <dimension ref="A1:O267"/>
@@ -8471,7 +10012,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:15" hidden="1">
+    <row r="8" spans="1:15">
       <c r="C8" t="s">
         <v>42</v>
       </c>
@@ -8512,7 +10053,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:15" hidden="1">
+    <row r="9" spans="1:15">
       <c r="C9" t="s">
         <v>51</v>
       </c>
@@ -8635,7 +10176,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:15" hidden="1">
+    <row r="12" spans="1:15">
       <c r="C12" t="s">
         <v>61</v>
       </c>
@@ -8676,7 +10217,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="1:15" hidden="1">
+    <row r="13" spans="1:15">
       <c r="C13" t="s">
         <v>68</v>
       </c>
@@ -8717,7 +10258,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:15" hidden="1">
+    <row r="14" spans="1:15">
       <c r="C14" t="s">
         <v>72</v>
       </c>
@@ -8758,7 +10299,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:15" hidden="1">
+    <row r="15" spans="1:15">
       <c r="C15" t="s">
         <v>75</v>
       </c>
@@ -8799,7 +10340,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:15" hidden="1">
+    <row r="16" spans="1:15">
       <c r="C16" t="s">
         <v>79</v>
       </c>
@@ -8840,7 +10381,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="3:15" hidden="1">
+    <row r="17" spans="3:15">
       <c r="C17" t="s">
         <v>83</v>
       </c>
@@ -8881,7 +10422,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="3:15" hidden="1">
+    <row r="18" spans="3:15">
       <c r="C18" t="s">
         <v>87</v>
       </c>
@@ -8922,7 +10463,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="3:15" hidden="1">
+    <row r="19" spans="3:15">
       <c r="C19" t="s">
         <v>90</v>
       </c>
@@ -8963,7 +10504,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:15" hidden="1">
+    <row r="20" spans="3:15">
       <c r="C20" t="s">
         <v>94</v>
       </c>
@@ -9004,7 +10545,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="3:15" hidden="1">
+    <row r="21" spans="3:15">
       <c r="C21" t="s">
         <v>98</v>
       </c>
@@ -9045,7 +10586,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:15" hidden="1">
+    <row r="22" spans="3:15">
       <c r="C22" t="s">
         <v>102</v>
       </c>
@@ -9086,7 +10627,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="3:15" hidden="1">
+    <row r="23" spans="3:15">
       <c r="C23" t="s">
         <v>106</v>
       </c>
@@ -9127,7 +10668,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="3:15" hidden="1">
+    <row r="24" spans="3:15">
       <c r="C24" t="s">
         <v>110</v>
       </c>
@@ -9168,7 +10709,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="3:15" hidden="1">
+    <row r="25" spans="3:15">
       <c r="C25" t="s">
         <v>113</v>
       </c>
@@ -9209,7 +10750,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="3:15" hidden="1">
+    <row r="26" spans="3:15">
       <c r="C26" t="s">
         <v>117</v>
       </c>
@@ -9250,7 +10791,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="27" spans="3:15" hidden="1">
+    <row r="27" spans="3:15">
       <c r="C27" t="s">
         <v>120</v>
       </c>
@@ -9291,7 +10832,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="3:15" hidden="1">
+    <row r="28" spans="3:15">
       <c r="C28" t="s">
         <v>124</v>
       </c>
@@ -9332,7 +10873,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="3:15" hidden="1">
+    <row r="29" spans="3:15">
       <c r="C29" t="s">
         <v>127</v>
       </c>
@@ -9373,7 +10914,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="3:15" hidden="1">
+    <row r="30" spans="3:15">
       <c r="C30" t="s">
         <v>130</v>
       </c>
@@ -9414,7 +10955,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="31" spans="3:15" hidden="1">
+    <row r="31" spans="3:15">
       <c r="C31" t="s">
         <v>133</v>
       </c>
@@ -9455,7 +10996,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="32" spans="3:15" hidden="1">
+    <row r="32" spans="3:15">
       <c r="C32" t="s">
         <v>133</v>
       </c>
@@ -9496,7 +11037,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="33" spans="3:15" hidden="1">
+    <row r="33" spans="3:15">
       <c r="C33" t="s">
         <v>136</v>
       </c>
@@ -9537,7 +11078,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="34" spans="3:15" hidden="1">
+    <row r="34" spans="3:15">
       <c r="C34" t="s">
         <v>139</v>
       </c>
@@ -9578,7 +11119,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="35" spans="3:15" hidden="1">
+    <row r="35" spans="3:15">
       <c r="C35" t="s">
         <v>142</v>
       </c>
@@ -9619,7 +11160,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="36" spans="3:15" hidden="1">
+    <row r="36" spans="3:15">
       <c r="C36" t="s">
         <v>146</v>
       </c>
@@ -9660,7 +11201,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="3:15" hidden="1">
+    <row r="37" spans="3:15">
       <c r="C37" t="s">
         <v>149</v>
       </c>
@@ -9701,7 +11242,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="38" spans="3:15" hidden="1">
+    <row r="38" spans="3:15">
       <c r="C38" t="s">
         <v>152</v>
       </c>
@@ -9742,7 +11283,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="39" spans="3:15" hidden="1">
+    <row r="39" spans="3:15">
       <c r="C39" t="s">
         <v>156</v>
       </c>
@@ -9783,7 +11324,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="40" spans="3:15" hidden="1">
+    <row r="40" spans="3:15">
       <c r="C40" t="s">
         <v>159</v>
       </c>
@@ -9824,7 +11365,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="41" spans="3:15" hidden="1">
+    <row r="41" spans="3:15">
       <c r="C41" t="s">
         <v>162</v>
       </c>
@@ -9865,7 +11406,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="3:15" hidden="1">
+    <row r="42" spans="3:15">
       <c r="C42" t="s">
         <v>165</v>
       </c>
@@ -9906,7 +11447,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="3:15" hidden="1">
+    <row r="43" spans="3:15">
       <c r="C43" t="s">
         <v>168</v>
       </c>
@@ -9947,7 +11488,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="44" spans="3:15" hidden="1">
+    <row r="44" spans="3:15">
       <c r="C44" t="s">
         <v>171</v>
       </c>
@@ -9988,7 +11529,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="45" spans="3:15" hidden="1">
+    <row r="45" spans="3:15">
       <c r="C45" t="s">
         <v>174</v>
       </c>
@@ -10029,7 +11570,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="46" spans="3:15" hidden="1">
+    <row r="46" spans="3:15">
       <c r="C46" t="s">
         <v>177</v>
       </c>
@@ -10070,7 +11611,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="47" spans="3:15" hidden="1">
+    <row r="47" spans="3:15">
       <c r="C47" t="s">
         <v>180</v>
       </c>
@@ -10111,7 +11652,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="48" spans="3:15" hidden="1">
+    <row r="48" spans="3:15">
       <c r="C48" t="s">
         <v>183</v>
       </c>
@@ -10152,7 +11693,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="49" spans="3:15" hidden="1">
+    <row r="49" spans="3:15">
       <c r="C49" t="s">
         <v>186</v>
       </c>
@@ -10193,7 +11734,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="50" spans="3:15" hidden="1">
+    <row r="50" spans="3:15">
       <c r="C50" t="s">
         <v>189</v>
       </c>
@@ -10234,7 +11775,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="51" spans="3:15" hidden="1">
+    <row r="51" spans="3:15">
       <c r="C51" t="s">
         <v>192</v>
       </c>
@@ -10275,7 +11816,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="52" spans="3:15" hidden="1">
+    <row r="52" spans="3:15">
       <c r="C52" t="s">
         <v>192</v>
       </c>
@@ -10316,7 +11857,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="53" spans="3:15" hidden="1">
+    <row r="53" spans="3:15">
       <c r="C53" t="s">
         <v>197</v>
       </c>
@@ -10357,7 +11898,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="54" spans="3:15" hidden="1">
+    <row r="54" spans="3:15">
       <c r="C54" t="s">
         <v>200</v>
       </c>
@@ -10398,7 +11939,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="3:15" hidden="1">
+    <row r="55" spans="3:15">
       <c r="C55" t="s">
         <v>203</v>
       </c>
@@ -10439,7 +11980,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="56" spans="3:15" hidden="1">
+    <row r="56" spans="3:15">
       <c r="C56" t="s">
         <v>206</v>
       </c>
@@ -10521,7 +12062,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="58" spans="3:15" hidden="1">
+    <row r="58" spans="3:15">
       <c r="C58" t="s">
         <v>210</v>
       </c>
@@ -10562,7 +12103,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="59" spans="3:15" hidden="1">
+    <row r="59" spans="3:15">
       <c r="C59" t="s">
         <v>213</v>
       </c>
@@ -10603,7 +12144,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="60" spans="3:15" hidden="1">
+    <row r="60" spans="3:15">
       <c r="C60" t="s">
         <v>216</v>
       </c>
@@ -10644,7 +12185,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="61" spans="3:15" hidden="1">
+    <row r="61" spans="3:15">
       <c r="C61" t="s">
         <v>220</v>
       </c>
@@ -10685,7 +12226,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="62" spans="3:15" hidden="1">
+    <row r="62" spans="3:15">
       <c r="C62" t="s">
         <v>223</v>
       </c>
@@ -10726,7 +12267,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="63" spans="3:15" hidden="1">
+    <row r="63" spans="3:15">
       <c r="C63" t="s">
         <v>226</v>
       </c>
@@ -10767,7 +12308,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="64" spans="3:15" hidden="1">
+    <row r="64" spans="3:15">
       <c r="C64" t="s">
         <v>229</v>
       </c>
@@ -10808,7 +12349,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="65" spans="3:15" hidden="1">
+    <row r="65" spans="3:15">
       <c r="C65" t="s">
         <v>232</v>
       </c>
@@ -10849,7 +12390,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="66" spans="3:15" hidden="1">
+    <row r="66" spans="3:15">
       <c r="C66" t="s">
         <v>235</v>
       </c>
@@ -10890,7 +12431,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="67" spans="3:15" hidden="1">
+    <row r="67" spans="3:15">
       <c r="C67" t="s">
         <v>238</v>
       </c>
@@ -10931,7 +12472,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="68" spans="3:15" hidden="1">
+    <row r="68" spans="3:15">
       <c r="C68" t="s">
         <v>241</v>
       </c>
@@ -10972,7 +12513,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="69" spans="3:15" hidden="1">
+    <row r="69" spans="3:15">
       <c r="C69" t="s">
         <v>244</v>
       </c>
@@ -11013,7 +12554,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="70" spans="3:15" hidden="1">
+    <row r="70" spans="3:15">
       <c r="C70" t="s">
         <v>247</v>
       </c>
@@ -11054,7 +12595,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="71" spans="3:15" hidden="1">
+    <row r="71" spans="3:15">
       <c r="C71" t="s">
         <v>248</v>
       </c>
@@ -11095,7 +12636,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="72" spans="3:15" hidden="1">
+    <row r="72" spans="3:15">
       <c r="C72" t="s">
         <v>251</v>
       </c>
@@ -11136,7 +12677,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="73" spans="3:15" hidden="1">
+    <row r="73" spans="3:15">
       <c r="C73" t="s">
         <v>254</v>
       </c>
@@ -11177,7 +12718,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="74" spans="3:15" hidden="1">
+    <row r="74" spans="3:15">
       <c r="C74" t="s">
         <v>257</v>
       </c>
@@ -11218,7 +12759,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="75" spans="3:15" hidden="1">
+    <row r="75" spans="3:15">
       <c r="C75" t="s">
         <v>260</v>
       </c>
@@ -11259,7 +12800,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="76" spans="3:15" hidden="1">
+    <row r="76" spans="3:15">
       <c r="C76" t="s">
         <v>260</v>
       </c>
@@ -11300,7 +12841,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="77" spans="3:15" hidden="1">
+    <row r="77" spans="3:15">
       <c r="C77" t="s">
         <v>265</v>
       </c>
@@ -11341,7 +12882,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="78" spans="3:15" hidden="1">
+    <row r="78" spans="3:15">
       <c r="C78" t="s">
         <v>268</v>
       </c>
@@ -11382,7 +12923,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="79" spans="3:15" hidden="1">
+    <row r="79" spans="3:15">
       <c r="C79" t="s">
         <v>271</v>
       </c>
@@ -11423,7 +12964,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="80" spans="3:15" hidden="1">
+    <row r="80" spans="3:15">
       <c r="C80" t="s">
         <v>274</v>
       </c>
@@ -11464,7 +13005,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="81" spans="3:15" hidden="1">
+    <row r="81" spans="3:15">
       <c r="C81" t="s">
         <v>277</v>
       </c>
@@ -11505,7 +13046,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="82" spans="3:15" hidden="1">
+    <row r="82" spans="3:15">
       <c r="C82" t="s">
         <v>280</v>
       </c>
@@ -11546,7 +13087,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="83" spans="3:15" hidden="1">
+    <row r="83" spans="3:15">
       <c r="C83" t="s">
         <v>283</v>
       </c>
@@ -11587,7 +13128,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="84" spans="3:15" hidden="1">
+    <row r="84" spans="3:15">
       <c r="C84" t="s">
         <v>286</v>
       </c>
@@ -11628,7 +13169,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="85" spans="3:15" hidden="1">
+    <row r="85" spans="3:15">
       <c r="C85" t="s">
         <v>289</v>
       </c>
@@ -11669,7 +13210,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="86" spans="3:15" hidden="1">
+    <row r="86" spans="3:15">
       <c r="C86" t="s">
         <v>292</v>
       </c>
@@ -11710,7 +13251,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="87" spans="3:15" hidden="1">
+    <row r="87" spans="3:15">
       <c r="C87" t="s">
         <v>295</v>
       </c>
@@ -11751,7 +13292,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="88" spans="3:15" hidden="1">
+    <row r="88" spans="3:15">
       <c r="C88" t="s">
         <v>298</v>
       </c>
@@ -11792,7 +13333,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="89" spans="3:15" hidden="1">
+    <row r="89" spans="3:15">
       <c r="C89" t="s">
         <v>301</v>
       </c>
@@ -11833,7 +13374,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="90" spans="3:15" hidden="1">
+    <row r="90" spans="3:15">
       <c r="C90" t="s">
         <v>304</v>
       </c>
@@ -11874,7 +13415,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="91" spans="3:15" hidden="1">
+    <row r="91" spans="3:15">
       <c r="C91" t="s">
         <v>304</v>
       </c>
@@ -11915,7 +13456,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="92" spans="3:15" hidden="1">
+    <row r="92" spans="3:15">
       <c r="C92" t="s">
         <v>309</v>
       </c>
@@ -11956,7 +13497,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="93" spans="3:15" hidden="1">
+    <row r="93" spans="3:15">
       <c r="C93" t="s">
         <v>309</v>
       </c>
@@ -11997,7 +13538,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="94" spans="3:15" hidden="1">
+    <row r="94" spans="3:15">
       <c r="C94" t="s">
         <v>312</v>
       </c>
@@ -12038,7 +13579,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="95" spans="3:15" hidden="1">
+    <row r="95" spans="3:15">
       <c r="C95" t="s">
         <v>315</v>
       </c>
@@ -12079,7 +13620,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="96" spans="3:15" hidden="1">
+    <row r="96" spans="3:15">
       <c r="C96" t="s">
         <v>318</v>
       </c>
@@ -12120,7 +13661,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="97" spans="3:15" hidden="1">
+    <row r="97" spans="3:15">
       <c r="C97" t="s">
         <v>321</v>
       </c>
@@ -12161,7 +13702,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="98" spans="3:15" hidden="1">
+    <row r="98" spans="3:15">
       <c r="C98" t="s">
         <v>324</v>
       </c>
@@ -12202,7 +13743,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="99" spans="3:15" hidden="1">
+    <row r="99" spans="3:15">
       <c r="C99" t="s">
         <v>327</v>
       </c>
@@ -12243,7 +13784,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="100" spans="3:15" hidden="1">
+    <row r="100" spans="3:15">
       <c r="C100" t="s">
         <v>330</v>
       </c>
@@ -12284,7 +13825,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="101" spans="3:15" hidden="1">
+    <row r="101" spans="3:15">
       <c r="C101" t="s">
         <v>333</v>
       </c>
@@ -12325,7 +13866,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="102" spans="3:15" hidden="1">
+    <row r="102" spans="3:15">
       <c r="C102" t="s">
         <v>333</v>
       </c>
@@ -12366,7 +13907,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="103" spans="3:15" hidden="1">
+    <row r="103" spans="3:15">
       <c r="C103" t="s">
         <v>336</v>
       </c>
@@ -12407,7 +13948,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="104" spans="3:15" hidden="1">
+    <row r="104" spans="3:15">
       <c r="C104" t="s">
         <v>339</v>
       </c>
@@ -12448,7 +13989,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="105" spans="3:15" hidden="1">
+    <row r="105" spans="3:15">
       <c r="C105" t="s">
         <v>342</v>
       </c>
@@ -12489,7 +14030,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="106" spans="3:15" hidden="1">
+    <row r="106" spans="3:15">
       <c r="C106" t="s">
         <v>345</v>
       </c>
@@ -12530,7 +14071,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="107" spans="3:15" hidden="1">
+    <row r="107" spans="3:15">
       <c r="C107" t="s">
         <v>348</v>
       </c>
@@ -12571,7 +14112,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="108" spans="3:15" hidden="1">
+    <row r="108" spans="3:15">
       <c r="C108" t="s">
         <v>351</v>
       </c>
@@ -12612,7 +14153,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="109" spans="3:15" hidden="1">
+    <row r="109" spans="3:15">
       <c r="C109" t="s">
         <v>354</v>
       </c>
@@ -12653,7 +14194,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="110" spans="3:15" hidden="1">
+    <row r="110" spans="3:15">
       <c r="C110" t="s">
         <v>354</v>
       </c>
@@ -12694,7 +14235,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="111" spans="3:15" hidden="1">
+    <row r="111" spans="3:15">
       <c r="C111" t="s">
         <v>357</v>
       </c>
@@ -12735,7 +14276,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="112" spans="3:15" hidden="1">
+    <row r="112" spans="3:15">
       <c r="C112" t="s">
         <v>360</v>
       </c>
@@ -12776,7 +14317,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="113" spans="3:15" hidden="1">
+    <row r="113" spans="3:15">
       <c r="C113" t="s">
         <v>363</v>
       </c>
@@ -12817,7 +14358,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="114" spans="3:15" hidden="1">
+    <row r="114" spans="3:15">
       <c r="C114" t="s">
         <v>366</v>
       </c>
@@ -12858,7 +14399,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="115" spans="3:15" hidden="1">
+    <row r="115" spans="3:15">
       <c r="C115" t="s">
         <v>366</v>
       </c>
@@ -12899,7 +14440,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="116" spans="3:15" hidden="1">
+    <row r="116" spans="3:15">
       <c r="C116" t="s">
         <v>369</v>
       </c>
@@ -12940,7 +14481,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="117" spans="3:15" hidden="1">
+    <row r="117" spans="3:15">
       <c r="C117" t="s">
         <v>372</v>
       </c>
@@ -12981,7 +14522,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="118" spans="3:15" hidden="1">
+    <row r="118" spans="3:15">
       <c r="C118" t="s">
         <v>375</v>
       </c>
@@ -13022,7 +14563,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="119" spans="3:15" hidden="1">
+    <row r="119" spans="3:15">
       <c r="C119" t="s">
         <v>378</v>
       </c>
@@ -13063,7 +14604,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="120" spans="3:15" hidden="1">
+    <row r="120" spans="3:15">
       <c r="C120" t="s">
         <v>381</v>
       </c>
@@ -13104,7 +14645,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="121" spans="3:15" hidden="1">
+    <row r="121" spans="3:15">
       <c r="C121" t="s">
         <v>384</v>
       </c>
@@ -13145,7 +14686,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="122" spans="3:15" hidden="1">
+    <row r="122" spans="3:15">
       <c r="C122" t="s">
         <v>387</v>
       </c>
@@ -13186,7 +14727,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="123" spans="3:15" hidden="1">
+    <row r="123" spans="3:15">
       <c r="C123" t="s">
         <v>390</v>
       </c>
@@ -13227,7 +14768,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="124" spans="3:15" hidden="1">
+    <row r="124" spans="3:15">
       <c r="C124" t="s">
         <v>393</v>
       </c>
@@ -13268,7 +14809,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="125" spans="3:15" hidden="1">
+    <row r="125" spans="3:15">
       <c r="C125" t="s">
         <v>396</v>
       </c>
@@ -13309,7 +14850,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="126" spans="3:15" hidden="1">
+    <row r="126" spans="3:15">
       <c r="C126" t="s">
         <v>399</v>
       </c>
@@ -13350,7 +14891,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="127" spans="3:15" hidden="1">
+    <row r="127" spans="3:15">
       <c r="C127" t="s">
         <v>402</v>
       </c>
@@ -13391,7 +14932,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="128" spans="3:15" hidden="1">
+    <row r="128" spans="3:15">
       <c r="C128" t="s">
         <v>405</v>
       </c>
@@ -13432,7 +14973,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="129" spans="3:15" hidden="1">
+    <row r="129" spans="3:15">
       <c r="C129" t="s">
         <v>408</v>
       </c>
@@ -13473,7 +15014,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="130" spans="3:15" hidden="1">
+    <row r="130" spans="3:15">
       <c r="C130" t="s">
         <v>411</v>
       </c>
@@ -13514,7 +15055,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="131" spans="3:15" hidden="1">
+    <row r="131" spans="3:15">
       <c r="C131" t="s">
         <v>414</v>
       </c>
@@ -13555,7 +15096,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="132" spans="3:15" hidden="1">
+    <row r="132" spans="3:15">
       <c r="C132" t="s">
         <v>417</v>
       </c>
@@ -13596,7 +15137,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="133" spans="3:15" hidden="1">
+    <row r="133" spans="3:15">
       <c r="C133" t="s">
         <v>420</v>
       </c>
@@ -13637,7 +15178,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="134" spans="3:15" hidden="1">
+    <row r="134" spans="3:15">
       <c r="C134" t="s">
         <v>420</v>
       </c>
@@ -13678,7 +15219,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="135" spans="3:15" hidden="1">
+    <row r="135" spans="3:15">
       <c r="C135" t="s">
         <v>425</v>
       </c>
@@ -13719,7 +15260,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="136" spans="3:15" hidden="1">
+    <row r="136" spans="3:15">
       <c r="C136" t="s">
         <v>428</v>
       </c>
@@ -13760,7 +15301,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="137" spans="3:15" hidden="1">
+    <row r="137" spans="3:15">
       <c r="C137" t="s">
         <v>431</v>
       </c>
@@ -13801,7 +15342,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="138" spans="3:15" hidden="1">
+    <row r="138" spans="3:15">
       <c r="C138" t="s">
         <v>434</v>
       </c>
@@ -13842,7 +15383,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="139" spans="3:15" hidden="1">
+    <row r="139" spans="3:15">
       <c r="C139" t="s">
         <v>437</v>
       </c>
@@ -13883,7 +15424,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="140" spans="3:15" hidden="1">
+    <row r="140" spans="3:15">
       <c r="C140" t="s">
         <v>440</v>
       </c>
@@ -13924,7 +15465,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="141" spans="3:15" hidden="1">
+    <row r="141" spans="3:15">
       <c r="C141" t="s">
         <v>443</v>
       </c>
@@ -13965,7 +15506,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="142" spans="3:15" hidden="1">
+    <row r="142" spans="3:15">
       <c r="C142" t="s">
         <v>446</v>
       </c>
@@ -14006,7 +15547,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="143" spans="3:15" hidden="1">
+    <row r="143" spans="3:15">
       <c r="C143" t="s">
         <v>446</v>
       </c>
@@ -14047,7 +15588,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="144" spans="3:15" hidden="1">
+    <row r="144" spans="3:15">
       <c r="C144" t="s">
         <v>449</v>
       </c>
@@ -14088,7 +15629,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="145" spans="3:15" hidden="1">
+    <row r="145" spans="3:15">
       <c r="C145" t="s">
         <v>452</v>
       </c>
@@ -14129,7 +15670,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="146" spans="3:15" hidden="1">
+    <row r="146" spans="3:15">
       <c r="C146" t="s">
         <v>455</v>
       </c>
@@ -14170,7 +15711,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="147" spans="3:15" hidden="1">
+    <row r="147" spans="3:15">
       <c r="C147" t="s">
         <v>458</v>
       </c>
@@ -14211,7 +15752,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="148" spans="3:15" hidden="1">
+    <row r="148" spans="3:15">
       <c r="C148" t="s">
         <v>458</v>
       </c>
@@ -14252,7 +15793,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="149" spans="3:15" hidden="1">
+    <row r="149" spans="3:15">
       <c r="C149" t="s">
         <v>463</v>
       </c>
@@ -14293,7 +15834,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="150" spans="3:15" hidden="1">
+    <row r="150" spans="3:15">
       <c r="C150" t="s">
         <v>466</v>
       </c>
@@ -14334,7 +15875,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="151" spans="3:15" hidden="1">
+    <row r="151" spans="3:15">
       <c r="C151" t="s">
         <v>469</v>
       </c>
@@ -14375,7 +15916,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="152" spans="3:15" hidden="1">
+    <row r="152" spans="3:15">
       <c r="C152" t="s">
         <v>472</v>
       </c>
@@ -14416,7 +15957,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="153" spans="3:15" hidden="1">
+    <row r="153" spans="3:15">
       <c r="C153" t="s">
         <v>475</v>
       </c>
@@ -14457,7 +15998,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="154" spans="3:15" hidden="1">
+    <row r="154" spans="3:15">
       <c r="C154" t="s">
         <v>475</v>
       </c>
@@ -14498,7 +16039,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="155" spans="3:15" hidden="1">
+    <row r="155" spans="3:15">
       <c r="C155" t="s">
         <v>478</v>
       </c>
@@ -14539,7 +16080,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="156" spans="3:15" hidden="1">
+    <row r="156" spans="3:15">
       <c r="C156" t="s">
         <v>481</v>
       </c>
@@ -14580,7 +16121,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="157" spans="3:15" hidden="1">
+    <row r="157" spans="3:15">
       <c r="C157" t="s">
         <v>484</v>
       </c>
@@ -14621,7 +16162,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="158" spans="3:15" hidden="1">
+    <row r="158" spans="3:15">
       <c r="C158" t="s">
         <v>484</v>
       </c>
@@ -14662,7 +16203,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="159" spans="3:15" hidden="1">
+    <row r="159" spans="3:15">
       <c r="C159" t="s">
         <v>487</v>
       </c>
@@ -14703,7 +16244,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="160" spans="3:15" hidden="1">
+    <row r="160" spans="3:15">
       <c r="C160" t="s">
         <v>490</v>
       </c>
@@ -14744,7 +16285,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="161" spans="3:15" hidden="1">
+    <row r="161" spans="3:15">
       <c r="C161" t="s">
         <v>491</v>
       </c>
@@ -14785,7 +16326,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="162" spans="3:15" hidden="1">
+    <row r="162" spans="3:15">
       <c r="C162" t="s">
         <v>494</v>
       </c>
@@ -14826,7 +16367,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="163" spans="3:15" hidden="1">
+    <row r="163" spans="3:15">
       <c r="C163" t="s">
         <v>497</v>
       </c>
@@ -14867,7 +16408,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="164" spans="3:15" hidden="1">
+    <row r="164" spans="3:15">
       <c r="C164" t="s">
         <v>500</v>
       </c>
@@ -14908,7 +16449,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="165" spans="3:15" hidden="1">
+    <row r="165" spans="3:15">
       <c r="C165" t="s">
         <v>503</v>
       </c>
@@ -14949,7 +16490,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="166" spans="3:15" hidden="1">
+    <row r="166" spans="3:15">
       <c r="C166" t="s">
         <v>503</v>
       </c>
@@ -14990,7 +16531,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="167" spans="3:15" hidden="1">
+    <row r="167" spans="3:15">
       <c r="C167" t="s">
         <v>506</v>
       </c>
@@ -15031,7 +16572,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="168" spans="3:15" hidden="1">
+    <row r="168" spans="3:15">
       <c r="C168" t="s">
         <v>506</v>
       </c>
@@ -15072,7 +16613,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="169" spans="3:15" hidden="1">
+    <row r="169" spans="3:15">
       <c r="C169" t="s">
         <v>509</v>
       </c>
@@ -15113,7 +16654,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="170" spans="3:15" hidden="1">
+    <row r="170" spans="3:15">
       <c r="C170" t="s">
         <v>512</v>
       </c>
@@ -15154,7 +16695,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="171" spans="3:15" hidden="1">
+    <row r="171" spans="3:15">
       <c r="C171" t="s">
         <v>515</v>
       </c>
@@ -15195,7 +16736,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="172" spans="3:15" hidden="1">
+    <row r="172" spans="3:15">
       <c r="C172" t="s">
         <v>518</v>
       </c>
@@ -15236,7 +16777,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="173" spans="3:15" hidden="1">
+    <row r="173" spans="3:15">
       <c r="C173" t="s">
         <v>521</v>
       </c>
@@ -15277,7 +16818,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="174" spans="3:15" hidden="1">
+    <row r="174" spans="3:15">
       <c r="C174" t="s">
         <v>524</v>
       </c>
@@ -15318,7 +16859,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="175" spans="3:15" hidden="1">
+    <row r="175" spans="3:15">
       <c r="C175" t="s">
         <v>524</v>
       </c>
@@ -15359,7 +16900,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="176" spans="3:15" hidden="1">
+    <row r="176" spans="3:15">
       <c r="C176" t="s">
         <v>528</v>
       </c>
@@ -15400,7 +16941,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="177" spans="3:15" hidden="1">
+    <row r="177" spans="3:15">
       <c r="C177" t="s">
         <v>532</v>
       </c>
@@ -15441,7 +16982,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="178" spans="3:15" hidden="1">
+    <row r="178" spans="3:15">
       <c r="C178" t="s">
         <v>535</v>
       </c>
@@ -15482,7 +17023,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="179" spans="3:15" hidden="1">
+    <row r="179" spans="3:15">
       <c r="C179" t="s">
         <v>535</v>
       </c>
@@ -15523,7 +17064,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="180" spans="3:15" hidden="1">
+    <row r="180" spans="3:15">
       <c r="C180" t="s">
         <v>538</v>
       </c>
@@ -15564,7 +17105,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="181" spans="3:15" hidden="1">
+    <row r="181" spans="3:15">
       <c r="C181" t="s">
         <v>541</v>
       </c>
@@ -15605,7 +17146,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="182" spans="3:15" hidden="1">
+    <row r="182" spans="3:15">
       <c r="C182" t="s">
         <v>542</v>
       </c>
@@ -15646,7 +17187,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="183" spans="3:15" hidden="1">
+    <row r="183" spans="3:15">
       <c r="C183" t="s">
         <v>545</v>
       </c>
@@ -15687,7 +17228,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="184" spans="3:15" hidden="1">
+    <row r="184" spans="3:15">
       <c r="C184" t="s">
         <v>548</v>
       </c>
@@ -15728,7 +17269,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="185" spans="3:15" hidden="1">
+    <row r="185" spans="3:15">
       <c r="C185" t="s">
         <v>548</v>
       </c>
@@ -15769,7 +17310,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="186" spans="3:15" hidden="1">
+    <row r="186" spans="3:15">
       <c r="C186" t="s">
         <v>551</v>
       </c>
@@ -15810,7 +17351,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="187" spans="3:15" hidden="1">
+    <row r="187" spans="3:15">
       <c r="C187" t="s">
         <v>551</v>
       </c>
@@ -15851,7 +17392,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="188" spans="3:15" hidden="1">
+    <row r="188" spans="3:15">
       <c r="C188" t="s">
         <v>556</v>
       </c>
@@ -15892,7 +17433,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="189" spans="3:15" hidden="1">
+    <row r="189" spans="3:15">
       <c r="C189" t="s">
         <v>559</v>
       </c>
@@ -15933,7 +17474,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="190" spans="3:15" hidden="1">
+    <row r="190" spans="3:15">
       <c r="C190" t="s">
         <v>562</v>
       </c>
@@ -15974,7 +17515,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="191" spans="3:15" hidden="1">
+    <row r="191" spans="3:15">
       <c r="C191" t="s">
         <v>565</v>
       </c>
@@ -16015,7 +17556,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="192" spans="3:15" hidden="1">
+    <row r="192" spans="3:15">
       <c r="C192" t="s">
         <v>568</v>
       </c>
@@ -16056,7 +17597,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="193" spans="3:15" hidden="1">
+    <row r="193" spans="3:15">
       <c r="C193" t="s">
         <v>571</v>
       </c>
@@ -16097,7 +17638,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="194" spans="3:15" hidden="1">
+    <row r="194" spans="3:15">
       <c r="C194" t="s">
         <v>574</v>
       </c>
@@ -16138,7 +17679,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="195" spans="3:15" hidden="1">
+    <row r="195" spans="3:15">
       <c r="C195" t="s">
         <v>574</v>
       </c>
@@ -16179,7 +17720,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="196" spans="3:15" hidden="1">
+    <row r="196" spans="3:15">
       <c r="C196" t="s">
         <v>576</v>
       </c>
@@ -16220,7 +17761,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="197" spans="3:15" hidden="1">
+    <row r="197" spans="3:15">
       <c r="C197" t="s">
         <v>579</v>
       </c>
@@ -16261,7 +17802,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="198" spans="3:15" hidden="1">
+    <row r="198" spans="3:15">
       <c r="C198" t="s">
         <v>582</v>
       </c>
@@ -16302,7 +17843,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="199" spans="3:15" hidden="1">
+    <row r="199" spans="3:15">
       <c r="C199" t="s">
         <v>585</v>
       </c>
@@ -16343,7 +17884,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="200" spans="3:15" hidden="1">
+    <row r="200" spans="3:15">
       <c r="C200" t="s">
         <v>588</v>
       </c>
@@ -16384,7 +17925,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="201" spans="3:15" hidden="1">
+    <row r="201" spans="3:15">
       <c r="C201" t="s">
         <v>591</v>
       </c>
@@ -16425,7 +17966,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="202" spans="3:15" hidden="1">
+    <row r="202" spans="3:15">
       <c r="C202" t="s">
         <v>594</v>
       </c>
@@ -16466,7 +18007,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="203" spans="3:15" hidden="1">
+    <row r="203" spans="3:15">
       <c r="C203" t="s">
         <v>596</v>
       </c>
@@ -16507,7 +18048,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="204" spans="3:15" hidden="1">
+    <row r="204" spans="3:15">
       <c r="C204" t="s">
         <v>599</v>
       </c>
@@ -16548,7 +18089,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="205" spans="3:15" hidden="1">
+    <row r="205" spans="3:15">
       <c r="C205" t="s">
         <v>602</v>
       </c>
@@ -16589,7 +18130,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="206" spans="3:15" hidden="1">
+    <row r="206" spans="3:15">
       <c r="C206" t="s">
         <v>602</v>
       </c>
@@ -16630,7 +18171,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="207" spans="3:15" hidden="1">
+    <row r="207" spans="3:15">
       <c r="C207" t="s">
         <v>605</v>
       </c>
@@ -16671,7 +18212,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="208" spans="3:15" hidden="1">
+    <row r="208" spans="3:15">
       <c r="C208" t="s">
         <v>608</v>
       </c>
@@ -16712,7 +18253,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="209" spans="3:15" hidden="1">
+    <row r="209" spans="3:15">
       <c r="C209" t="s">
         <v>611</v>
       </c>
@@ -16753,7 +18294,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="210" spans="3:15" hidden="1">
+    <row r="210" spans="3:15">
       <c r="C210" t="s">
         <v>614</v>
       </c>
@@ -16794,7 +18335,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="211" spans="3:15" hidden="1">
+    <row r="211" spans="3:15">
       <c r="C211" t="s">
         <v>617</v>
       </c>
@@ -16835,7 +18376,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="212" spans="3:15" hidden="1">
+    <row r="212" spans="3:15">
       <c r="C212" t="s">
         <v>620</v>
       </c>
@@ -16876,7 +18417,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="213" spans="3:15" hidden="1">
+    <row r="213" spans="3:15">
       <c r="C213" t="s">
         <v>623</v>
       </c>
@@ -16917,7 +18458,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="214" spans="3:15" hidden="1">
+    <row r="214" spans="3:15">
       <c r="C214" t="s">
         <v>626</v>
       </c>
@@ -16958,7 +18499,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="215" spans="3:15" hidden="1">
+    <row r="215" spans="3:15">
       <c r="C215" t="s">
         <v>629</v>
       </c>
@@ -16999,7 +18540,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="216" spans="3:15" hidden="1">
+    <row r="216" spans="3:15">
       <c r="C216" t="s">
         <v>629</v>
       </c>
@@ -17040,7 +18581,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="217" spans="3:15" hidden="1">
+    <row r="217" spans="3:15">
       <c r="C217" t="s">
         <v>634</v>
       </c>
@@ -17081,7 +18622,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="218" spans="3:15" hidden="1">
+    <row r="218" spans="3:15">
       <c r="C218" t="s">
         <v>637</v>
       </c>
@@ -17122,7 +18663,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="219" spans="3:15" hidden="1">
+    <row r="219" spans="3:15">
       <c r="C219" t="s">
         <v>640</v>
       </c>
@@ -17163,7 +18704,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="220" spans="3:15" hidden="1">
+    <row r="220" spans="3:15">
       <c r="C220" t="s">
         <v>643</v>
       </c>
@@ -17204,7 +18745,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="221" spans="3:15" hidden="1">
+    <row r="221" spans="3:15">
       <c r="C221" t="s">
         <v>646</v>
       </c>
@@ -17245,7 +18786,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="222" spans="3:15" hidden="1">
+    <row r="222" spans="3:15">
       <c r="C222" t="s">
         <v>649</v>
       </c>
@@ -17286,7 +18827,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="223" spans="3:15" hidden="1">
+    <row r="223" spans="3:15">
       <c r="C223" t="s">
         <v>649</v>
       </c>
@@ -17327,7 +18868,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="224" spans="3:15" hidden="1">
+    <row r="224" spans="3:15">
       <c r="C224" t="s">
         <v>652</v>
       </c>
@@ -17368,7 +18909,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="225" spans="3:15" hidden="1">
+    <row r="225" spans="3:15">
       <c r="C225" t="s">
         <v>655</v>
       </c>
@@ -17409,7 +18950,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="226" spans="3:15" hidden="1">
+    <row r="226" spans="3:15">
       <c r="C226" t="s">
         <v>658</v>
       </c>
@@ -17450,7 +18991,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="227" spans="3:15" hidden="1">
+    <row r="227" spans="3:15">
       <c r="C227" t="s">
         <v>662</v>
       </c>
@@ -17491,7 +19032,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="228" spans="3:15" hidden="1">
+    <row r="228" spans="3:15">
       <c r="C228" t="s">
         <v>662</v>
       </c>
@@ -17532,7 +19073,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="229" spans="3:15" hidden="1">
+    <row r="229" spans="3:15">
       <c r="C229" t="s">
         <v>665</v>
       </c>
@@ -17573,7 +19114,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="230" spans="3:15" hidden="1">
+    <row r="230" spans="3:15">
       <c r="C230" t="s">
         <v>668</v>
       </c>
@@ -17614,7 +19155,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="231" spans="3:15" hidden="1">
+    <row r="231" spans="3:15">
       <c r="C231" t="s">
         <v>668</v>
       </c>
@@ -17655,7 +19196,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="232" spans="3:15" hidden="1">
+    <row r="232" spans="3:15">
       <c r="C232" t="s">
         <v>671</v>
       </c>
@@ -17696,7 +19237,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="233" spans="3:15" hidden="1">
+    <row r="233" spans="3:15">
       <c r="C233" t="s">
         <v>674</v>
       </c>
@@ -17737,7 +19278,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="234" spans="3:15" hidden="1">
+    <row r="234" spans="3:15">
       <c r="C234" t="s">
         <v>677</v>
       </c>
@@ -17778,7 +19319,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="235" spans="3:15" hidden="1">
+    <row r="235" spans="3:15">
       <c r="C235" t="s">
         <v>680</v>
       </c>
@@ -17819,7 +19360,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="236" spans="3:15" hidden="1">
+    <row r="236" spans="3:15">
       <c r="C236" t="s">
         <v>683</v>
       </c>
@@ -17860,7 +19401,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="237" spans="3:15" hidden="1">
+    <row r="237" spans="3:15">
       <c r="C237" t="s">
         <v>686</v>
       </c>
@@ -17901,7 +19442,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="238" spans="3:15" hidden="1">
+    <row r="238" spans="3:15">
       <c r="C238" t="s">
         <v>689</v>
       </c>
@@ -17942,7 +19483,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="239" spans="3:15" hidden="1">
+    <row r="239" spans="3:15">
       <c r="C239" t="s">
         <v>692</v>
       </c>
@@ -17983,7 +19524,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="240" spans="3:15" hidden="1">
+    <row r="240" spans="3:15">
       <c r="C240" t="s">
         <v>695</v>
       </c>
@@ -18024,7 +19565,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="241" spans="3:15" hidden="1">
+    <row r="241" spans="3:15">
       <c r="C241" t="s">
         <v>695</v>
       </c>
@@ -18065,7 +19606,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="242" spans="3:15" hidden="1">
+    <row r="242" spans="3:15">
       <c r="C242" t="s">
         <v>698</v>
       </c>
@@ -18106,7 +19647,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="243" spans="3:15" hidden="1">
+    <row r="243" spans="3:15">
       <c r="C243" t="s">
         <v>701</v>
       </c>
@@ -18147,7 +19688,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="244" spans="3:15" hidden="1">
+    <row r="244" spans="3:15">
       <c r="C244" t="s">
         <v>701</v>
       </c>
@@ -18188,7 +19729,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="245" spans="3:15" hidden="1">
+    <row r="245" spans="3:15">
       <c r="C245" t="s">
         <v>704</v>
       </c>
@@ -18229,7 +19770,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="246" spans="3:15" hidden="1">
+    <row r="246" spans="3:15">
       <c r="C246" t="s">
         <v>707</v>
       </c>
@@ -18270,7 +19811,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="247" spans="3:15" hidden="1">
+    <row r="247" spans="3:15">
       <c r="C247" t="s">
         <v>710</v>
       </c>
@@ -18311,7 +19852,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="248" spans="3:15" hidden="1">
+    <row r="248" spans="3:15">
       <c r="C248" t="s">
         <v>713</v>
       </c>
@@ -18352,7 +19893,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="249" spans="3:15" hidden="1">
+    <row r="249" spans="3:15">
       <c r="C249" t="s">
         <v>716</v>
       </c>
@@ -18393,7 +19934,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="250" spans="3:15" hidden="1">
+    <row r="250" spans="3:15">
       <c r="C250" t="s">
         <v>719</v>
       </c>
@@ -18434,7 +19975,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="251" spans="3:15" hidden="1">
+    <row r="251" spans="3:15">
       <c r="C251" t="s">
         <v>722</v>
       </c>
@@ -18475,7 +20016,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="252" spans="3:15" hidden="1">
+    <row r="252" spans="3:15">
       <c r="C252" t="s">
         <v>725</v>
       </c>
@@ -18516,7 +20057,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="253" spans="3:15" hidden="1">
+    <row r="253" spans="3:15">
       <c r="C253" t="s">
         <v>725</v>
       </c>
@@ -18557,7 +20098,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="254" spans="3:15" hidden="1">
+    <row r="254" spans="3:15">
       <c r="C254" t="s">
         <v>728</v>
       </c>
@@ -18598,7 +20139,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="255" spans="3:15" hidden="1">
+    <row r="255" spans="3:15">
       <c r="C255" t="s">
         <v>728</v>
       </c>
@@ -18639,7 +20180,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="256" spans="3:15" hidden="1">
+    <row r="256" spans="3:15">
       <c r="C256" t="s">
         <v>733</v>
       </c>
@@ -18680,7 +20221,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="257" spans="3:15" hidden="1">
+    <row r="257" spans="3:15">
       <c r="C257" t="s">
         <v>736</v>
       </c>
@@ -18721,7 +20262,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="258" spans="3:15" hidden="1">
+    <row r="258" spans="3:15">
       <c r="C258" t="s">
         <v>739</v>
       </c>
@@ -18762,7 +20303,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="259" spans="3:15" hidden="1">
+    <row r="259" spans="3:15">
       <c r="C259" t="s">
         <v>739</v>
       </c>
@@ -18803,7 +20344,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="260" spans="3:15" hidden="1">
+    <row r="260" spans="3:15">
       <c r="C260" t="s">
         <v>744</v>
       </c>
@@ -18844,7 +20385,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="261" spans="3:15" hidden="1">
+    <row r="261" spans="3:15">
       <c r="C261" t="s">
         <v>747</v>
       </c>
@@ -18885,7 +20426,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="262" spans="3:15" hidden="1">
+    <row r="262" spans="3:15">
       <c r="C262" t="s">
         <v>750</v>
       </c>
@@ -18926,7 +20467,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="263" spans="3:15" hidden="1">
+    <row r="263" spans="3:15">
       <c r="C263" t="s">
         <v>753</v>
       </c>
@@ -18967,7 +20508,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="264" spans="3:15" hidden="1">
+    <row r="264" spans="3:15">
       <c r="C264" t="s">
         <v>756</v>
       </c>
@@ -19008,7 +20549,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="265" spans="3:15" hidden="1">
+    <row r="265" spans="3:15">
       <c r="C265" t="s">
         <v>759</v>
       </c>
@@ -19049,7 +20590,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="266" spans="3:15" hidden="1">
+    <row r="266" spans="3:15">
       <c r="C266" t="s">
         <v>762</v>
       </c>
@@ -19090,7 +20631,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="267" spans="3:15" hidden="1">
+    <row r="267" spans="3:15">
       <c r="C267" t="s">
         <v>765</v>
       </c>
